--- a/Journals/Front-end journal/Markup ჟურნალი.xlsx
+++ b/Journals/Front-end journal/Markup ჟურნალი.xlsx
@@ -524,6 +524,15 @@
     <xf numFmtId="10" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -536,23 +545,26 @@
     <xf numFmtId="14" fontId="2" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -582,16 +594,7 @@
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -605,17 +608,14 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -878,74 +878,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:166" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="36"/>
-      <c r="F1" s="28">
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="40"/>
+      <c r="F1" s="24">
         <v>5</v>
       </c>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="28">
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="24">
         <v>4</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28">
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="24">
         <v>6</v>
       </c>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="29"/>
-      <c r="R1" s="29"/>
-      <c r="S1" s="29"/>
-      <c r="T1" s="30"/>
-      <c r="U1" s="28">
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
+      <c r="R1" s="25"/>
+      <c r="S1" s="25"/>
+      <c r="T1" s="26"/>
+      <c r="U1" s="24">
         <v>4</v>
       </c>
-      <c r="V1" s="29"/>
-      <c r="W1" s="29"/>
-      <c r="X1" s="30"/>
-      <c r="Y1" s="28">
+      <c r="V1" s="25"/>
+      <c r="W1" s="25"/>
+      <c r="X1" s="26"/>
+      <c r="Y1" s="24">
         <v>5</v>
       </c>
-      <c r="Z1" s="29"/>
-      <c r="AA1" s="29"/>
-      <c r="AB1" s="29"/>
-      <c r="AC1" s="30"/>
-      <c r="AD1" s="28">
+      <c r="Z1" s="25"/>
+      <c r="AA1" s="25"/>
+      <c r="AB1" s="25"/>
+      <c r="AC1" s="26"/>
+      <c r="AD1" s="24">
         <v>4</v>
       </c>
-      <c r="AE1" s="29"/>
-      <c r="AF1" s="29"/>
-      <c r="AG1" s="30"/>
-      <c r="AH1" s="28">
+      <c r="AE1" s="25"/>
+      <c r="AF1" s="25"/>
+      <c r="AG1" s="26"/>
+      <c r="AH1" s="24">
         <v>6</v>
       </c>
-      <c r="AI1" s="29"/>
-      <c r="AJ1" s="29"/>
-      <c r="AK1" s="29"/>
-      <c r="AL1" s="29"/>
-      <c r="AM1" s="30"/>
-      <c r="AN1" s="28">
+      <c r="AI1" s="25"/>
+      <c r="AJ1" s="25"/>
+      <c r="AK1" s="25"/>
+      <c r="AL1" s="25"/>
+      <c r="AM1" s="26"/>
+      <c r="AN1" s="24">
         <v>6</v>
       </c>
-      <c r="AO1" s="29"/>
-      <c r="AP1" s="29"/>
-      <c r="AQ1" s="29"/>
-      <c r="AR1" s="29"/>
-      <c r="AS1" s="30"/>
-      <c r="AT1" s="28">
+      <c r="AO1" s="25"/>
+      <c r="AP1" s="25"/>
+      <c r="AQ1" s="25"/>
+      <c r="AR1" s="25"/>
+      <c r="AS1" s="26"/>
+      <c r="AT1" s="24">
         <v>4</v>
       </c>
-      <c r="AU1" s="29"/>
-      <c r="AV1" s="29"/>
-      <c r="AW1" s="30"/>
+      <c r="AU1" s="25"/>
+      <c r="AV1" s="25"/>
+      <c r="AW1" s="26"/>
       <c r="AX1" s="22"/>
       <c r="AY1" s="22"/>
       <c r="AZ1" s="22"/>
@@ -1068,1783 +1068,1783 @@
       </c>
     </row>
     <row r="2" spans="1:166" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="37"/>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="40" t="s">
+      <c r="A2" s="41"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="26">
+      <c r="F2" s="29">
         <v>46307</v>
       </c>
-      <c r="G2" s="26">
+      <c r="G2" s="29">
         <v>46307</v>
       </c>
-      <c r="H2" s="26">
+      <c r="H2" s="29">
         <v>46307</v>
       </c>
-      <c r="I2" s="26">
+      <c r="I2" s="29">
         <v>46307</v>
       </c>
-      <c r="J2" s="26">
+      <c r="J2" s="29">
         <v>46307</v>
       </c>
-      <c r="K2" s="26">
+      <c r="K2" s="29">
         <v>46308</v>
       </c>
-      <c r="L2" s="26">
+      <c r="L2" s="29">
         <v>46308</v>
       </c>
-      <c r="M2" s="26">
+      <c r="M2" s="29">
         <v>46308</v>
       </c>
-      <c r="N2" s="26">
+      <c r="N2" s="29">
         <v>46308</v>
       </c>
-      <c r="O2" s="26">
+      <c r="O2" s="29">
         <v>46310</v>
       </c>
-      <c r="P2" s="26">
+      <c r="P2" s="29">
         <v>46310</v>
       </c>
-      <c r="Q2" s="26">
+      <c r="Q2" s="29">
         <v>46310</v>
       </c>
-      <c r="R2" s="26">
+      <c r="R2" s="29">
         <v>46310</v>
       </c>
-      <c r="S2" s="26">
+      <c r="S2" s="29">
         <v>46310</v>
       </c>
-      <c r="T2" s="26">
+      <c r="T2" s="29">
         <v>46310</v>
       </c>
-      <c r="U2" s="26">
+      <c r="U2" s="29">
         <v>46311</v>
       </c>
-      <c r="V2" s="26">
+      <c r="V2" s="29">
         <v>46311</v>
       </c>
-      <c r="W2" s="26">
+      <c r="W2" s="29">
         <v>46311</v>
       </c>
-      <c r="X2" s="26">
+      <c r="X2" s="29">
         <v>46311</v>
       </c>
-      <c r="Y2" s="26">
+      <c r="Y2" s="29">
         <v>46314</v>
       </c>
-      <c r="Z2" s="26">
+      <c r="Z2" s="29">
         <v>46314</v>
       </c>
-      <c r="AA2" s="26">
+      <c r="AA2" s="29">
         <v>46314</v>
       </c>
-      <c r="AB2" s="26">
+      <c r="AB2" s="29">
         <v>46314</v>
       </c>
-      <c r="AC2" s="26">
+      <c r="AC2" s="29">
         <v>46314</v>
       </c>
-      <c r="AD2" s="26">
+      <c r="AD2" s="29">
         <v>46315</v>
       </c>
-      <c r="AE2" s="26">
+      <c r="AE2" s="29">
         <v>46315</v>
       </c>
-      <c r="AF2" s="26">
+      <c r="AF2" s="29">
         <v>46315</v>
       </c>
-      <c r="AG2" s="26">
+      <c r="AG2" s="29">
         <v>46315</v>
       </c>
-      <c r="AH2" s="26">
+      <c r="AH2" s="29">
         <v>46316</v>
       </c>
-      <c r="AI2" s="26">
+      <c r="AI2" s="29">
         <v>46316</v>
       </c>
-      <c r="AJ2" s="26">
+      <c r="AJ2" s="29">
         <v>46316</v>
       </c>
-      <c r="AK2" s="26">
+      <c r="AK2" s="29">
         <v>46316</v>
       </c>
-      <c r="AL2" s="26">
+      <c r="AL2" s="29">
         <v>46316</v>
       </c>
-      <c r="AM2" s="26">
+      <c r="AM2" s="29">
         <v>46316</v>
       </c>
-      <c r="AN2" s="26">
+      <c r="AN2" s="29">
         <v>46317</v>
       </c>
-      <c r="AO2" s="26">
+      <c r="AO2" s="29">
         <v>46317</v>
       </c>
-      <c r="AP2" s="26">
+      <c r="AP2" s="29">
         <v>46317</v>
       </c>
-      <c r="AQ2" s="26">
+      <c r="AQ2" s="29">
         <v>46317</v>
       </c>
-      <c r="AR2" s="26">
+      <c r="AR2" s="29">
         <v>46317</v>
       </c>
-      <c r="AS2" s="26">
+      <c r="AS2" s="29">
         <v>46317</v>
       </c>
-      <c r="AT2" s="26">
+      <c r="AT2" s="29">
         <v>46318</v>
       </c>
-      <c r="AU2" s="26">
+      <c r="AU2" s="29">
         <v>46318</v>
       </c>
-      <c r="AV2" s="26">
+      <c r="AV2" s="29">
         <v>46318</v>
       </c>
-      <c r="AW2" s="26">
+      <c r="AW2" s="29">
         <v>46318</v>
       </c>
-      <c r="AX2" s="26"/>
-      <c r="AY2" s="26"/>
-      <c r="AZ2" s="26"/>
-      <c r="BA2" s="26"/>
-      <c r="BB2" s="26"/>
-      <c r="BC2" s="26"/>
-      <c r="BD2" s="26"/>
-      <c r="BE2" s="26"/>
-      <c r="BF2" s="26"/>
-      <c r="BG2" s="26"/>
-      <c r="BH2" s="26"/>
-      <c r="BI2" s="26"/>
-      <c r="BJ2" s="26"/>
-      <c r="BK2" s="26"/>
-      <c r="BL2" s="26"/>
-      <c r="BM2" s="26"/>
-      <c r="BN2" s="26"/>
-      <c r="BO2" s="26"/>
-      <c r="BP2" s="26"/>
-      <c r="BQ2" s="26"/>
-      <c r="BR2" s="26"/>
-      <c r="BS2" s="26"/>
-      <c r="BT2" s="26"/>
-      <c r="BU2" s="26"/>
-      <c r="BV2" s="26"/>
-      <c r="BW2" s="26"/>
-      <c r="BX2" s="26"/>
-      <c r="BY2" s="26"/>
-      <c r="BZ2" s="26"/>
-      <c r="CA2" s="26"/>
-      <c r="CB2" s="26"/>
-      <c r="CC2" s="26"/>
-      <c r="CD2" s="26"/>
-      <c r="CE2" s="26"/>
-      <c r="CF2" s="26"/>
-      <c r="CG2" s="26"/>
-      <c r="CH2" s="26"/>
-      <c r="CI2" s="26"/>
-      <c r="CJ2" s="26"/>
-      <c r="CK2" s="26"/>
-      <c r="CL2" s="26"/>
-      <c r="CM2" s="26"/>
-      <c r="CN2" s="26"/>
-      <c r="CO2" s="26"/>
-      <c r="CP2" s="26"/>
-      <c r="CQ2" s="26"/>
-      <c r="CR2" s="26"/>
-      <c r="CS2" s="26"/>
-      <c r="CT2" s="26"/>
-      <c r="CU2" s="26"/>
-      <c r="CV2" s="26"/>
-      <c r="CW2" s="26"/>
-      <c r="CX2" s="26"/>
-      <c r="CY2" s="26"/>
-      <c r="CZ2" s="26"/>
-      <c r="DA2" s="26"/>
-      <c r="DB2" s="26"/>
-      <c r="DC2" s="26"/>
-      <c r="DD2" s="26"/>
-      <c r="DE2" s="26"/>
-      <c r="DF2" s="26"/>
-      <c r="DG2" s="26"/>
-      <c r="DH2" s="26"/>
-      <c r="DI2" s="26"/>
-      <c r="DJ2" s="26"/>
-      <c r="DK2" s="26"/>
-      <c r="DL2" s="26"/>
-      <c r="DM2" s="26"/>
-      <c r="DN2" s="26"/>
-      <c r="DO2" s="26"/>
-      <c r="DP2" s="26"/>
-      <c r="DQ2" s="26"/>
-      <c r="DR2" s="26"/>
-      <c r="DS2" s="26"/>
-      <c r="DT2" s="26"/>
-      <c r="DU2" s="26"/>
-      <c r="DV2" s="26"/>
-      <c r="DW2" s="26"/>
-      <c r="DX2" s="26"/>
-      <c r="DY2" s="26"/>
-      <c r="DZ2" s="26"/>
-      <c r="EA2" s="26"/>
-      <c r="EB2" s="26"/>
-      <c r="EC2" s="26"/>
-      <c r="ED2" s="26"/>
-      <c r="EE2" s="26"/>
-      <c r="EF2" s="26"/>
-      <c r="EG2" s="26"/>
-      <c r="EH2" s="26"/>
-      <c r="EI2" s="26"/>
-      <c r="EJ2" s="26"/>
-      <c r="EK2" s="26"/>
-      <c r="EL2" s="26"/>
-      <c r="EM2" s="26"/>
-      <c r="EN2" s="26"/>
-      <c r="EO2" s="26"/>
-      <c r="EP2" s="26"/>
-      <c r="EQ2" s="26"/>
-      <c r="ER2" s="26"/>
-      <c r="ES2" s="26"/>
-      <c r="ET2" s="26"/>
-      <c r="EU2" s="26"/>
-      <c r="EV2" s="26"/>
-      <c r="EW2" s="26"/>
-      <c r="EX2" s="26"/>
-      <c r="EY2" s="26"/>
-      <c r="EZ2" s="26"/>
-      <c r="FA2" s="26"/>
-      <c r="FB2" s="26"/>
-      <c r="FC2" s="26"/>
-      <c r="FD2" s="26"/>
-      <c r="FE2" s="26"/>
-      <c r="FF2" s="26"/>
-      <c r="FG2" s="26"/>
-      <c r="FH2" s="26"/>
-      <c r="FI2" s="26"/>
+      <c r="AX2" s="29"/>
+      <c r="AY2" s="29"/>
+      <c r="AZ2" s="29"/>
+      <c r="BA2" s="29"/>
+      <c r="BB2" s="29"/>
+      <c r="BC2" s="29"/>
+      <c r="BD2" s="29"/>
+      <c r="BE2" s="29"/>
+      <c r="BF2" s="29"/>
+      <c r="BG2" s="29"/>
+      <c r="BH2" s="29"/>
+      <c r="BI2" s="29"/>
+      <c r="BJ2" s="29"/>
+      <c r="BK2" s="29"/>
+      <c r="BL2" s="29"/>
+      <c r="BM2" s="29"/>
+      <c r="BN2" s="29"/>
+      <c r="BO2" s="29"/>
+      <c r="BP2" s="29"/>
+      <c r="BQ2" s="29"/>
+      <c r="BR2" s="29"/>
+      <c r="BS2" s="29"/>
+      <c r="BT2" s="29"/>
+      <c r="BU2" s="29"/>
+      <c r="BV2" s="29"/>
+      <c r="BW2" s="29"/>
+      <c r="BX2" s="29"/>
+      <c r="BY2" s="29"/>
+      <c r="BZ2" s="29"/>
+      <c r="CA2" s="29"/>
+      <c r="CB2" s="29"/>
+      <c r="CC2" s="29"/>
+      <c r="CD2" s="29"/>
+      <c r="CE2" s="29"/>
+      <c r="CF2" s="29"/>
+      <c r="CG2" s="29"/>
+      <c r="CH2" s="29"/>
+      <c r="CI2" s="29"/>
+      <c r="CJ2" s="29"/>
+      <c r="CK2" s="29"/>
+      <c r="CL2" s="29"/>
+      <c r="CM2" s="29"/>
+      <c r="CN2" s="29"/>
+      <c r="CO2" s="29"/>
+      <c r="CP2" s="29"/>
+      <c r="CQ2" s="29"/>
+      <c r="CR2" s="29"/>
+      <c r="CS2" s="29"/>
+      <c r="CT2" s="29"/>
+      <c r="CU2" s="29"/>
+      <c r="CV2" s="29"/>
+      <c r="CW2" s="29"/>
+      <c r="CX2" s="29"/>
+      <c r="CY2" s="29"/>
+      <c r="CZ2" s="29"/>
+      <c r="DA2" s="29"/>
+      <c r="DB2" s="29"/>
+      <c r="DC2" s="29"/>
+      <c r="DD2" s="29"/>
+      <c r="DE2" s="29"/>
+      <c r="DF2" s="29"/>
+      <c r="DG2" s="29"/>
+      <c r="DH2" s="29"/>
+      <c r="DI2" s="29"/>
+      <c r="DJ2" s="29"/>
+      <c r="DK2" s="29"/>
+      <c r="DL2" s="29"/>
+      <c r="DM2" s="29"/>
+      <c r="DN2" s="29"/>
+      <c r="DO2" s="29"/>
+      <c r="DP2" s="29"/>
+      <c r="DQ2" s="29"/>
+      <c r="DR2" s="29"/>
+      <c r="DS2" s="29"/>
+      <c r="DT2" s="29"/>
+      <c r="DU2" s="29"/>
+      <c r="DV2" s="29"/>
+      <c r="DW2" s="29"/>
+      <c r="DX2" s="29"/>
+      <c r="DY2" s="29"/>
+      <c r="DZ2" s="29"/>
+      <c r="EA2" s="29"/>
+      <c r="EB2" s="29"/>
+      <c r="EC2" s="29"/>
+      <c r="ED2" s="29"/>
+      <c r="EE2" s="29"/>
+      <c r="EF2" s="29"/>
+      <c r="EG2" s="29"/>
+      <c r="EH2" s="29"/>
+      <c r="EI2" s="29"/>
+      <c r="EJ2" s="29"/>
+      <c r="EK2" s="29"/>
+      <c r="EL2" s="29"/>
+      <c r="EM2" s="29"/>
+      <c r="EN2" s="29"/>
+      <c r="EO2" s="29"/>
+      <c r="EP2" s="29"/>
+      <c r="EQ2" s="29"/>
+      <c r="ER2" s="29"/>
+      <c r="ES2" s="29"/>
+      <c r="ET2" s="29"/>
+      <c r="EU2" s="29"/>
+      <c r="EV2" s="29"/>
+      <c r="EW2" s="29"/>
+      <c r="EX2" s="29"/>
+      <c r="EY2" s="29"/>
+      <c r="EZ2" s="29"/>
+      <c r="FA2" s="29"/>
+      <c r="FB2" s="29"/>
+      <c r="FC2" s="29"/>
+      <c r="FD2" s="29"/>
+      <c r="FE2" s="29"/>
+      <c r="FF2" s="29"/>
+      <c r="FG2" s="29"/>
+      <c r="FH2" s="29"/>
+      <c r="FI2" s="29"/>
     </row>
     <row r="3" spans="1:166" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="26"/>
-      <c r="M3" s="26"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="26"/>
-      <c r="P3" s="26"/>
-      <c r="Q3" s="26"/>
-      <c r="R3" s="26"/>
-      <c r="S3" s="26"/>
-      <c r="T3" s="26"/>
-      <c r="U3" s="26"/>
-      <c r="V3" s="26"/>
-      <c r="W3" s="26"/>
-      <c r="X3" s="26"/>
-      <c r="Y3" s="26"/>
-      <c r="Z3" s="26"/>
-      <c r="AA3" s="26"/>
-      <c r="AB3" s="26"/>
-      <c r="AC3" s="26"/>
-      <c r="AD3" s="26"/>
-      <c r="AE3" s="26"/>
-      <c r="AF3" s="26"/>
-      <c r="AG3" s="26"/>
-      <c r="AH3" s="26"/>
-      <c r="AI3" s="26"/>
-      <c r="AJ3" s="26"/>
-      <c r="AK3" s="26"/>
-      <c r="AL3" s="26"/>
-      <c r="AM3" s="26"/>
-      <c r="AN3" s="26"/>
-      <c r="AO3" s="26"/>
-      <c r="AP3" s="26"/>
-      <c r="AQ3" s="26"/>
-      <c r="AR3" s="26"/>
-      <c r="AS3" s="26"/>
-      <c r="AT3" s="26"/>
-      <c r="AU3" s="26"/>
-      <c r="AV3" s="26"/>
-      <c r="AW3" s="26"/>
-      <c r="AX3" s="26"/>
-      <c r="AY3" s="26"/>
-      <c r="AZ3" s="26"/>
-      <c r="BA3" s="26"/>
-      <c r="BB3" s="26"/>
-      <c r="BC3" s="26"/>
-      <c r="BD3" s="26"/>
-      <c r="BE3" s="26"/>
-      <c r="BF3" s="26"/>
-      <c r="BG3" s="26"/>
-      <c r="BH3" s="26"/>
-      <c r="BI3" s="26"/>
-      <c r="BJ3" s="26"/>
-      <c r="BK3" s="26"/>
-      <c r="BL3" s="26"/>
-      <c r="BM3" s="26"/>
-      <c r="BN3" s="26"/>
-      <c r="BO3" s="26"/>
-      <c r="BP3" s="26"/>
-      <c r="BQ3" s="26"/>
-      <c r="BR3" s="26"/>
-      <c r="BS3" s="26"/>
-      <c r="BT3" s="26"/>
-      <c r="BU3" s="26"/>
-      <c r="BV3" s="26"/>
-      <c r="BW3" s="26"/>
-      <c r="BX3" s="26"/>
-      <c r="BY3" s="26"/>
-      <c r="BZ3" s="26"/>
-      <c r="CA3" s="26"/>
-      <c r="CB3" s="26"/>
-      <c r="CC3" s="26"/>
-      <c r="CD3" s="26"/>
-      <c r="CE3" s="26"/>
-      <c r="CF3" s="26"/>
-      <c r="CG3" s="26"/>
-      <c r="CH3" s="26"/>
-      <c r="CI3" s="26"/>
-      <c r="CJ3" s="26"/>
-      <c r="CK3" s="26"/>
-      <c r="CL3" s="26"/>
-      <c r="CM3" s="26"/>
-      <c r="CN3" s="26"/>
-      <c r="CO3" s="26"/>
-      <c r="CP3" s="26"/>
-      <c r="CQ3" s="26"/>
-      <c r="CR3" s="26"/>
-      <c r="CS3" s="26"/>
-      <c r="CT3" s="26"/>
-      <c r="CU3" s="26"/>
-      <c r="CV3" s="26"/>
-      <c r="CW3" s="26"/>
-      <c r="CX3" s="26"/>
-      <c r="CY3" s="26"/>
-      <c r="CZ3" s="26"/>
-      <c r="DA3" s="26"/>
-      <c r="DB3" s="26"/>
-      <c r="DC3" s="26"/>
-      <c r="DD3" s="26"/>
-      <c r="DE3" s="26"/>
-      <c r="DF3" s="26"/>
-      <c r="DG3" s="26"/>
-      <c r="DH3" s="26"/>
-      <c r="DI3" s="26"/>
-      <c r="DJ3" s="26"/>
-      <c r="DK3" s="26"/>
-      <c r="DL3" s="26"/>
-      <c r="DM3" s="26"/>
-      <c r="DN3" s="26"/>
-      <c r="DO3" s="26"/>
-      <c r="DP3" s="26"/>
-      <c r="DQ3" s="26"/>
-      <c r="DR3" s="26"/>
-      <c r="DS3" s="26"/>
-      <c r="DT3" s="26"/>
-      <c r="DU3" s="26"/>
-      <c r="DV3" s="26"/>
-      <c r="DW3" s="26"/>
-      <c r="DX3" s="26"/>
-      <c r="DY3" s="26"/>
-      <c r="DZ3" s="26"/>
-      <c r="EA3" s="26"/>
-      <c r="EB3" s="26"/>
-      <c r="EC3" s="26"/>
-      <c r="ED3" s="26"/>
-      <c r="EE3" s="26"/>
-      <c r="EF3" s="26"/>
-      <c r="EG3" s="26"/>
-      <c r="EH3" s="26"/>
-      <c r="EI3" s="26"/>
-      <c r="EJ3" s="26"/>
-      <c r="EK3" s="26"/>
-      <c r="EL3" s="26"/>
-      <c r="EM3" s="26"/>
-      <c r="EN3" s="26"/>
-      <c r="EO3" s="26"/>
-      <c r="EP3" s="26"/>
-      <c r="EQ3" s="26"/>
-      <c r="ER3" s="26"/>
-      <c r="ES3" s="26"/>
-      <c r="ET3" s="26"/>
-      <c r="EU3" s="26"/>
-      <c r="EV3" s="26"/>
-      <c r="EW3" s="26"/>
-      <c r="EX3" s="26"/>
-      <c r="EY3" s="26"/>
-      <c r="EZ3" s="26"/>
-      <c r="FA3" s="26"/>
-      <c r="FB3" s="26"/>
-      <c r="FC3" s="26"/>
-      <c r="FD3" s="26"/>
-      <c r="FE3" s="26"/>
-      <c r="FF3" s="26"/>
-      <c r="FG3" s="26"/>
-      <c r="FH3" s="26"/>
-      <c r="FI3" s="26"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="29"/>
+      <c r="L3" s="29"/>
+      <c r="M3" s="29"/>
+      <c r="N3" s="29"/>
+      <c r="O3" s="29"/>
+      <c r="P3" s="29"/>
+      <c r="Q3" s="29"/>
+      <c r="R3" s="29"/>
+      <c r="S3" s="29"/>
+      <c r="T3" s="29"/>
+      <c r="U3" s="29"/>
+      <c r="V3" s="29"/>
+      <c r="W3" s="29"/>
+      <c r="X3" s="29"/>
+      <c r="Y3" s="29"/>
+      <c r="Z3" s="29"/>
+      <c r="AA3" s="29"/>
+      <c r="AB3" s="29"/>
+      <c r="AC3" s="29"/>
+      <c r="AD3" s="29"/>
+      <c r="AE3" s="29"/>
+      <c r="AF3" s="29"/>
+      <c r="AG3" s="29"/>
+      <c r="AH3" s="29"/>
+      <c r="AI3" s="29"/>
+      <c r="AJ3" s="29"/>
+      <c r="AK3" s="29"/>
+      <c r="AL3" s="29"/>
+      <c r="AM3" s="29"/>
+      <c r="AN3" s="29"/>
+      <c r="AO3" s="29"/>
+      <c r="AP3" s="29"/>
+      <c r="AQ3" s="29"/>
+      <c r="AR3" s="29"/>
+      <c r="AS3" s="29"/>
+      <c r="AT3" s="29"/>
+      <c r="AU3" s="29"/>
+      <c r="AV3" s="29"/>
+      <c r="AW3" s="29"/>
+      <c r="AX3" s="29"/>
+      <c r="AY3" s="29"/>
+      <c r="AZ3" s="29"/>
+      <c r="BA3" s="29"/>
+      <c r="BB3" s="29"/>
+      <c r="BC3" s="29"/>
+      <c r="BD3" s="29"/>
+      <c r="BE3" s="29"/>
+      <c r="BF3" s="29"/>
+      <c r="BG3" s="29"/>
+      <c r="BH3" s="29"/>
+      <c r="BI3" s="29"/>
+      <c r="BJ3" s="29"/>
+      <c r="BK3" s="29"/>
+      <c r="BL3" s="29"/>
+      <c r="BM3" s="29"/>
+      <c r="BN3" s="29"/>
+      <c r="BO3" s="29"/>
+      <c r="BP3" s="29"/>
+      <c r="BQ3" s="29"/>
+      <c r="BR3" s="29"/>
+      <c r="BS3" s="29"/>
+      <c r="BT3" s="29"/>
+      <c r="BU3" s="29"/>
+      <c r="BV3" s="29"/>
+      <c r="BW3" s="29"/>
+      <c r="BX3" s="29"/>
+      <c r="BY3" s="29"/>
+      <c r="BZ3" s="29"/>
+      <c r="CA3" s="29"/>
+      <c r="CB3" s="29"/>
+      <c r="CC3" s="29"/>
+      <c r="CD3" s="29"/>
+      <c r="CE3" s="29"/>
+      <c r="CF3" s="29"/>
+      <c r="CG3" s="29"/>
+      <c r="CH3" s="29"/>
+      <c r="CI3" s="29"/>
+      <c r="CJ3" s="29"/>
+      <c r="CK3" s="29"/>
+      <c r="CL3" s="29"/>
+      <c r="CM3" s="29"/>
+      <c r="CN3" s="29"/>
+      <c r="CO3" s="29"/>
+      <c r="CP3" s="29"/>
+      <c r="CQ3" s="29"/>
+      <c r="CR3" s="29"/>
+      <c r="CS3" s="29"/>
+      <c r="CT3" s="29"/>
+      <c r="CU3" s="29"/>
+      <c r="CV3" s="29"/>
+      <c r="CW3" s="29"/>
+      <c r="CX3" s="29"/>
+      <c r="CY3" s="29"/>
+      <c r="CZ3" s="29"/>
+      <c r="DA3" s="29"/>
+      <c r="DB3" s="29"/>
+      <c r="DC3" s="29"/>
+      <c r="DD3" s="29"/>
+      <c r="DE3" s="29"/>
+      <c r="DF3" s="29"/>
+      <c r="DG3" s="29"/>
+      <c r="DH3" s="29"/>
+      <c r="DI3" s="29"/>
+      <c r="DJ3" s="29"/>
+      <c r="DK3" s="29"/>
+      <c r="DL3" s="29"/>
+      <c r="DM3" s="29"/>
+      <c r="DN3" s="29"/>
+      <c r="DO3" s="29"/>
+      <c r="DP3" s="29"/>
+      <c r="DQ3" s="29"/>
+      <c r="DR3" s="29"/>
+      <c r="DS3" s="29"/>
+      <c r="DT3" s="29"/>
+      <c r="DU3" s="29"/>
+      <c r="DV3" s="29"/>
+      <c r="DW3" s="29"/>
+      <c r="DX3" s="29"/>
+      <c r="DY3" s="29"/>
+      <c r="DZ3" s="29"/>
+      <c r="EA3" s="29"/>
+      <c r="EB3" s="29"/>
+      <c r="EC3" s="29"/>
+      <c r="ED3" s="29"/>
+      <c r="EE3" s="29"/>
+      <c r="EF3" s="29"/>
+      <c r="EG3" s="29"/>
+      <c r="EH3" s="29"/>
+      <c r="EI3" s="29"/>
+      <c r="EJ3" s="29"/>
+      <c r="EK3" s="29"/>
+      <c r="EL3" s="29"/>
+      <c r="EM3" s="29"/>
+      <c r="EN3" s="29"/>
+      <c r="EO3" s="29"/>
+      <c r="EP3" s="29"/>
+      <c r="EQ3" s="29"/>
+      <c r="ER3" s="29"/>
+      <c r="ES3" s="29"/>
+      <c r="ET3" s="29"/>
+      <c r="EU3" s="29"/>
+      <c r="EV3" s="29"/>
+      <c r="EW3" s="29"/>
+      <c r="EX3" s="29"/>
+      <c r="EY3" s="29"/>
+      <c r="EZ3" s="29"/>
+      <c r="FA3" s="29"/>
+      <c r="FB3" s="29"/>
+      <c r="FC3" s="29"/>
+      <c r="FD3" s="29"/>
+      <c r="FE3" s="29"/>
+      <c r="FF3" s="29"/>
+      <c r="FG3" s="29"/>
+      <c r="FH3" s="29"/>
+      <c r="FI3" s="29"/>
     </row>
     <row r="4" spans="1:166" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="44"/>
-      <c r="C4" s="45" t="s">
+      <c r="A4" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="47"/>
+      <c r="C4" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="46"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="26"/>
-      <c r="O4" s="26"/>
-      <c r="P4" s="26"/>
-      <c r="Q4" s="26"/>
-      <c r="R4" s="26"/>
-      <c r="S4" s="26"/>
-      <c r="T4" s="26"/>
-      <c r="U4" s="26"/>
-      <c r="V4" s="26"/>
-      <c r="W4" s="26"/>
-      <c r="X4" s="26"/>
-      <c r="Y4" s="26"/>
-      <c r="Z4" s="26"/>
-      <c r="AA4" s="26"/>
-      <c r="AB4" s="26"/>
-      <c r="AC4" s="26"/>
-      <c r="AD4" s="26"/>
-      <c r="AE4" s="26"/>
-      <c r="AF4" s="26"/>
-      <c r="AG4" s="26"/>
-      <c r="AH4" s="26"/>
-      <c r="AI4" s="26"/>
-      <c r="AJ4" s="26"/>
-      <c r="AK4" s="26"/>
-      <c r="AL4" s="26"/>
-      <c r="AM4" s="26"/>
-      <c r="AN4" s="26"/>
-      <c r="AO4" s="26"/>
-      <c r="AP4" s="26"/>
-      <c r="AQ4" s="26"/>
-      <c r="AR4" s="26"/>
-      <c r="AS4" s="26"/>
-      <c r="AT4" s="26"/>
-      <c r="AU4" s="26"/>
-      <c r="AV4" s="26"/>
-      <c r="AW4" s="26"/>
-      <c r="AX4" s="26"/>
-      <c r="AY4" s="26"/>
-      <c r="AZ4" s="26"/>
-      <c r="BA4" s="26"/>
-      <c r="BB4" s="26"/>
-      <c r="BC4" s="26"/>
-      <c r="BD4" s="26"/>
-      <c r="BE4" s="26"/>
-      <c r="BF4" s="26"/>
-      <c r="BG4" s="26"/>
-      <c r="BH4" s="26"/>
-      <c r="BI4" s="26"/>
-      <c r="BJ4" s="26"/>
-      <c r="BK4" s="26"/>
-      <c r="BL4" s="26"/>
-      <c r="BM4" s="26"/>
-      <c r="BN4" s="26"/>
-      <c r="BO4" s="26"/>
-      <c r="BP4" s="26"/>
-      <c r="BQ4" s="26"/>
-      <c r="BR4" s="26"/>
-      <c r="BS4" s="26"/>
-      <c r="BT4" s="26"/>
-      <c r="BU4" s="26"/>
-      <c r="BV4" s="26"/>
-      <c r="BW4" s="26"/>
-      <c r="BX4" s="26"/>
-      <c r="BY4" s="26"/>
-      <c r="BZ4" s="26"/>
-      <c r="CA4" s="26"/>
-      <c r="CB4" s="26"/>
-      <c r="CC4" s="26"/>
-      <c r="CD4" s="26"/>
-      <c r="CE4" s="26"/>
-      <c r="CF4" s="26"/>
-      <c r="CG4" s="26"/>
-      <c r="CH4" s="26"/>
-      <c r="CI4" s="26"/>
-      <c r="CJ4" s="26"/>
-      <c r="CK4" s="26"/>
-      <c r="CL4" s="26"/>
-      <c r="CM4" s="26"/>
-      <c r="CN4" s="26"/>
-      <c r="CO4" s="26"/>
-      <c r="CP4" s="26"/>
-      <c r="CQ4" s="26"/>
-      <c r="CR4" s="26"/>
-      <c r="CS4" s="26"/>
-      <c r="CT4" s="26"/>
-      <c r="CU4" s="26"/>
-      <c r="CV4" s="26"/>
-      <c r="CW4" s="26"/>
-      <c r="CX4" s="26"/>
-      <c r="CY4" s="26"/>
-      <c r="CZ4" s="26"/>
-      <c r="DA4" s="26"/>
-      <c r="DB4" s="26"/>
-      <c r="DC4" s="26"/>
-      <c r="DD4" s="26"/>
-      <c r="DE4" s="26"/>
-      <c r="DF4" s="26"/>
-      <c r="DG4" s="26"/>
-      <c r="DH4" s="26"/>
-      <c r="DI4" s="26"/>
-      <c r="DJ4" s="26"/>
-      <c r="DK4" s="26"/>
-      <c r="DL4" s="26"/>
-      <c r="DM4" s="26"/>
-      <c r="DN4" s="26"/>
-      <c r="DO4" s="26"/>
-      <c r="DP4" s="26"/>
-      <c r="DQ4" s="26"/>
-      <c r="DR4" s="26"/>
-      <c r="DS4" s="26"/>
-      <c r="DT4" s="26"/>
-      <c r="DU4" s="26"/>
-      <c r="DV4" s="26"/>
-      <c r="DW4" s="26"/>
-      <c r="DX4" s="26"/>
-      <c r="DY4" s="26"/>
-      <c r="DZ4" s="26"/>
-      <c r="EA4" s="26"/>
-      <c r="EB4" s="26"/>
-      <c r="EC4" s="26"/>
-      <c r="ED4" s="26"/>
-      <c r="EE4" s="26"/>
-      <c r="EF4" s="26"/>
-      <c r="EG4" s="26"/>
-      <c r="EH4" s="26"/>
-      <c r="EI4" s="26"/>
-      <c r="EJ4" s="26"/>
-      <c r="EK4" s="26"/>
-      <c r="EL4" s="26"/>
-      <c r="EM4" s="26"/>
-      <c r="EN4" s="26"/>
-      <c r="EO4" s="26"/>
-      <c r="EP4" s="26"/>
-      <c r="EQ4" s="26"/>
-      <c r="ER4" s="26"/>
-      <c r="ES4" s="26"/>
-      <c r="ET4" s="26"/>
-      <c r="EU4" s="26"/>
-      <c r="EV4" s="26"/>
-      <c r="EW4" s="26"/>
-      <c r="EX4" s="26"/>
-      <c r="EY4" s="26"/>
-      <c r="EZ4" s="26"/>
-      <c r="FA4" s="26"/>
-      <c r="FB4" s="26"/>
-      <c r="FC4" s="26"/>
-      <c r="FD4" s="26"/>
-      <c r="FE4" s="26"/>
-      <c r="FF4" s="26"/>
-      <c r="FG4" s="26"/>
-      <c r="FH4" s="26"/>
-      <c r="FI4" s="26"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="29"/>
+      <c r="L4" s="29"/>
+      <c r="M4" s="29"/>
+      <c r="N4" s="29"/>
+      <c r="O4" s="29"/>
+      <c r="P4" s="29"/>
+      <c r="Q4" s="29"/>
+      <c r="R4" s="29"/>
+      <c r="S4" s="29"/>
+      <c r="T4" s="29"/>
+      <c r="U4" s="29"/>
+      <c r="V4" s="29"/>
+      <c r="W4" s="29"/>
+      <c r="X4" s="29"/>
+      <c r="Y4" s="29"/>
+      <c r="Z4" s="29"/>
+      <c r="AA4" s="29"/>
+      <c r="AB4" s="29"/>
+      <c r="AC4" s="29"/>
+      <c r="AD4" s="29"/>
+      <c r="AE4" s="29"/>
+      <c r="AF4" s="29"/>
+      <c r="AG4" s="29"/>
+      <c r="AH4" s="29"/>
+      <c r="AI4" s="29"/>
+      <c r="AJ4" s="29"/>
+      <c r="AK4" s="29"/>
+      <c r="AL4" s="29"/>
+      <c r="AM4" s="29"/>
+      <c r="AN4" s="29"/>
+      <c r="AO4" s="29"/>
+      <c r="AP4" s="29"/>
+      <c r="AQ4" s="29"/>
+      <c r="AR4" s="29"/>
+      <c r="AS4" s="29"/>
+      <c r="AT4" s="29"/>
+      <c r="AU4" s="29"/>
+      <c r="AV4" s="29"/>
+      <c r="AW4" s="29"/>
+      <c r="AX4" s="29"/>
+      <c r="AY4" s="29"/>
+      <c r="AZ4" s="29"/>
+      <c r="BA4" s="29"/>
+      <c r="BB4" s="29"/>
+      <c r="BC4" s="29"/>
+      <c r="BD4" s="29"/>
+      <c r="BE4" s="29"/>
+      <c r="BF4" s="29"/>
+      <c r="BG4" s="29"/>
+      <c r="BH4" s="29"/>
+      <c r="BI4" s="29"/>
+      <c r="BJ4" s="29"/>
+      <c r="BK4" s="29"/>
+      <c r="BL4" s="29"/>
+      <c r="BM4" s="29"/>
+      <c r="BN4" s="29"/>
+      <c r="BO4" s="29"/>
+      <c r="BP4" s="29"/>
+      <c r="BQ4" s="29"/>
+      <c r="BR4" s="29"/>
+      <c r="BS4" s="29"/>
+      <c r="BT4" s="29"/>
+      <c r="BU4" s="29"/>
+      <c r="BV4" s="29"/>
+      <c r="BW4" s="29"/>
+      <c r="BX4" s="29"/>
+      <c r="BY4" s="29"/>
+      <c r="BZ4" s="29"/>
+      <c r="CA4" s="29"/>
+      <c r="CB4" s="29"/>
+      <c r="CC4" s="29"/>
+      <c r="CD4" s="29"/>
+      <c r="CE4" s="29"/>
+      <c r="CF4" s="29"/>
+      <c r="CG4" s="29"/>
+      <c r="CH4" s="29"/>
+      <c r="CI4" s="29"/>
+      <c r="CJ4" s="29"/>
+      <c r="CK4" s="29"/>
+      <c r="CL4" s="29"/>
+      <c r="CM4" s="29"/>
+      <c r="CN4" s="29"/>
+      <c r="CO4" s="29"/>
+      <c r="CP4" s="29"/>
+      <c r="CQ4" s="29"/>
+      <c r="CR4" s="29"/>
+      <c r="CS4" s="29"/>
+      <c r="CT4" s="29"/>
+      <c r="CU4" s="29"/>
+      <c r="CV4" s="29"/>
+      <c r="CW4" s="29"/>
+      <c r="CX4" s="29"/>
+      <c r="CY4" s="29"/>
+      <c r="CZ4" s="29"/>
+      <c r="DA4" s="29"/>
+      <c r="DB4" s="29"/>
+      <c r="DC4" s="29"/>
+      <c r="DD4" s="29"/>
+      <c r="DE4" s="29"/>
+      <c r="DF4" s="29"/>
+      <c r="DG4" s="29"/>
+      <c r="DH4" s="29"/>
+      <c r="DI4" s="29"/>
+      <c r="DJ4" s="29"/>
+      <c r="DK4" s="29"/>
+      <c r="DL4" s="29"/>
+      <c r="DM4" s="29"/>
+      <c r="DN4" s="29"/>
+      <c r="DO4" s="29"/>
+      <c r="DP4" s="29"/>
+      <c r="DQ4" s="29"/>
+      <c r="DR4" s="29"/>
+      <c r="DS4" s="29"/>
+      <c r="DT4" s="29"/>
+      <c r="DU4" s="29"/>
+      <c r="DV4" s="29"/>
+      <c r="DW4" s="29"/>
+      <c r="DX4" s="29"/>
+      <c r="DY4" s="29"/>
+      <c r="DZ4" s="29"/>
+      <c r="EA4" s="29"/>
+      <c r="EB4" s="29"/>
+      <c r="EC4" s="29"/>
+      <c r="ED4" s="29"/>
+      <c r="EE4" s="29"/>
+      <c r="EF4" s="29"/>
+      <c r="EG4" s="29"/>
+      <c r="EH4" s="29"/>
+      <c r="EI4" s="29"/>
+      <c r="EJ4" s="29"/>
+      <c r="EK4" s="29"/>
+      <c r="EL4" s="29"/>
+      <c r="EM4" s="29"/>
+      <c r="EN4" s="29"/>
+      <c r="EO4" s="29"/>
+      <c r="EP4" s="29"/>
+      <c r="EQ4" s="29"/>
+      <c r="ER4" s="29"/>
+      <c r="ES4" s="29"/>
+      <c r="ET4" s="29"/>
+      <c r="EU4" s="29"/>
+      <c r="EV4" s="29"/>
+      <c r="EW4" s="29"/>
+      <c r="EX4" s="29"/>
+      <c r="EY4" s="29"/>
+      <c r="EZ4" s="29"/>
+      <c r="FA4" s="29"/>
+      <c r="FB4" s="29"/>
+      <c r="FC4" s="29"/>
+      <c r="FD4" s="29"/>
+      <c r="FE4" s="29"/>
+      <c r="FF4" s="29"/>
+      <c r="FG4" s="29"/>
+      <c r="FH4" s="29"/>
+      <c r="FI4" s="29"/>
     </row>
     <row r="5" spans="1:166" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="47" t="s">
+      <c r="A5" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="48">
+      <c r="B5" s="48"/>
+      <c r="C5" s="49">
         <v>140</v>
       </c>
-      <c r="D5" s="49"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
-      <c r="K5" s="26"/>
-      <c r="L5" s="26"/>
-      <c r="M5" s="26"/>
-      <c r="N5" s="26"/>
-      <c r="O5" s="26"/>
-      <c r="P5" s="26"/>
-      <c r="Q5" s="26"/>
-      <c r="R5" s="26"/>
-      <c r="S5" s="26"/>
-      <c r="T5" s="26"/>
-      <c r="U5" s="26"/>
-      <c r="V5" s="26"/>
-      <c r="W5" s="26"/>
-      <c r="X5" s="26"/>
-      <c r="Y5" s="26"/>
-      <c r="Z5" s="26"/>
-      <c r="AA5" s="26"/>
-      <c r="AB5" s="26"/>
-      <c r="AC5" s="26"/>
-      <c r="AD5" s="26"/>
-      <c r="AE5" s="26"/>
-      <c r="AF5" s="26"/>
-      <c r="AG5" s="26"/>
-      <c r="AH5" s="26"/>
-      <c r="AI5" s="26"/>
-      <c r="AJ5" s="26"/>
-      <c r="AK5" s="26"/>
-      <c r="AL5" s="26"/>
-      <c r="AM5" s="26"/>
-      <c r="AN5" s="26"/>
-      <c r="AO5" s="26"/>
-      <c r="AP5" s="26"/>
-      <c r="AQ5" s="26"/>
-      <c r="AR5" s="26"/>
-      <c r="AS5" s="26"/>
-      <c r="AT5" s="26"/>
-      <c r="AU5" s="26"/>
-      <c r="AV5" s="26"/>
-      <c r="AW5" s="26"/>
-      <c r="AX5" s="26"/>
-      <c r="AY5" s="26"/>
-      <c r="AZ5" s="26"/>
-      <c r="BA5" s="26"/>
-      <c r="BB5" s="26"/>
-      <c r="BC5" s="26"/>
-      <c r="BD5" s="26"/>
-      <c r="BE5" s="26"/>
-      <c r="BF5" s="26"/>
-      <c r="BG5" s="26"/>
-      <c r="BH5" s="26"/>
-      <c r="BI5" s="26"/>
-      <c r="BJ5" s="26"/>
-      <c r="BK5" s="26"/>
-      <c r="BL5" s="26"/>
-      <c r="BM5" s="26"/>
-      <c r="BN5" s="26"/>
-      <c r="BO5" s="26"/>
-      <c r="BP5" s="26"/>
-      <c r="BQ5" s="26"/>
-      <c r="BR5" s="26"/>
-      <c r="BS5" s="26"/>
-      <c r="BT5" s="26"/>
-      <c r="BU5" s="26"/>
-      <c r="BV5" s="26"/>
-      <c r="BW5" s="26"/>
-      <c r="BX5" s="26"/>
-      <c r="BY5" s="26"/>
-      <c r="BZ5" s="26"/>
-      <c r="CA5" s="26"/>
-      <c r="CB5" s="26"/>
-      <c r="CC5" s="26"/>
-      <c r="CD5" s="26"/>
-      <c r="CE5" s="26"/>
-      <c r="CF5" s="26"/>
-      <c r="CG5" s="26"/>
-      <c r="CH5" s="26"/>
-      <c r="CI5" s="26"/>
-      <c r="CJ5" s="26"/>
-      <c r="CK5" s="26"/>
-      <c r="CL5" s="26"/>
-      <c r="CM5" s="26"/>
-      <c r="CN5" s="26"/>
-      <c r="CO5" s="26"/>
-      <c r="CP5" s="26"/>
-      <c r="CQ5" s="26"/>
-      <c r="CR5" s="26"/>
-      <c r="CS5" s="26"/>
-      <c r="CT5" s="26"/>
-      <c r="CU5" s="26"/>
-      <c r="CV5" s="26"/>
-      <c r="CW5" s="26"/>
-      <c r="CX5" s="26"/>
-      <c r="CY5" s="26"/>
-      <c r="CZ5" s="26"/>
-      <c r="DA5" s="26"/>
-      <c r="DB5" s="26"/>
-      <c r="DC5" s="26"/>
-      <c r="DD5" s="26"/>
-      <c r="DE5" s="26"/>
-      <c r="DF5" s="26"/>
-      <c r="DG5" s="26"/>
-      <c r="DH5" s="26"/>
-      <c r="DI5" s="26"/>
-      <c r="DJ5" s="26"/>
-      <c r="DK5" s="26"/>
-      <c r="DL5" s="26"/>
-      <c r="DM5" s="26"/>
-      <c r="DN5" s="26"/>
-      <c r="DO5" s="26"/>
-      <c r="DP5" s="26"/>
-      <c r="DQ5" s="26"/>
-      <c r="DR5" s="26"/>
-      <c r="DS5" s="26"/>
-      <c r="DT5" s="26"/>
-      <c r="DU5" s="26"/>
-      <c r="DV5" s="26"/>
-      <c r="DW5" s="26"/>
-      <c r="DX5" s="26"/>
-      <c r="DY5" s="26"/>
-      <c r="DZ5" s="26"/>
-      <c r="EA5" s="26"/>
-      <c r="EB5" s="26"/>
-      <c r="EC5" s="26"/>
-      <c r="ED5" s="26"/>
-      <c r="EE5" s="26"/>
-      <c r="EF5" s="26"/>
-      <c r="EG5" s="26"/>
-      <c r="EH5" s="26"/>
-      <c r="EI5" s="26"/>
-      <c r="EJ5" s="26"/>
-      <c r="EK5" s="26"/>
-      <c r="EL5" s="26"/>
-      <c r="EM5" s="26"/>
-      <c r="EN5" s="26"/>
-      <c r="EO5" s="26"/>
-      <c r="EP5" s="26"/>
-      <c r="EQ5" s="26"/>
-      <c r="ER5" s="26"/>
-      <c r="ES5" s="26"/>
-      <c r="ET5" s="26"/>
-      <c r="EU5" s="26"/>
-      <c r="EV5" s="26"/>
-      <c r="EW5" s="26"/>
-      <c r="EX5" s="26"/>
-      <c r="EY5" s="26"/>
-      <c r="EZ5" s="26"/>
-      <c r="FA5" s="26"/>
-      <c r="FB5" s="26"/>
-      <c r="FC5" s="26"/>
-      <c r="FD5" s="26"/>
-      <c r="FE5" s="26"/>
-      <c r="FF5" s="26"/>
-      <c r="FG5" s="26"/>
-      <c r="FH5" s="26"/>
-      <c r="FI5" s="26"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="29"/>
+      <c r="N5" s="29"/>
+      <c r="O5" s="29"/>
+      <c r="P5" s="29"/>
+      <c r="Q5" s="29"/>
+      <c r="R5" s="29"/>
+      <c r="S5" s="29"/>
+      <c r="T5" s="29"/>
+      <c r="U5" s="29"/>
+      <c r="V5" s="29"/>
+      <c r="W5" s="29"/>
+      <c r="X5" s="29"/>
+      <c r="Y5" s="29"/>
+      <c r="Z5" s="29"/>
+      <c r="AA5" s="29"/>
+      <c r="AB5" s="29"/>
+      <c r="AC5" s="29"/>
+      <c r="AD5" s="29"/>
+      <c r="AE5" s="29"/>
+      <c r="AF5" s="29"/>
+      <c r="AG5" s="29"/>
+      <c r="AH5" s="29"/>
+      <c r="AI5" s="29"/>
+      <c r="AJ5" s="29"/>
+      <c r="AK5" s="29"/>
+      <c r="AL5" s="29"/>
+      <c r="AM5" s="29"/>
+      <c r="AN5" s="29"/>
+      <c r="AO5" s="29"/>
+      <c r="AP5" s="29"/>
+      <c r="AQ5" s="29"/>
+      <c r="AR5" s="29"/>
+      <c r="AS5" s="29"/>
+      <c r="AT5" s="29"/>
+      <c r="AU5" s="29"/>
+      <c r="AV5" s="29"/>
+      <c r="AW5" s="29"/>
+      <c r="AX5" s="29"/>
+      <c r="AY5" s="29"/>
+      <c r="AZ5" s="29"/>
+      <c r="BA5" s="29"/>
+      <c r="BB5" s="29"/>
+      <c r="BC5" s="29"/>
+      <c r="BD5" s="29"/>
+      <c r="BE5" s="29"/>
+      <c r="BF5" s="29"/>
+      <c r="BG5" s="29"/>
+      <c r="BH5" s="29"/>
+      <c r="BI5" s="29"/>
+      <c r="BJ5" s="29"/>
+      <c r="BK5" s="29"/>
+      <c r="BL5" s="29"/>
+      <c r="BM5" s="29"/>
+      <c r="BN5" s="29"/>
+      <c r="BO5" s="29"/>
+      <c r="BP5" s="29"/>
+      <c r="BQ5" s="29"/>
+      <c r="BR5" s="29"/>
+      <c r="BS5" s="29"/>
+      <c r="BT5" s="29"/>
+      <c r="BU5" s="29"/>
+      <c r="BV5" s="29"/>
+      <c r="BW5" s="29"/>
+      <c r="BX5" s="29"/>
+      <c r="BY5" s="29"/>
+      <c r="BZ5" s="29"/>
+      <c r="CA5" s="29"/>
+      <c r="CB5" s="29"/>
+      <c r="CC5" s="29"/>
+      <c r="CD5" s="29"/>
+      <c r="CE5" s="29"/>
+      <c r="CF5" s="29"/>
+      <c r="CG5" s="29"/>
+      <c r="CH5" s="29"/>
+      <c r="CI5" s="29"/>
+      <c r="CJ5" s="29"/>
+      <c r="CK5" s="29"/>
+      <c r="CL5" s="29"/>
+      <c r="CM5" s="29"/>
+      <c r="CN5" s="29"/>
+      <c r="CO5" s="29"/>
+      <c r="CP5" s="29"/>
+      <c r="CQ5" s="29"/>
+      <c r="CR5" s="29"/>
+      <c r="CS5" s="29"/>
+      <c r="CT5" s="29"/>
+      <c r="CU5" s="29"/>
+      <c r="CV5" s="29"/>
+      <c r="CW5" s="29"/>
+      <c r="CX5" s="29"/>
+      <c r="CY5" s="29"/>
+      <c r="CZ5" s="29"/>
+      <c r="DA5" s="29"/>
+      <c r="DB5" s="29"/>
+      <c r="DC5" s="29"/>
+      <c r="DD5" s="29"/>
+      <c r="DE5" s="29"/>
+      <c r="DF5" s="29"/>
+      <c r="DG5" s="29"/>
+      <c r="DH5" s="29"/>
+      <c r="DI5" s="29"/>
+      <c r="DJ5" s="29"/>
+      <c r="DK5" s="29"/>
+      <c r="DL5" s="29"/>
+      <c r="DM5" s="29"/>
+      <c r="DN5" s="29"/>
+      <c r="DO5" s="29"/>
+      <c r="DP5" s="29"/>
+      <c r="DQ5" s="29"/>
+      <c r="DR5" s="29"/>
+      <c r="DS5" s="29"/>
+      <c r="DT5" s="29"/>
+      <c r="DU5" s="29"/>
+      <c r="DV5" s="29"/>
+      <c r="DW5" s="29"/>
+      <c r="DX5" s="29"/>
+      <c r="DY5" s="29"/>
+      <c r="DZ5" s="29"/>
+      <c r="EA5" s="29"/>
+      <c r="EB5" s="29"/>
+      <c r="EC5" s="29"/>
+      <c r="ED5" s="29"/>
+      <c r="EE5" s="29"/>
+      <c r="EF5" s="29"/>
+      <c r="EG5" s="29"/>
+      <c r="EH5" s="29"/>
+      <c r="EI5" s="29"/>
+      <c r="EJ5" s="29"/>
+      <c r="EK5" s="29"/>
+      <c r="EL5" s="29"/>
+      <c r="EM5" s="29"/>
+      <c r="EN5" s="29"/>
+      <c r="EO5" s="29"/>
+      <c r="EP5" s="29"/>
+      <c r="EQ5" s="29"/>
+      <c r="ER5" s="29"/>
+      <c r="ES5" s="29"/>
+      <c r="ET5" s="29"/>
+      <c r="EU5" s="29"/>
+      <c r="EV5" s="29"/>
+      <c r="EW5" s="29"/>
+      <c r="EX5" s="29"/>
+      <c r="EY5" s="29"/>
+      <c r="EZ5" s="29"/>
+      <c r="FA5" s="29"/>
+      <c r="FB5" s="29"/>
+      <c r="FC5" s="29"/>
+      <c r="FD5" s="29"/>
+      <c r="FE5" s="29"/>
+      <c r="FF5" s="29"/>
+      <c r="FG5" s="29"/>
+      <c r="FH5" s="29"/>
+      <c r="FI5" s="29"/>
     </row>
     <row r="6" spans="1:166" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="47" t="s">
+      <c r="A6" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="48">
+      <c r="B6" s="48"/>
+      <c r="C6" s="49">
         <v>25</v>
       </c>
-      <c r="D6" s="49"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
-      <c r="K6" s="26"/>
-      <c r="L6" s="26"/>
-      <c r="M6" s="26"/>
-      <c r="N6" s="26"/>
-      <c r="O6" s="26"/>
-      <c r="P6" s="26"/>
-      <c r="Q6" s="26"/>
-      <c r="R6" s="26"/>
-      <c r="S6" s="26"/>
-      <c r="T6" s="26"/>
-      <c r="U6" s="26"/>
-      <c r="V6" s="26"/>
-      <c r="W6" s="26"/>
-      <c r="X6" s="26"/>
-      <c r="Y6" s="26"/>
-      <c r="Z6" s="26"/>
-      <c r="AA6" s="26"/>
-      <c r="AB6" s="26"/>
-      <c r="AC6" s="26"/>
-      <c r="AD6" s="26"/>
-      <c r="AE6" s="26"/>
-      <c r="AF6" s="26"/>
-      <c r="AG6" s="26"/>
-      <c r="AH6" s="26"/>
-      <c r="AI6" s="26"/>
-      <c r="AJ6" s="26"/>
-      <c r="AK6" s="26"/>
-      <c r="AL6" s="26"/>
-      <c r="AM6" s="26"/>
-      <c r="AN6" s="26"/>
-      <c r="AO6" s="26"/>
-      <c r="AP6" s="26"/>
-      <c r="AQ6" s="26"/>
-      <c r="AR6" s="26"/>
-      <c r="AS6" s="26"/>
-      <c r="AT6" s="26"/>
-      <c r="AU6" s="26"/>
-      <c r="AV6" s="26"/>
-      <c r="AW6" s="26"/>
-      <c r="AX6" s="26"/>
-      <c r="AY6" s="26"/>
-      <c r="AZ6" s="26"/>
-      <c r="BA6" s="26"/>
-      <c r="BB6" s="26"/>
-      <c r="BC6" s="26"/>
-      <c r="BD6" s="26"/>
-      <c r="BE6" s="26"/>
-      <c r="BF6" s="26"/>
-      <c r="BG6" s="26"/>
-      <c r="BH6" s="26"/>
-      <c r="BI6" s="26"/>
-      <c r="BJ6" s="26"/>
-      <c r="BK6" s="26"/>
-      <c r="BL6" s="26"/>
-      <c r="BM6" s="26"/>
-      <c r="BN6" s="26"/>
-      <c r="BO6" s="26"/>
-      <c r="BP6" s="26"/>
-      <c r="BQ6" s="26"/>
-      <c r="BR6" s="26"/>
-      <c r="BS6" s="26"/>
-      <c r="BT6" s="26"/>
-      <c r="BU6" s="26"/>
-      <c r="BV6" s="26"/>
-      <c r="BW6" s="26"/>
-      <c r="BX6" s="26"/>
-      <c r="BY6" s="26"/>
-      <c r="BZ6" s="26"/>
-      <c r="CA6" s="26"/>
-      <c r="CB6" s="26"/>
-      <c r="CC6" s="26"/>
-      <c r="CD6" s="26"/>
-      <c r="CE6" s="26"/>
-      <c r="CF6" s="26"/>
-      <c r="CG6" s="26"/>
-      <c r="CH6" s="26"/>
-      <c r="CI6" s="26"/>
-      <c r="CJ6" s="26"/>
-      <c r="CK6" s="26"/>
-      <c r="CL6" s="26"/>
-      <c r="CM6" s="26"/>
-      <c r="CN6" s="26"/>
-      <c r="CO6" s="26"/>
-      <c r="CP6" s="26"/>
-      <c r="CQ6" s="26"/>
-      <c r="CR6" s="26"/>
-      <c r="CS6" s="26"/>
-      <c r="CT6" s="26"/>
-      <c r="CU6" s="26"/>
-      <c r="CV6" s="26"/>
-      <c r="CW6" s="26"/>
-      <c r="CX6" s="26"/>
-      <c r="CY6" s="26"/>
-      <c r="CZ6" s="26"/>
-      <c r="DA6" s="26"/>
-      <c r="DB6" s="26"/>
-      <c r="DC6" s="26"/>
-      <c r="DD6" s="26"/>
-      <c r="DE6" s="26"/>
-      <c r="DF6" s="26"/>
-      <c r="DG6" s="26"/>
-      <c r="DH6" s="26"/>
-      <c r="DI6" s="26"/>
-      <c r="DJ6" s="26"/>
-      <c r="DK6" s="26"/>
-      <c r="DL6" s="26"/>
-      <c r="DM6" s="26"/>
-      <c r="DN6" s="26"/>
-      <c r="DO6" s="26"/>
-      <c r="DP6" s="26"/>
-      <c r="DQ6" s="26"/>
-      <c r="DR6" s="26"/>
-      <c r="DS6" s="26"/>
-      <c r="DT6" s="26"/>
-      <c r="DU6" s="26"/>
-      <c r="DV6" s="26"/>
-      <c r="DW6" s="26"/>
-      <c r="DX6" s="26"/>
-      <c r="DY6" s="26"/>
-      <c r="DZ6" s="26"/>
-      <c r="EA6" s="26"/>
-      <c r="EB6" s="26"/>
-      <c r="EC6" s="26"/>
-      <c r="ED6" s="26"/>
-      <c r="EE6" s="26"/>
-      <c r="EF6" s="26"/>
-      <c r="EG6" s="26"/>
-      <c r="EH6" s="26"/>
-      <c r="EI6" s="26"/>
-      <c r="EJ6" s="26"/>
-      <c r="EK6" s="26"/>
-      <c r="EL6" s="26"/>
-      <c r="EM6" s="26"/>
-      <c r="EN6" s="26"/>
-      <c r="EO6" s="26"/>
-      <c r="EP6" s="26"/>
-      <c r="EQ6" s="26"/>
-      <c r="ER6" s="26"/>
-      <c r="ES6" s="26"/>
-      <c r="ET6" s="26"/>
-      <c r="EU6" s="26"/>
-      <c r="EV6" s="26"/>
-      <c r="EW6" s="26"/>
-      <c r="EX6" s="26"/>
-      <c r="EY6" s="26"/>
-      <c r="EZ6" s="26"/>
-      <c r="FA6" s="26"/>
-      <c r="FB6" s="26"/>
-      <c r="FC6" s="26"/>
-      <c r="FD6" s="26"/>
-      <c r="FE6" s="26"/>
-      <c r="FF6" s="26"/>
-      <c r="FG6" s="26"/>
-      <c r="FH6" s="26"/>
-      <c r="FI6" s="26"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="29"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="29"/>
+      <c r="N6" s="29"/>
+      <c r="O6" s="29"/>
+      <c r="P6" s="29"/>
+      <c r="Q6" s="29"/>
+      <c r="R6" s="29"/>
+      <c r="S6" s="29"/>
+      <c r="T6" s="29"/>
+      <c r="U6" s="29"/>
+      <c r="V6" s="29"/>
+      <c r="W6" s="29"/>
+      <c r="X6" s="29"/>
+      <c r="Y6" s="29"/>
+      <c r="Z6" s="29"/>
+      <c r="AA6" s="29"/>
+      <c r="AB6" s="29"/>
+      <c r="AC6" s="29"/>
+      <c r="AD6" s="29"/>
+      <c r="AE6" s="29"/>
+      <c r="AF6" s="29"/>
+      <c r="AG6" s="29"/>
+      <c r="AH6" s="29"/>
+      <c r="AI6" s="29"/>
+      <c r="AJ6" s="29"/>
+      <c r="AK6" s="29"/>
+      <c r="AL6" s="29"/>
+      <c r="AM6" s="29"/>
+      <c r="AN6" s="29"/>
+      <c r="AO6" s="29"/>
+      <c r="AP6" s="29"/>
+      <c r="AQ6" s="29"/>
+      <c r="AR6" s="29"/>
+      <c r="AS6" s="29"/>
+      <c r="AT6" s="29"/>
+      <c r="AU6" s="29"/>
+      <c r="AV6" s="29"/>
+      <c r="AW6" s="29"/>
+      <c r="AX6" s="29"/>
+      <c r="AY6" s="29"/>
+      <c r="AZ6" s="29"/>
+      <c r="BA6" s="29"/>
+      <c r="BB6" s="29"/>
+      <c r="BC6" s="29"/>
+      <c r="BD6" s="29"/>
+      <c r="BE6" s="29"/>
+      <c r="BF6" s="29"/>
+      <c r="BG6" s="29"/>
+      <c r="BH6" s="29"/>
+      <c r="BI6" s="29"/>
+      <c r="BJ6" s="29"/>
+      <c r="BK6" s="29"/>
+      <c r="BL6" s="29"/>
+      <c r="BM6" s="29"/>
+      <c r="BN6" s="29"/>
+      <c r="BO6" s="29"/>
+      <c r="BP6" s="29"/>
+      <c r="BQ6" s="29"/>
+      <c r="BR6" s="29"/>
+      <c r="BS6" s="29"/>
+      <c r="BT6" s="29"/>
+      <c r="BU6" s="29"/>
+      <c r="BV6" s="29"/>
+      <c r="BW6" s="29"/>
+      <c r="BX6" s="29"/>
+      <c r="BY6" s="29"/>
+      <c r="BZ6" s="29"/>
+      <c r="CA6" s="29"/>
+      <c r="CB6" s="29"/>
+      <c r="CC6" s="29"/>
+      <c r="CD6" s="29"/>
+      <c r="CE6" s="29"/>
+      <c r="CF6" s="29"/>
+      <c r="CG6" s="29"/>
+      <c r="CH6" s="29"/>
+      <c r="CI6" s="29"/>
+      <c r="CJ6" s="29"/>
+      <c r="CK6" s="29"/>
+      <c r="CL6" s="29"/>
+      <c r="CM6" s="29"/>
+      <c r="CN6" s="29"/>
+      <c r="CO6" s="29"/>
+      <c r="CP6" s="29"/>
+      <c r="CQ6" s="29"/>
+      <c r="CR6" s="29"/>
+      <c r="CS6" s="29"/>
+      <c r="CT6" s="29"/>
+      <c r="CU6" s="29"/>
+      <c r="CV6" s="29"/>
+      <c r="CW6" s="29"/>
+      <c r="CX6" s="29"/>
+      <c r="CY6" s="29"/>
+      <c r="CZ6" s="29"/>
+      <c r="DA6" s="29"/>
+      <c r="DB6" s="29"/>
+      <c r="DC6" s="29"/>
+      <c r="DD6" s="29"/>
+      <c r="DE6" s="29"/>
+      <c r="DF6" s="29"/>
+      <c r="DG6" s="29"/>
+      <c r="DH6" s="29"/>
+      <c r="DI6" s="29"/>
+      <c r="DJ6" s="29"/>
+      <c r="DK6" s="29"/>
+      <c r="DL6" s="29"/>
+      <c r="DM6" s="29"/>
+      <c r="DN6" s="29"/>
+      <c r="DO6" s="29"/>
+      <c r="DP6" s="29"/>
+      <c r="DQ6" s="29"/>
+      <c r="DR6" s="29"/>
+      <c r="DS6" s="29"/>
+      <c r="DT6" s="29"/>
+      <c r="DU6" s="29"/>
+      <c r="DV6" s="29"/>
+      <c r="DW6" s="29"/>
+      <c r="DX6" s="29"/>
+      <c r="DY6" s="29"/>
+      <c r="DZ6" s="29"/>
+      <c r="EA6" s="29"/>
+      <c r="EB6" s="29"/>
+      <c r="EC6" s="29"/>
+      <c r="ED6" s="29"/>
+      <c r="EE6" s="29"/>
+      <c r="EF6" s="29"/>
+      <c r="EG6" s="29"/>
+      <c r="EH6" s="29"/>
+      <c r="EI6" s="29"/>
+      <c r="EJ6" s="29"/>
+      <c r="EK6" s="29"/>
+      <c r="EL6" s="29"/>
+      <c r="EM6" s="29"/>
+      <c r="EN6" s="29"/>
+      <c r="EO6" s="29"/>
+      <c r="EP6" s="29"/>
+      <c r="EQ6" s="29"/>
+      <c r="ER6" s="29"/>
+      <c r="ES6" s="29"/>
+      <c r="ET6" s="29"/>
+      <c r="EU6" s="29"/>
+      <c r="EV6" s="29"/>
+      <c r="EW6" s="29"/>
+      <c r="EX6" s="29"/>
+      <c r="EY6" s="29"/>
+      <c r="EZ6" s="29"/>
+      <c r="FA6" s="29"/>
+      <c r="FB6" s="29"/>
+      <c r="FC6" s="29"/>
+      <c r="FD6" s="29"/>
+      <c r="FE6" s="29"/>
+      <c r="FF6" s="29"/>
+      <c r="FG6" s="29"/>
+      <c r="FH6" s="29"/>
+      <c r="FI6" s="29"/>
     </row>
     <row r="7" spans="1:166" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="50" t="s">
+      <c r="A7" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="50"/>
-      <c r="C7" s="48">
+      <c r="B7" s="51"/>
+      <c r="C7" s="49">
         <v>10</v>
       </c>
-      <c r="D7" s="49"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27"/>
-      <c r="I7" s="27"/>
-      <c r="J7" s="27"/>
-      <c r="K7" s="27"/>
-      <c r="L7" s="27"/>
-      <c r="M7" s="27"/>
-      <c r="N7" s="27"/>
-      <c r="O7" s="27"/>
-      <c r="P7" s="27"/>
-      <c r="Q7" s="27"/>
-      <c r="R7" s="27"/>
-      <c r="S7" s="27"/>
-      <c r="T7" s="27"/>
-      <c r="U7" s="27"/>
-      <c r="V7" s="27"/>
-      <c r="W7" s="27"/>
-      <c r="X7" s="27"/>
-      <c r="Y7" s="27"/>
-      <c r="Z7" s="27"/>
-      <c r="AA7" s="27"/>
-      <c r="AB7" s="27"/>
-      <c r="AC7" s="27"/>
-      <c r="AD7" s="27"/>
-      <c r="AE7" s="27"/>
-      <c r="AF7" s="27"/>
-      <c r="AG7" s="27"/>
-      <c r="AH7" s="27"/>
-      <c r="AI7" s="27"/>
-      <c r="AJ7" s="27"/>
-      <c r="AK7" s="27"/>
-      <c r="AL7" s="27"/>
-      <c r="AM7" s="27"/>
-      <c r="AN7" s="27"/>
-      <c r="AO7" s="27"/>
-      <c r="AP7" s="27"/>
-      <c r="AQ7" s="27"/>
-      <c r="AR7" s="27"/>
-      <c r="AS7" s="27"/>
-      <c r="AT7" s="27"/>
-      <c r="AU7" s="27"/>
-      <c r="AV7" s="27"/>
-      <c r="AW7" s="27"/>
-      <c r="AX7" s="27"/>
-      <c r="AY7" s="27"/>
-      <c r="AZ7" s="27"/>
-      <c r="BA7" s="27"/>
-      <c r="BB7" s="27"/>
-      <c r="BC7" s="27"/>
-      <c r="BD7" s="27"/>
-      <c r="BE7" s="27"/>
-      <c r="BF7" s="27"/>
-      <c r="BG7" s="27"/>
-      <c r="BH7" s="27"/>
-      <c r="BI7" s="27"/>
-      <c r="BJ7" s="27"/>
-      <c r="BK7" s="27"/>
-      <c r="BL7" s="27"/>
-      <c r="BM7" s="27"/>
-      <c r="BN7" s="27"/>
-      <c r="BO7" s="27"/>
-      <c r="BP7" s="27"/>
-      <c r="BQ7" s="27"/>
-      <c r="BR7" s="27"/>
-      <c r="BS7" s="27"/>
-      <c r="BT7" s="27"/>
-      <c r="BU7" s="27"/>
-      <c r="BV7" s="27"/>
-      <c r="BW7" s="27"/>
-      <c r="BX7" s="27"/>
-      <c r="BY7" s="27"/>
-      <c r="BZ7" s="27"/>
-      <c r="CA7" s="27"/>
-      <c r="CB7" s="27"/>
-      <c r="CC7" s="27"/>
-      <c r="CD7" s="27"/>
-      <c r="CE7" s="27"/>
-      <c r="CF7" s="27"/>
-      <c r="CG7" s="27"/>
-      <c r="CH7" s="27"/>
-      <c r="CI7" s="27"/>
-      <c r="CJ7" s="27"/>
-      <c r="CK7" s="27"/>
-      <c r="CL7" s="27"/>
-      <c r="CM7" s="27"/>
-      <c r="CN7" s="27"/>
-      <c r="CO7" s="27"/>
-      <c r="CP7" s="27"/>
-      <c r="CQ7" s="27"/>
-      <c r="CR7" s="27"/>
-      <c r="CS7" s="27"/>
-      <c r="CT7" s="27"/>
-      <c r="CU7" s="27"/>
-      <c r="CV7" s="27"/>
-      <c r="CW7" s="27"/>
-      <c r="CX7" s="27"/>
-      <c r="CY7" s="27"/>
-      <c r="CZ7" s="27"/>
-      <c r="DA7" s="27"/>
-      <c r="DB7" s="27"/>
-      <c r="DC7" s="27"/>
-      <c r="DD7" s="27"/>
-      <c r="DE7" s="27"/>
-      <c r="DF7" s="27"/>
-      <c r="DG7" s="27"/>
-      <c r="DH7" s="27"/>
-      <c r="DI7" s="27"/>
-      <c r="DJ7" s="27"/>
-      <c r="DK7" s="27"/>
-      <c r="DL7" s="27"/>
-      <c r="DM7" s="27"/>
-      <c r="DN7" s="27"/>
-      <c r="DO7" s="27"/>
-      <c r="DP7" s="27"/>
-      <c r="DQ7" s="27"/>
-      <c r="DR7" s="27"/>
-      <c r="DS7" s="27"/>
-      <c r="DT7" s="27"/>
-      <c r="DU7" s="27"/>
-      <c r="DV7" s="27"/>
-      <c r="DW7" s="27"/>
-      <c r="DX7" s="27"/>
-      <c r="DY7" s="27"/>
-      <c r="DZ7" s="27"/>
-      <c r="EA7" s="27"/>
-      <c r="EB7" s="27"/>
-      <c r="EC7" s="27"/>
-      <c r="ED7" s="27"/>
-      <c r="EE7" s="27"/>
-      <c r="EF7" s="27"/>
-      <c r="EG7" s="27"/>
-      <c r="EH7" s="27"/>
-      <c r="EI7" s="27"/>
-      <c r="EJ7" s="27"/>
-      <c r="EK7" s="27"/>
-      <c r="EL7" s="27"/>
-      <c r="EM7" s="27"/>
-      <c r="EN7" s="27"/>
-      <c r="EO7" s="27"/>
-      <c r="EP7" s="27"/>
-      <c r="EQ7" s="27"/>
-      <c r="ER7" s="27"/>
-      <c r="ES7" s="27"/>
-      <c r="ET7" s="27"/>
-      <c r="EU7" s="27"/>
-      <c r="EV7" s="27"/>
-      <c r="EW7" s="27"/>
-      <c r="EX7" s="27"/>
-      <c r="EY7" s="27"/>
-      <c r="EZ7" s="27"/>
-      <c r="FA7" s="27"/>
-      <c r="FB7" s="27"/>
-      <c r="FC7" s="27"/>
-      <c r="FD7" s="27"/>
-      <c r="FE7" s="27"/>
-      <c r="FF7" s="27"/>
-      <c r="FG7" s="27"/>
-      <c r="FH7" s="27"/>
-      <c r="FI7" s="27"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="30"/>
+      <c r="M7" s="30"/>
+      <c r="N7" s="30"/>
+      <c r="O7" s="30"/>
+      <c r="P7" s="30"/>
+      <c r="Q7" s="30"/>
+      <c r="R7" s="30"/>
+      <c r="S7" s="30"/>
+      <c r="T7" s="30"/>
+      <c r="U7" s="30"/>
+      <c r="V7" s="30"/>
+      <c r="W7" s="30"/>
+      <c r="X7" s="30"/>
+      <c r="Y7" s="30"/>
+      <c r="Z7" s="30"/>
+      <c r="AA7" s="30"/>
+      <c r="AB7" s="30"/>
+      <c r="AC7" s="30"/>
+      <c r="AD7" s="30"/>
+      <c r="AE7" s="30"/>
+      <c r="AF7" s="30"/>
+      <c r="AG7" s="30"/>
+      <c r="AH7" s="30"/>
+      <c r="AI7" s="30"/>
+      <c r="AJ7" s="30"/>
+      <c r="AK7" s="30"/>
+      <c r="AL7" s="30"/>
+      <c r="AM7" s="30"/>
+      <c r="AN7" s="30"/>
+      <c r="AO7" s="30"/>
+      <c r="AP7" s="30"/>
+      <c r="AQ7" s="30"/>
+      <c r="AR7" s="30"/>
+      <c r="AS7" s="30"/>
+      <c r="AT7" s="30"/>
+      <c r="AU7" s="30"/>
+      <c r="AV7" s="30"/>
+      <c r="AW7" s="30"/>
+      <c r="AX7" s="30"/>
+      <c r="AY7" s="30"/>
+      <c r="AZ7" s="30"/>
+      <c r="BA7" s="30"/>
+      <c r="BB7" s="30"/>
+      <c r="BC7" s="30"/>
+      <c r="BD7" s="30"/>
+      <c r="BE7" s="30"/>
+      <c r="BF7" s="30"/>
+      <c r="BG7" s="30"/>
+      <c r="BH7" s="30"/>
+      <c r="BI7" s="30"/>
+      <c r="BJ7" s="30"/>
+      <c r="BK7" s="30"/>
+      <c r="BL7" s="30"/>
+      <c r="BM7" s="30"/>
+      <c r="BN7" s="30"/>
+      <c r="BO7" s="30"/>
+      <c r="BP7" s="30"/>
+      <c r="BQ7" s="30"/>
+      <c r="BR7" s="30"/>
+      <c r="BS7" s="30"/>
+      <c r="BT7" s="30"/>
+      <c r="BU7" s="30"/>
+      <c r="BV7" s="30"/>
+      <c r="BW7" s="30"/>
+      <c r="BX7" s="30"/>
+      <c r="BY7" s="30"/>
+      <c r="BZ7" s="30"/>
+      <c r="CA7" s="30"/>
+      <c r="CB7" s="30"/>
+      <c r="CC7" s="30"/>
+      <c r="CD7" s="30"/>
+      <c r="CE7" s="30"/>
+      <c r="CF7" s="30"/>
+      <c r="CG7" s="30"/>
+      <c r="CH7" s="30"/>
+      <c r="CI7" s="30"/>
+      <c r="CJ7" s="30"/>
+      <c r="CK7" s="30"/>
+      <c r="CL7" s="30"/>
+      <c r="CM7" s="30"/>
+      <c r="CN7" s="30"/>
+      <c r="CO7" s="30"/>
+      <c r="CP7" s="30"/>
+      <c r="CQ7" s="30"/>
+      <c r="CR7" s="30"/>
+      <c r="CS7" s="30"/>
+      <c r="CT7" s="30"/>
+      <c r="CU7" s="30"/>
+      <c r="CV7" s="30"/>
+      <c r="CW7" s="30"/>
+      <c r="CX7" s="30"/>
+      <c r="CY7" s="30"/>
+      <c r="CZ7" s="30"/>
+      <c r="DA7" s="30"/>
+      <c r="DB7" s="30"/>
+      <c r="DC7" s="30"/>
+      <c r="DD7" s="30"/>
+      <c r="DE7" s="30"/>
+      <c r="DF7" s="30"/>
+      <c r="DG7" s="30"/>
+      <c r="DH7" s="30"/>
+      <c r="DI7" s="30"/>
+      <c r="DJ7" s="30"/>
+      <c r="DK7" s="30"/>
+      <c r="DL7" s="30"/>
+      <c r="DM7" s="30"/>
+      <c r="DN7" s="30"/>
+      <c r="DO7" s="30"/>
+      <c r="DP7" s="30"/>
+      <c r="DQ7" s="30"/>
+      <c r="DR7" s="30"/>
+      <c r="DS7" s="30"/>
+      <c r="DT7" s="30"/>
+      <c r="DU7" s="30"/>
+      <c r="DV7" s="30"/>
+      <c r="DW7" s="30"/>
+      <c r="DX7" s="30"/>
+      <c r="DY7" s="30"/>
+      <c r="DZ7" s="30"/>
+      <c r="EA7" s="30"/>
+      <c r="EB7" s="30"/>
+      <c r="EC7" s="30"/>
+      <c r="ED7" s="30"/>
+      <c r="EE7" s="30"/>
+      <c r="EF7" s="30"/>
+      <c r="EG7" s="30"/>
+      <c r="EH7" s="30"/>
+      <c r="EI7" s="30"/>
+      <c r="EJ7" s="30"/>
+      <c r="EK7" s="30"/>
+      <c r="EL7" s="30"/>
+      <c r="EM7" s="30"/>
+      <c r="EN7" s="30"/>
+      <c r="EO7" s="30"/>
+      <c r="EP7" s="30"/>
+      <c r="EQ7" s="30"/>
+      <c r="ER7" s="30"/>
+      <c r="ES7" s="30"/>
+      <c r="ET7" s="30"/>
+      <c r="EU7" s="30"/>
+      <c r="EV7" s="30"/>
+      <c r="EW7" s="30"/>
+      <c r="EX7" s="30"/>
+      <c r="EY7" s="30"/>
+      <c r="EZ7" s="30"/>
+      <c r="FA7" s="30"/>
+      <c r="FB7" s="30"/>
+      <c r="FC7" s="30"/>
+      <c r="FD7" s="30"/>
+      <c r="FE7" s="30"/>
+      <c r="FF7" s="30"/>
+      <c r="FG7" s="30"/>
+      <c r="FH7" s="30"/>
+      <c r="FI7" s="30"/>
     </row>
     <row r="8" spans="1:166" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="51" t="s">
+      <c r="A8" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="51"/>
-      <c r="C8" s="52">
+      <c r="B8" s="33"/>
+      <c r="C8" s="31">
         <f>SUM(C5:D7)</f>
         <v>175</v>
       </c>
-      <c r="D8" s="46"/>
+      <c r="D8" s="34"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="24">
-        <v>1</v>
-      </c>
-      <c r="G8" s="24">
+      <c r="F8" s="27">
+        <v>1</v>
+      </c>
+      <c r="G8" s="27">
         <v>2</v>
       </c>
-      <c r="H8" s="24">
+      <c r="H8" s="27">
         <v>3</v>
       </c>
-      <c r="I8" s="24">
+      <c r="I8" s="27">
         <v>4</v>
       </c>
-      <c r="J8" s="24">
+      <c r="J8" s="27">
         <v>5</v>
       </c>
-      <c r="K8" s="24">
+      <c r="K8" s="27">
         <v>6</v>
       </c>
-      <c r="L8" s="24">
+      <c r="L8" s="27">
         <v>7</v>
       </c>
-      <c r="M8" s="24">
+      <c r="M8" s="27">
         <v>8</v>
       </c>
-      <c r="N8" s="24">
+      <c r="N8" s="27">
         <v>9</v>
       </c>
-      <c r="O8" s="24">
+      <c r="O8" s="27">
         <v>10</v>
       </c>
-      <c r="P8" s="24">
+      <c r="P8" s="27">
         <v>11</v>
       </c>
-      <c r="Q8" s="24">
+      <c r="Q8" s="27">
         <v>12</v>
       </c>
-      <c r="R8" s="24">
+      <c r="R8" s="27">
         <v>13</v>
       </c>
-      <c r="S8" s="24">
+      <c r="S8" s="27">
         <v>14</v>
       </c>
-      <c r="T8" s="24">
+      <c r="T8" s="27">
         <v>15</v>
       </c>
-      <c r="U8" s="24">
+      <c r="U8" s="27">
         <v>16</v>
       </c>
-      <c r="V8" s="24">
+      <c r="V8" s="27">
         <v>17</v>
       </c>
-      <c r="W8" s="24">
+      <c r="W8" s="27">
         <v>18</v>
       </c>
-      <c r="X8" s="24">
+      <c r="X8" s="27">
         <v>19</v>
       </c>
-      <c r="Y8" s="24">
+      <c r="Y8" s="27">
         <v>20</v>
       </c>
-      <c r="Z8" s="24">
+      <c r="Z8" s="27">
         <v>21</v>
       </c>
-      <c r="AA8" s="24">
+      <c r="AA8" s="27">
         <v>22</v>
       </c>
-      <c r="AB8" s="24">
+      <c r="AB8" s="27">
         <v>23</v>
       </c>
-      <c r="AC8" s="24">
+      <c r="AC8" s="27">
         <v>24</v>
       </c>
-      <c r="AD8" s="24">
+      <c r="AD8" s="27">
         <v>25</v>
       </c>
-      <c r="AE8" s="24">
+      <c r="AE8" s="27">
         <v>26</v>
       </c>
-      <c r="AF8" s="24">
+      <c r="AF8" s="27">
         <v>27</v>
       </c>
-      <c r="AG8" s="24">
+      <c r="AG8" s="27">
         <v>28</v>
       </c>
-      <c r="AH8" s="24">
+      <c r="AH8" s="27">
         <v>29</v>
       </c>
-      <c r="AI8" s="24">
+      <c r="AI8" s="27">
         <v>30</v>
       </c>
-      <c r="AJ8" s="24">
+      <c r="AJ8" s="27">
         <v>31</v>
       </c>
-      <c r="AK8" s="24">
+      <c r="AK8" s="27">
         <v>32</v>
       </c>
-      <c r="AL8" s="24">
+      <c r="AL8" s="27">
         <v>33</v>
       </c>
-      <c r="AM8" s="24">
+      <c r="AM8" s="27">
         <v>34</v>
       </c>
-      <c r="AN8" s="24">
+      <c r="AN8" s="27">
         <v>35</v>
       </c>
-      <c r="AO8" s="24">
+      <c r="AO8" s="27">
         <v>36</v>
       </c>
-      <c r="AP8" s="24">
+      <c r="AP8" s="27">
         <v>37</v>
       </c>
-      <c r="AQ8" s="24">
+      <c r="AQ8" s="27">
         <v>38</v>
       </c>
-      <c r="AR8" s="24">
+      <c r="AR8" s="27">
         <v>39</v>
       </c>
-      <c r="AS8" s="24">
+      <c r="AS8" s="27">
         <v>40</v>
       </c>
-      <c r="AT8" s="24">
+      <c r="AT8" s="27">
         <v>41</v>
       </c>
-      <c r="AU8" s="24">
+      <c r="AU8" s="27">
         <v>42</v>
       </c>
-      <c r="AV8" s="24">
+      <c r="AV8" s="27">
         <v>43</v>
       </c>
-      <c r="AW8" s="24">
+      <c r="AW8" s="27">
         <v>44</v>
       </c>
-      <c r="AX8" s="24">
+      <c r="AX8" s="27">
         <v>45</v>
       </c>
-      <c r="AY8" s="24">
+      <c r="AY8" s="27">
         <v>46</v>
       </c>
-      <c r="AZ8" s="24">
+      <c r="AZ8" s="27">
         <v>47</v>
       </c>
-      <c r="BA8" s="24">
+      <c r="BA8" s="27">
         <v>48</v>
       </c>
-      <c r="BB8" s="24">
+      <c r="BB8" s="27">
         <v>49</v>
       </c>
-      <c r="BC8" s="24">
+      <c r="BC8" s="27">
         <v>50</v>
       </c>
-      <c r="BD8" s="24">
+      <c r="BD8" s="27">
         <v>51</v>
       </c>
-      <c r="BE8" s="24">
+      <c r="BE8" s="27">
         <v>52</v>
       </c>
-      <c r="BF8" s="24">
+      <c r="BF8" s="27">
         <v>53</v>
       </c>
-      <c r="BG8" s="24">
+      <c r="BG8" s="27">
         <v>54</v>
       </c>
-      <c r="BH8" s="24">
+      <c r="BH8" s="27">
         <v>55</v>
       </c>
-      <c r="BI8" s="24">
+      <c r="BI8" s="27">
         <v>56</v>
       </c>
-      <c r="BJ8" s="24">
+      <c r="BJ8" s="27">
         <v>57</v>
       </c>
-      <c r="BK8" s="24">
+      <c r="BK8" s="27">
         <v>58</v>
       </c>
-      <c r="BL8" s="24">
+      <c r="BL8" s="27">
         <v>59</v>
       </c>
-      <c r="BM8" s="24">
+      <c r="BM8" s="27">
         <v>60</v>
       </c>
-      <c r="BN8" s="24">
+      <c r="BN8" s="27">
         <v>61</v>
       </c>
-      <c r="BO8" s="24">
+      <c r="BO8" s="27">
         <v>62</v>
       </c>
-      <c r="BP8" s="24">
+      <c r="BP8" s="27">
         <v>63</v>
       </c>
-      <c r="BQ8" s="24">
+      <c r="BQ8" s="27">
         <v>64</v>
       </c>
-      <c r="BR8" s="24">
+      <c r="BR8" s="27">
         <v>65</v>
       </c>
-      <c r="BS8" s="24">
+      <c r="BS8" s="27">
         <v>66</v>
       </c>
-      <c r="BT8" s="24">
+      <c r="BT8" s="27">
         <v>67</v>
       </c>
-      <c r="BU8" s="24">
+      <c r="BU8" s="27">
         <v>68</v>
       </c>
-      <c r="BV8" s="24">
+      <c r="BV8" s="27">
         <v>69</v>
       </c>
-      <c r="BW8" s="24">
+      <c r="BW8" s="27">
         <v>70</v>
       </c>
-      <c r="BX8" s="24">
+      <c r="BX8" s="27">
         <v>71</v>
       </c>
-      <c r="BY8" s="24">
+      <c r="BY8" s="27">
         <v>72</v>
       </c>
-      <c r="BZ8" s="24">
+      <c r="BZ8" s="27">
         <v>73</v>
       </c>
-      <c r="CA8" s="24">
+      <c r="CA8" s="27">
         <v>74</v>
       </c>
-      <c r="CB8" s="24">
+      <c r="CB8" s="27">
         <v>75</v>
       </c>
-      <c r="CC8" s="24">
+      <c r="CC8" s="27">
         <v>76</v>
       </c>
-      <c r="CD8" s="24">
+      <c r="CD8" s="27">
         <v>77</v>
       </c>
-      <c r="CE8" s="24">
+      <c r="CE8" s="27">
         <v>78</v>
       </c>
-      <c r="CF8" s="24">
+      <c r="CF8" s="27">
         <v>79</v>
       </c>
-      <c r="CG8" s="24">
+      <c r="CG8" s="27">
         <v>80</v>
       </c>
-      <c r="CH8" s="24">
+      <c r="CH8" s="27">
         <v>81</v>
       </c>
-      <c r="CI8" s="24">
+      <c r="CI8" s="27">
         <v>82</v>
       </c>
-      <c r="CJ8" s="24">
+      <c r="CJ8" s="27">
         <v>83</v>
       </c>
-      <c r="CK8" s="24">
+      <c r="CK8" s="27">
         <v>84</v>
       </c>
-      <c r="CL8" s="24">
+      <c r="CL8" s="27">
         <v>85</v>
       </c>
-      <c r="CM8" s="24">
+      <c r="CM8" s="27">
         <v>86</v>
       </c>
-      <c r="CN8" s="24">
+      <c r="CN8" s="27">
         <v>87</v>
       </c>
-      <c r="CO8" s="24">
+      <c r="CO8" s="27">
         <v>88</v>
       </c>
-      <c r="CP8" s="24">
+      <c r="CP8" s="27">
         <v>89</v>
       </c>
-      <c r="CQ8" s="24">
+      <c r="CQ8" s="27">
         <v>90</v>
       </c>
-      <c r="CR8" s="24">
+      <c r="CR8" s="27">
         <v>91</v>
       </c>
-      <c r="CS8" s="24">
+      <c r="CS8" s="27">
         <v>92</v>
       </c>
-      <c r="CT8" s="24">
+      <c r="CT8" s="27">
         <v>93</v>
       </c>
-      <c r="CU8" s="24">
+      <c r="CU8" s="27">
         <v>94</v>
       </c>
-      <c r="CV8" s="24">
+      <c r="CV8" s="27">
         <v>95</v>
       </c>
-      <c r="CW8" s="24">
+      <c r="CW8" s="27">
         <v>96</v>
       </c>
-      <c r="CX8" s="24">
+      <c r="CX8" s="27">
         <v>97</v>
       </c>
-      <c r="CY8" s="24">
+      <c r="CY8" s="27">
         <v>98</v>
       </c>
-      <c r="CZ8" s="24">
+      <c r="CZ8" s="27">
         <v>99</v>
       </c>
-      <c r="DA8" s="24">
+      <c r="DA8" s="27">
         <v>100</v>
       </c>
-      <c r="DB8" s="24">
+      <c r="DB8" s="27">
         <v>101</v>
       </c>
-      <c r="DC8" s="24">
+      <c r="DC8" s="27">
         <v>102</v>
       </c>
-      <c r="DD8" s="24">
+      <c r="DD8" s="27">
         <v>103</v>
       </c>
-      <c r="DE8" s="24">
+      <c r="DE8" s="27">
         <v>104</v>
       </c>
-      <c r="DF8" s="24">
+      <c r="DF8" s="27">
         <v>105</v>
       </c>
-      <c r="DG8" s="24">
+      <c r="DG8" s="27">
         <v>106</v>
       </c>
-      <c r="DH8" s="24">
+      <c r="DH8" s="27">
         <v>107</v>
       </c>
-      <c r="DI8" s="24">
+      <c r="DI8" s="27">
         <v>108</v>
       </c>
-      <c r="DJ8" s="24">
+      <c r="DJ8" s="27">
         <v>109</v>
       </c>
-      <c r="DK8" s="24">
+      <c r="DK8" s="27">
         <v>110</v>
       </c>
-      <c r="DL8" s="24">
+      <c r="DL8" s="27">
         <v>111</v>
       </c>
-      <c r="DM8" s="24">
+      <c r="DM8" s="27">
         <v>112</v>
       </c>
-      <c r="DN8" s="24">
+      <c r="DN8" s="27">
         <v>113</v>
       </c>
-      <c r="DO8" s="24">
+      <c r="DO8" s="27">
         <v>114</v>
       </c>
-      <c r="DP8" s="24">
+      <c r="DP8" s="27">
         <v>115</v>
       </c>
-      <c r="DQ8" s="24">
+      <c r="DQ8" s="27">
         <v>116</v>
       </c>
-      <c r="DR8" s="24">
+      <c r="DR8" s="27">
         <v>117</v>
       </c>
-      <c r="DS8" s="24">
+      <c r="DS8" s="27">
         <v>118</v>
       </c>
-      <c r="DT8" s="24">
+      <c r="DT8" s="27">
         <v>119</v>
       </c>
-      <c r="DU8" s="24">
+      <c r="DU8" s="27">
         <v>120</v>
       </c>
-      <c r="DV8" s="24">
+      <c r="DV8" s="27">
         <v>121</v>
       </c>
-      <c r="DW8" s="24">
+      <c r="DW8" s="27">
         <v>122</v>
       </c>
-      <c r="DX8" s="24">
+      <c r="DX8" s="27">
         <v>123</v>
       </c>
-      <c r="DY8" s="24">
+      <c r="DY8" s="27">
         <v>124</v>
       </c>
-      <c r="DZ8" s="24">
+      <c r="DZ8" s="27">
         <v>125</v>
       </c>
-      <c r="EA8" s="24">
+      <c r="EA8" s="27">
         <v>126</v>
       </c>
-      <c r="EB8" s="24">
+      <c r="EB8" s="27">
         <v>127</v>
       </c>
-      <c r="EC8" s="24">
+      <c r="EC8" s="27">
         <v>128</v>
       </c>
-      <c r="ED8" s="24">
+      <c r="ED8" s="27">
         <v>129</v>
       </c>
-      <c r="EE8" s="24">
+      <c r="EE8" s="27">
         <v>130</v>
       </c>
-      <c r="EF8" s="24">
+      <c r="EF8" s="27">
         <v>131</v>
       </c>
-      <c r="EG8" s="24">
+      <c r="EG8" s="27">
         <v>132</v>
       </c>
-      <c r="EH8" s="24">
+      <c r="EH8" s="27">
         <v>133</v>
       </c>
-      <c r="EI8" s="24">
+      <c r="EI8" s="27">
         <v>134</v>
       </c>
-      <c r="EJ8" s="24">
+      <c r="EJ8" s="27">
         <v>135</v>
       </c>
-      <c r="EK8" s="24">
+      <c r="EK8" s="27">
         <v>136</v>
       </c>
-      <c r="EL8" s="24">
+      <c r="EL8" s="27">
         <v>137</v>
       </c>
-      <c r="EM8" s="24">
+      <c r="EM8" s="27">
         <v>138</v>
       </c>
-      <c r="EN8" s="24">
+      <c r="EN8" s="27">
         <v>139</v>
       </c>
-      <c r="EO8" s="24">
+      <c r="EO8" s="27">
         <v>140</v>
       </c>
-      <c r="EP8" s="24">
+      <c r="EP8" s="27">
         <v>141</v>
       </c>
-      <c r="EQ8" s="24">
+      <c r="EQ8" s="27">
         <v>142</v>
       </c>
-      <c r="ER8" s="24">
+      <c r="ER8" s="27">
         <v>143</v>
       </c>
-      <c r="ES8" s="24">
+      <c r="ES8" s="27">
         <v>144</v>
       </c>
-      <c r="ET8" s="24">
+      <c r="ET8" s="27">
         <v>145</v>
       </c>
-      <c r="EU8" s="24">
+      <c r="EU8" s="27">
         <v>146</v>
       </c>
-      <c r="EV8" s="24">
+      <c r="EV8" s="27">
         <v>147</v>
       </c>
-      <c r="EW8" s="24">
+      <c r="EW8" s="27">
         <v>148</v>
       </c>
-      <c r="EX8" s="24">
+      <c r="EX8" s="27">
         <v>149</v>
       </c>
-      <c r="EY8" s="24">
+      <c r="EY8" s="27">
         <v>150</v>
       </c>
-      <c r="EZ8" s="24">
+      <c r="EZ8" s="27">
         <v>151</v>
       </c>
-      <c r="FA8" s="24">
+      <c r="FA8" s="27">
         <v>152</v>
       </c>
-      <c r="FB8" s="24">
+      <c r="FB8" s="27">
         <v>153</v>
       </c>
-      <c r="FC8" s="24">
+      <c r="FC8" s="27">
         <v>154</v>
       </c>
-      <c r="FD8" s="24">
+      <c r="FD8" s="27">
         <v>155</v>
       </c>
-      <c r="FE8" s="24">
+      <c r="FE8" s="27">
         <v>156</v>
       </c>
-      <c r="FF8" s="24">
+      <c r="FF8" s="27">
         <v>157</v>
       </c>
-      <c r="FG8" s="24">
+      <c r="FG8" s="27">
         <v>158</v>
       </c>
-      <c r="FH8" s="24">
+      <c r="FH8" s="27">
         <v>159</v>
       </c>
-      <c r="FI8" s="24">
+      <c r="FI8" s="27">
         <v>160</v>
       </c>
     </row>
     <row r="9" spans="1:166" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="43" t="s">
+      <c r="A9" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="53" t="s">
+      <c r="B9" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="54" t="s">
+      <c r="C9" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="53"/>
+      <c r="D9" s="36"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="25"/>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="25"/>
-      <c r="M9" s="25"/>
-      <c r="N9" s="25"/>
-      <c r="O9" s="25"/>
-      <c r="P9" s="25"/>
-      <c r="Q9" s="25"/>
-      <c r="R9" s="25"/>
-      <c r="S9" s="25"/>
-      <c r="T9" s="25"/>
-      <c r="U9" s="25"/>
-      <c r="V9" s="25"/>
-      <c r="W9" s="25"/>
-      <c r="X9" s="25"/>
-      <c r="Y9" s="25"/>
-      <c r="Z9" s="25"/>
-      <c r="AA9" s="25"/>
-      <c r="AB9" s="25"/>
-      <c r="AC9" s="25"/>
-      <c r="AD9" s="25"/>
-      <c r="AE9" s="25"/>
-      <c r="AF9" s="25"/>
-      <c r="AG9" s="25"/>
-      <c r="AH9" s="25"/>
-      <c r="AI9" s="25"/>
-      <c r="AJ9" s="25"/>
-      <c r="AK9" s="25"/>
-      <c r="AL9" s="25"/>
-      <c r="AM9" s="25"/>
-      <c r="AN9" s="25"/>
-      <c r="AO9" s="25"/>
-      <c r="AP9" s="25"/>
-      <c r="AQ9" s="25"/>
-      <c r="AR9" s="25"/>
-      <c r="AS9" s="25"/>
-      <c r="AT9" s="25"/>
-      <c r="AU9" s="25"/>
-      <c r="AV9" s="25"/>
-      <c r="AW9" s="25"/>
-      <c r="AX9" s="25"/>
-      <c r="AY9" s="25"/>
-      <c r="AZ9" s="25"/>
-      <c r="BA9" s="25"/>
-      <c r="BB9" s="25"/>
-      <c r="BC9" s="25"/>
-      <c r="BD9" s="25"/>
-      <c r="BE9" s="25"/>
-      <c r="BF9" s="25"/>
-      <c r="BG9" s="25"/>
-      <c r="BH9" s="25"/>
-      <c r="BI9" s="25"/>
-      <c r="BJ9" s="25"/>
-      <c r="BK9" s="25"/>
-      <c r="BL9" s="25"/>
-      <c r="BM9" s="25"/>
-      <c r="BN9" s="25"/>
-      <c r="BO9" s="25"/>
-      <c r="BP9" s="25"/>
-      <c r="BQ9" s="25"/>
-      <c r="BR9" s="25"/>
-      <c r="BS9" s="25"/>
-      <c r="BT9" s="25"/>
-      <c r="BU9" s="25"/>
-      <c r="BV9" s="25"/>
-      <c r="BW9" s="25"/>
-      <c r="BX9" s="25"/>
-      <c r="BY9" s="25"/>
-      <c r="BZ9" s="25"/>
-      <c r="CA9" s="25"/>
-      <c r="CB9" s="25"/>
-      <c r="CC9" s="25"/>
-      <c r="CD9" s="25"/>
-      <c r="CE9" s="25"/>
-      <c r="CF9" s="25"/>
-      <c r="CG9" s="25"/>
-      <c r="CH9" s="25"/>
-      <c r="CI9" s="25"/>
-      <c r="CJ9" s="25"/>
-      <c r="CK9" s="25"/>
-      <c r="CL9" s="25"/>
-      <c r="CM9" s="25"/>
-      <c r="CN9" s="25"/>
-      <c r="CO9" s="25"/>
-      <c r="CP9" s="25"/>
-      <c r="CQ9" s="25"/>
-      <c r="CR9" s="25"/>
-      <c r="CS9" s="25"/>
-      <c r="CT9" s="25"/>
-      <c r="CU9" s="25"/>
-      <c r="CV9" s="25"/>
-      <c r="CW9" s="25"/>
-      <c r="CX9" s="25"/>
-      <c r="CY9" s="25"/>
-      <c r="CZ9" s="25"/>
-      <c r="DA9" s="25"/>
-      <c r="DB9" s="25"/>
-      <c r="DC9" s="25"/>
-      <c r="DD9" s="25"/>
-      <c r="DE9" s="25"/>
-      <c r="DF9" s="25"/>
-      <c r="DG9" s="25"/>
-      <c r="DH9" s="25"/>
-      <c r="DI9" s="25"/>
-      <c r="DJ9" s="25"/>
-      <c r="DK9" s="25"/>
-      <c r="DL9" s="25"/>
-      <c r="DM9" s="25"/>
-      <c r="DN9" s="25"/>
-      <c r="DO9" s="25"/>
-      <c r="DP9" s="25"/>
-      <c r="DQ9" s="25"/>
-      <c r="DR9" s="25"/>
-      <c r="DS9" s="25"/>
-      <c r="DT9" s="25"/>
-      <c r="DU9" s="25"/>
-      <c r="DV9" s="25"/>
-      <c r="DW9" s="25"/>
-      <c r="DX9" s="25"/>
-      <c r="DY9" s="25"/>
-      <c r="DZ9" s="25"/>
-      <c r="EA9" s="25"/>
-      <c r="EB9" s="25"/>
-      <c r="EC9" s="25"/>
-      <c r="ED9" s="25"/>
-      <c r="EE9" s="25"/>
-      <c r="EF9" s="25"/>
-      <c r="EG9" s="25"/>
-      <c r="EH9" s="25"/>
-      <c r="EI9" s="25"/>
-      <c r="EJ9" s="25"/>
-      <c r="EK9" s="25"/>
-      <c r="EL9" s="25"/>
-      <c r="EM9" s="25"/>
-      <c r="EN9" s="25"/>
-      <c r="EO9" s="25"/>
-      <c r="EP9" s="25"/>
-      <c r="EQ9" s="25"/>
-      <c r="ER9" s="25"/>
-      <c r="ES9" s="25"/>
-      <c r="ET9" s="25"/>
-      <c r="EU9" s="25"/>
-      <c r="EV9" s="25"/>
-      <c r="EW9" s="25"/>
-      <c r="EX9" s="25"/>
-      <c r="EY9" s="25"/>
-      <c r="EZ9" s="25"/>
-      <c r="FA9" s="25"/>
-      <c r="FB9" s="25"/>
-      <c r="FC9" s="25"/>
-      <c r="FD9" s="25"/>
-      <c r="FE9" s="25"/>
-      <c r="FF9" s="25"/>
-      <c r="FG9" s="25"/>
-      <c r="FH9" s="25"/>
-      <c r="FI9" s="25"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+      <c r="M9" s="28"/>
+      <c r="N9" s="28"/>
+      <c r="O9" s="28"/>
+      <c r="P9" s="28"/>
+      <c r="Q9" s="28"/>
+      <c r="R9" s="28"/>
+      <c r="S9" s="28"/>
+      <c r="T9" s="28"/>
+      <c r="U9" s="28"/>
+      <c r="V9" s="28"/>
+      <c r="W9" s="28"/>
+      <c r="X9" s="28"/>
+      <c r="Y9" s="28"/>
+      <c r="Z9" s="28"/>
+      <c r="AA9" s="28"/>
+      <c r="AB9" s="28"/>
+      <c r="AC9" s="28"/>
+      <c r="AD9" s="28"/>
+      <c r="AE9" s="28"/>
+      <c r="AF9" s="28"/>
+      <c r="AG9" s="28"/>
+      <c r="AH9" s="28"/>
+      <c r="AI9" s="28"/>
+      <c r="AJ9" s="28"/>
+      <c r="AK9" s="28"/>
+      <c r="AL9" s="28"/>
+      <c r="AM9" s="28"/>
+      <c r="AN9" s="28"/>
+      <c r="AO9" s="28"/>
+      <c r="AP9" s="28"/>
+      <c r="AQ9" s="28"/>
+      <c r="AR9" s="28"/>
+      <c r="AS9" s="28"/>
+      <c r="AT9" s="28"/>
+      <c r="AU9" s="28"/>
+      <c r="AV9" s="28"/>
+      <c r="AW9" s="28"/>
+      <c r="AX9" s="28"/>
+      <c r="AY9" s="28"/>
+      <c r="AZ9" s="28"/>
+      <c r="BA9" s="28"/>
+      <c r="BB9" s="28"/>
+      <c r="BC9" s="28"/>
+      <c r="BD9" s="28"/>
+      <c r="BE9" s="28"/>
+      <c r="BF9" s="28"/>
+      <c r="BG9" s="28"/>
+      <c r="BH9" s="28"/>
+      <c r="BI9" s="28"/>
+      <c r="BJ9" s="28"/>
+      <c r="BK9" s="28"/>
+      <c r="BL9" s="28"/>
+      <c r="BM9" s="28"/>
+      <c r="BN9" s="28"/>
+      <c r="BO9" s="28"/>
+      <c r="BP9" s="28"/>
+      <c r="BQ9" s="28"/>
+      <c r="BR9" s="28"/>
+      <c r="BS9" s="28"/>
+      <c r="BT9" s="28"/>
+      <c r="BU9" s="28"/>
+      <c r="BV9" s="28"/>
+      <c r="BW9" s="28"/>
+      <c r="BX9" s="28"/>
+      <c r="BY9" s="28"/>
+      <c r="BZ9" s="28"/>
+      <c r="CA9" s="28"/>
+      <c r="CB9" s="28"/>
+      <c r="CC9" s="28"/>
+      <c r="CD9" s="28"/>
+      <c r="CE9" s="28"/>
+      <c r="CF9" s="28"/>
+      <c r="CG9" s="28"/>
+      <c r="CH9" s="28"/>
+      <c r="CI9" s="28"/>
+      <c r="CJ9" s="28"/>
+      <c r="CK9" s="28"/>
+      <c r="CL9" s="28"/>
+      <c r="CM9" s="28"/>
+      <c r="CN9" s="28"/>
+      <c r="CO9" s="28"/>
+      <c r="CP9" s="28"/>
+      <c r="CQ9" s="28"/>
+      <c r="CR9" s="28"/>
+      <c r="CS9" s="28"/>
+      <c r="CT9" s="28"/>
+      <c r="CU9" s="28"/>
+      <c r="CV9" s="28"/>
+      <c r="CW9" s="28"/>
+      <c r="CX9" s="28"/>
+      <c r="CY9" s="28"/>
+      <c r="CZ9" s="28"/>
+      <c r="DA9" s="28"/>
+      <c r="DB9" s="28"/>
+      <c r="DC9" s="28"/>
+      <c r="DD9" s="28"/>
+      <c r="DE9" s="28"/>
+      <c r="DF9" s="28"/>
+      <c r="DG9" s="28"/>
+      <c r="DH9" s="28"/>
+      <c r="DI9" s="28"/>
+      <c r="DJ9" s="28"/>
+      <c r="DK9" s="28"/>
+      <c r="DL9" s="28"/>
+      <c r="DM9" s="28"/>
+      <c r="DN9" s="28"/>
+      <c r="DO9" s="28"/>
+      <c r="DP9" s="28"/>
+      <c r="DQ9" s="28"/>
+      <c r="DR9" s="28"/>
+      <c r="DS9" s="28"/>
+      <c r="DT9" s="28"/>
+      <c r="DU9" s="28"/>
+      <c r="DV9" s="28"/>
+      <c r="DW9" s="28"/>
+      <c r="DX9" s="28"/>
+      <c r="DY9" s="28"/>
+      <c r="DZ9" s="28"/>
+      <c r="EA9" s="28"/>
+      <c r="EB9" s="28"/>
+      <c r="EC9" s="28"/>
+      <c r="ED9" s="28"/>
+      <c r="EE9" s="28"/>
+      <c r="EF9" s="28"/>
+      <c r="EG9" s="28"/>
+      <c r="EH9" s="28"/>
+      <c r="EI9" s="28"/>
+      <c r="EJ9" s="28"/>
+      <c r="EK9" s="28"/>
+      <c r="EL9" s="28"/>
+      <c r="EM9" s="28"/>
+      <c r="EN9" s="28"/>
+      <c r="EO9" s="28"/>
+      <c r="EP9" s="28"/>
+      <c r="EQ9" s="28"/>
+      <c r="ER9" s="28"/>
+      <c r="ES9" s="28"/>
+      <c r="ET9" s="28"/>
+      <c r="EU9" s="28"/>
+      <c r="EV9" s="28"/>
+      <c r="EW9" s="28"/>
+      <c r="EX9" s="28"/>
+      <c r="EY9" s="28"/>
+      <c r="EZ9" s="28"/>
+      <c r="FA9" s="28"/>
+      <c r="FB9" s="28"/>
+      <c r="FC9" s="28"/>
+      <c r="FD9" s="28"/>
+      <c r="FE9" s="28"/>
+      <c r="FF9" s="28"/>
+      <c r="FG9" s="28"/>
+      <c r="FH9" s="28"/>
+      <c r="FI9" s="28"/>
     </row>
     <row r="10" spans="1:166" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="43"/>
-      <c r="B10" s="53"/>
+      <c r="A10" s="35"/>
+      <c r="B10" s="36"/>
       <c r="C10" s="6"/>
       <c r="D10" s="4" t="s">
         <v>10</v>
@@ -5979,329 +5979,329 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E26" s="52"/>
-      <c r="F26" s="45"/>
-      <c r="G26" s="45"/>
-      <c r="H26" s="45"/>
-      <c r="I26" s="45"/>
-      <c r="J26" s="45"/>
-      <c r="K26" s="45"/>
-      <c r="L26" s="45"/>
-      <c r="M26" s="45"/>
-      <c r="N26" s="45"/>
-      <c r="O26" s="45"/>
-      <c r="P26" s="45"/>
-      <c r="Q26" s="45"/>
-      <c r="R26" s="45"/>
-      <c r="S26" s="45"/>
-      <c r="T26" s="45"/>
-      <c r="U26" s="45"/>
-      <c r="V26" s="45"/>
-      <c r="W26" s="45"/>
-      <c r="X26" s="45"/>
-      <c r="Y26" s="45"/>
-      <c r="Z26" s="45"/>
-      <c r="AA26" s="45"/>
-      <c r="AB26" s="45"/>
-      <c r="AC26" s="45"/>
-      <c r="AD26" s="45"/>
-      <c r="AE26" s="45"/>
-      <c r="AF26" s="45"/>
-      <c r="AG26" s="45"/>
-      <c r="AH26" s="45"/>
-      <c r="AI26" s="45"/>
-      <c r="AJ26" s="45"/>
-      <c r="AK26" s="45"/>
-      <c r="AL26" s="45"/>
-      <c r="AM26" s="45"/>
-      <c r="AN26" s="45"/>
-      <c r="AO26" s="45"/>
-      <c r="AP26" s="45"/>
-      <c r="AQ26" s="45"/>
-      <c r="AR26" s="45"/>
-      <c r="AS26" s="45"/>
-      <c r="AT26" s="45"/>
-      <c r="AU26" s="45"/>
-      <c r="AV26" s="45"/>
-      <c r="AW26" s="45"/>
-      <c r="AX26" s="45"/>
-      <c r="AY26" s="45"/>
-      <c r="AZ26" s="45"/>
-      <c r="BA26" s="45"/>
-      <c r="BB26" s="45"/>
-      <c r="BC26" s="45"/>
-      <c r="BD26" s="45"/>
-      <c r="BE26" s="45"/>
-      <c r="BF26" s="45"/>
-      <c r="BG26" s="45"/>
-      <c r="BH26" s="45"/>
-      <c r="BI26" s="45"/>
-      <c r="BJ26" s="45"/>
-      <c r="BK26" s="45"/>
-      <c r="BL26" s="45"/>
-      <c r="BM26" s="45"/>
-      <c r="BN26" s="45"/>
-      <c r="BO26" s="45"/>
-      <c r="BP26" s="45"/>
-      <c r="BQ26" s="45"/>
-      <c r="BR26" s="45"/>
-      <c r="BS26" s="45"/>
-      <c r="BT26" s="45"/>
-      <c r="BU26" s="45"/>
-      <c r="BV26" s="45"/>
-      <c r="BW26" s="45"/>
-      <c r="BX26" s="45"/>
-      <c r="BY26" s="45"/>
-      <c r="BZ26" s="45"/>
-      <c r="CA26" s="45"/>
-      <c r="CB26" s="45"/>
-      <c r="CC26" s="45"/>
-      <c r="CD26" s="45"/>
-      <c r="CE26" s="45"/>
-      <c r="CF26" s="45"/>
-      <c r="CG26" s="45"/>
-      <c r="CH26" s="45"/>
-      <c r="CI26" s="45"/>
-      <c r="CJ26" s="45"/>
-      <c r="CK26" s="45"/>
-      <c r="CL26" s="45"/>
-      <c r="CM26" s="45"/>
-      <c r="CN26" s="45"/>
-      <c r="CO26" s="45"/>
-      <c r="CP26" s="45"/>
-      <c r="CQ26" s="45"/>
-      <c r="CR26" s="45"/>
-      <c r="CS26" s="45"/>
-      <c r="CT26" s="45"/>
-      <c r="CU26" s="45"/>
-      <c r="CV26" s="45"/>
-      <c r="CW26" s="45"/>
-      <c r="CX26" s="45"/>
-      <c r="CY26" s="45"/>
-      <c r="CZ26" s="45"/>
-      <c r="DA26" s="45"/>
-      <c r="DB26" s="45"/>
-      <c r="DC26" s="45"/>
-      <c r="DD26" s="45"/>
-      <c r="DE26" s="45"/>
-      <c r="DF26" s="45"/>
-      <c r="DG26" s="45"/>
-      <c r="DH26" s="45"/>
-      <c r="DI26" s="45"/>
-      <c r="DJ26" s="45"/>
-      <c r="DK26" s="45"/>
-      <c r="DL26" s="45"/>
-      <c r="DM26" s="45"/>
-      <c r="DN26" s="45"/>
-      <c r="DO26" s="45"/>
-      <c r="DP26" s="45"/>
-      <c r="DQ26" s="45"/>
-      <c r="DR26" s="45"/>
-      <c r="DS26" s="45"/>
-      <c r="DT26" s="45"/>
-      <c r="DU26" s="45"/>
-      <c r="DV26" s="45"/>
-      <c r="DW26" s="45"/>
-      <c r="DX26" s="45"/>
-      <c r="DY26" s="45"/>
-      <c r="DZ26" s="45"/>
-      <c r="EA26" s="45"/>
-      <c r="EB26" s="45"/>
-      <c r="EC26" s="45"/>
-      <c r="ED26" s="45"/>
-      <c r="EE26" s="45"/>
-      <c r="EF26" s="45"/>
-      <c r="EG26" s="45"/>
-      <c r="EH26" s="45"/>
-      <c r="EI26" s="45"/>
-      <c r="EJ26" s="45"/>
-      <c r="EK26" s="45"/>
-      <c r="EL26" s="45"/>
-      <c r="EM26" s="45"/>
-      <c r="EN26" s="45"/>
-      <c r="EO26" s="45"/>
-      <c r="EP26" s="45"/>
-      <c r="EQ26" s="45"/>
-      <c r="ER26" s="45"/>
-      <c r="ES26" s="45"/>
-      <c r="ET26" s="45"/>
-      <c r="EU26" s="45"/>
-      <c r="EV26" s="45"/>
-      <c r="EW26" s="45"/>
-      <c r="EX26" s="45"/>
-      <c r="EY26" s="45"/>
-      <c r="EZ26" s="45"/>
-      <c r="FA26" s="45"/>
-      <c r="FB26" s="45"/>
-      <c r="FC26" s="45"/>
-      <c r="FD26" s="45"/>
-      <c r="FE26" s="45"/>
-      <c r="FF26" s="45"/>
-      <c r="FG26" s="45"/>
-      <c r="FH26" s="45"/>
-      <c r="FI26" s="45"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="32"/>
+      <c r="J26" s="32"/>
+      <c r="K26" s="32"/>
+      <c r="L26" s="32"/>
+      <c r="M26" s="32"/>
+      <c r="N26" s="32"/>
+      <c r="O26" s="32"/>
+      <c r="P26" s="32"/>
+      <c r="Q26" s="32"/>
+      <c r="R26" s="32"/>
+      <c r="S26" s="32"/>
+      <c r="T26" s="32"/>
+      <c r="U26" s="32"/>
+      <c r="V26" s="32"/>
+      <c r="W26" s="32"/>
+      <c r="X26" s="32"/>
+      <c r="Y26" s="32"/>
+      <c r="Z26" s="32"/>
+      <c r="AA26" s="32"/>
+      <c r="AB26" s="32"/>
+      <c r="AC26" s="32"/>
+      <c r="AD26" s="32"/>
+      <c r="AE26" s="32"/>
+      <c r="AF26" s="32"/>
+      <c r="AG26" s="32"/>
+      <c r="AH26" s="32"/>
+      <c r="AI26" s="32"/>
+      <c r="AJ26" s="32"/>
+      <c r="AK26" s="32"/>
+      <c r="AL26" s="32"/>
+      <c r="AM26" s="32"/>
+      <c r="AN26" s="32"/>
+      <c r="AO26" s="32"/>
+      <c r="AP26" s="32"/>
+      <c r="AQ26" s="32"/>
+      <c r="AR26" s="32"/>
+      <c r="AS26" s="32"/>
+      <c r="AT26" s="32"/>
+      <c r="AU26" s="32"/>
+      <c r="AV26" s="32"/>
+      <c r="AW26" s="32"/>
+      <c r="AX26" s="32"/>
+      <c r="AY26" s="32"/>
+      <c r="AZ26" s="32"/>
+      <c r="BA26" s="32"/>
+      <c r="BB26" s="32"/>
+      <c r="BC26" s="32"/>
+      <c r="BD26" s="32"/>
+      <c r="BE26" s="32"/>
+      <c r="BF26" s="32"/>
+      <c r="BG26" s="32"/>
+      <c r="BH26" s="32"/>
+      <c r="BI26" s="32"/>
+      <c r="BJ26" s="32"/>
+      <c r="BK26" s="32"/>
+      <c r="BL26" s="32"/>
+      <c r="BM26" s="32"/>
+      <c r="BN26" s="32"/>
+      <c r="BO26" s="32"/>
+      <c r="BP26" s="32"/>
+      <c r="BQ26" s="32"/>
+      <c r="BR26" s="32"/>
+      <c r="BS26" s="32"/>
+      <c r="BT26" s="32"/>
+      <c r="BU26" s="32"/>
+      <c r="BV26" s="32"/>
+      <c r="BW26" s="32"/>
+      <c r="BX26" s="32"/>
+      <c r="BY26" s="32"/>
+      <c r="BZ26" s="32"/>
+      <c r="CA26" s="32"/>
+      <c r="CB26" s="32"/>
+      <c r="CC26" s="32"/>
+      <c r="CD26" s="32"/>
+      <c r="CE26" s="32"/>
+      <c r="CF26" s="32"/>
+      <c r="CG26" s="32"/>
+      <c r="CH26" s="32"/>
+      <c r="CI26" s="32"/>
+      <c r="CJ26" s="32"/>
+      <c r="CK26" s="32"/>
+      <c r="CL26" s="32"/>
+      <c r="CM26" s="32"/>
+      <c r="CN26" s="32"/>
+      <c r="CO26" s="32"/>
+      <c r="CP26" s="32"/>
+      <c r="CQ26" s="32"/>
+      <c r="CR26" s="32"/>
+      <c r="CS26" s="32"/>
+      <c r="CT26" s="32"/>
+      <c r="CU26" s="32"/>
+      <c r="CV26" s="32"/>
+      <c r="CW26" s="32"/>
+      <c r="CX26" s="32"/>
+      <c r="CY26" s="32"/>
+      <c r="CZ26" s="32"/>
+      <c r="DA26" s="32"/>
+      <c r="DB26" s="32"/>
+      <c r="DC26" s="32"/>
+      <c r="DD26" s="32"/>
+      <c r="DE26" s="32"/>
+      <c r="DF26" s="32"/>
+      <c r="DG26" s="32"/>
+      <c r="DH26" s="32"/>
+      <c r="DI26" s="32"/>
+      <c r="DJ26" s="32"/>
+      <c r="DK26" s="32"/>
+      <c r="DL26" s="32"/>
+      <c r="DM26" s="32"/>
+      <c r="DN26" s="32"/>
+      <c r="DO26" s="32"/>
+      <c r="DP26" s="32"/>
+      <c r="DQ26" s="32"/>
+      <c r="DR26" s="32"/>
+      <c r="DS26" s="32"/>
+      <c r="DT26" s="32"/>
+      <c r="DU26" s="32"/>
+      <c r="DV26" s="32"/>
+      <c r="DW26" s="32"/>
+      <c r="DX26" s="32"/>
+      <c r="DY26" s="32"/>
+      <c r="DZ26" s="32"/>
+      <c r="EA26" s="32"/>
+      <c r="EB26" s="32"/>
+      <c r="EC26" s="32"/>
+      <c r="ED26" s="32"/>
+      <c r="EE26" s="32"/>
+      <c r="EF26" s="32"/>
+      <c r="EG26" s="32"/>
+      <c r="EH26" s="32"/>
+      <c r="EI26" s="32"/>
+      <c r="EJ26" s="32"/>
+      <c r="EK26" s="32"/>
+      <c r="EL26" s="32"/>
+      <c r="EM26" s="32"/>
+      <c r="EN26" s="32"/>
+      <c r="EO26" s="32"/>
+      <c r="EP26" s="32"/>
+      <c r="EQ26" s="32"/>
+      <c r="ER26" s="32"/>
+      <c r="ES26" s="32"/>
+      <c r="ET26" s="32"/>
+      <c r="EU26" s="32"/>
+      <c r="EV26" s="32"/>
+      <c r="EW26" s="32"/>
+      <c r="EX26" s="32"/>
+      <c r="EY26" s="32"/>
+      <c r="EZ26" s="32"/>
+      <c r="FA26" s="32"/>
+      <c r="FB26" s="32"/>
+      <c r="FC26" s="32"/>
+      <c r="FD26" s="32"/>
+      <c r="FE26" s="32"/>
+      <c r="FF26" s="32"/>
+      <c r="FG26" s="32"/>
+      <c r="FH26" s="32"/>
+      <c r="FI26" s="32"/>
     </row>
     <row r="27" spans="1:165" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F27" s="31"/>
-      <c r="G27" s="31"/>
-      <c r="H27" s="31"/>
-      <c r="I27" s="31"/>
-      <c r="J27" s="31"/>
-      <c r="K27" s="31"/>
-      <c r="L27" s="31"/>
-      <c r="M27" s="31"/>
-      <c r="N27" s="31"/>
-      <c r="O27" s="31"/>
-      <c r="P27" s="31"/>
-      <c r="Q27" s="31"/>
-      <c r="R27" s="31"/>
-      <c r="S27" s="31"/>
-      <c r="T27" s="31"/>
-      <c r="U27" s="31"/>
-      <c r="V27" s="31"/>
-      <c r="W27" s="31"/>
-      <c r="X27" s="31"/>
-      <c r="Y27" s="31"/>
-      <c r="Z27" s="31"/>
-      <c r="AA27" s="31"/>
-      <c r="AB27" s="31"/>
-      <c r="AC27" s="31"/>
-      <c r="AD27" s="31"/>
-      <c r="AE27" s="31"/>
-      <c r="AF27" s="31"/>
-      <c r="AG27" s="31"/>
-      <c r="AH27" s="31"/>
-      <c r="AI27" s="31"/>
-      <c r="AJ27" s="31"/>
-      <c r="AK27" s="31"/>
-      <c r="AL27" s="31"/>
-      <c r="AM27" s="31"/>
-      <c r="AN27" s="31"/>
-      <c r="AO27" s="31"/>
-      <c r="AP27" s="31"/>
-      <c r="AQ27" s="31"/>
-      <c r="AR27" s="31"/>
-      <c r="AS27" s="31"/>
-      <c r="AT27" s="31"/>
-      <c r="AU27" s="31"/>
-      <c r="AV27" s="31"/>
-      <c r="AW27" s="31"/>
-      <c r="AX27" s="31"/>
-      <c r="AY27" s="31"/>
-      <c r="AZ27" s="31"/>
-      <c r="BA27" s="31"/>
-      <c r="BB27" s="31"/>
-      <c r="BC27" s="31"/>
-      <c r="BD27" s="31"/>
-      <c r="BE27" s="31"/>
-      <c r="BF27" s="31"/>
-      <c r="BG27" s="31"/>
-      <c r="BH27" s="31"/>
-      <c r="BI27" s="31"/>
-      <c r="BJ27" s="31"/>
-      <c r="BK27" s="31"/>
-      <c r="BL27" s="31"/>
-      <c r="BM27" s="31"/>
-      <c r="BN27" s="31"/>
-      <c r="BO27" s="31"/>
-      <c r="BP27" s="31"/>
-      <c r="BQ27" s="31"/>
-      <c r="BR27" s="31"/>
-      <c r="BS27" s="31"/>
-      <c r="BT27" s="31"/>
-      <c r="BU27" s="31"/>
-      <c r="BV27" s="31"/>
-      <c r="BW27" s="31"/>
-      <c r="BX27" s="31"/>
-      <c r="BY27" s="31"/>
-      <c r="BZ27" s="31"/>
-      <c r="CA27" s="31"/>
-      <c r="CB27" s="31"/>
-      <c r="CC27" s="31"/>
-      <c r="CD27" s="31"/>
-      <c r="CE27" s="32"/>
-      <c r="CF27" s="33"/>
-      <c r="CG27" s="33"/>
-      <c r="CH27" s="33"/>
-      <c r="CI27" s="33"/>
-      <c r="CJ27" s="33"/>
-      <c r="CK27" s="33"/>
-      <c r="CL27" s="33"/>
-      <c r="CM27" s="33"/>
-      <c r="CN27" s="33"/>
-      <c r="CO27" s="33"/>
-      <c r="CP27" s="33"/>
-      <c r="CQ27" s="33"/>
-      <c r="CR27" s="33"/>
-      <c r="CS27" s="33"/>
-      <c r="CT27" s="33"/>
-      <c r="CU27" s="33"/>
-      <c r="CV27" s="33"/>
-      <c r="CW27" s="33"/>
-      <c r="CX27" s="33"/>
-      <c r="CY27" s="33"/>
-      <c r="CZ27" s="33"/>
-      <c r="DA27" s="33"/>
-      <c r="DB27" s="33"/>
-      <c r="DC27" s="33"/>
-      <c r="DD27" s="33"/>
-      <c r="DE27" s="33"/>
-      <c r="DF27" s="33"/>
-      <c r="DG27" s="33"/>
-      <c r="DH27" s="33"/>
-      <c r="DI27" s="33"/>
-      <c r="DJ27" s="33"/>
-      <c r="DK27" s="33"/>
-      <c r="DL27" s="33"/>
-      <c r="DM27" s="33"/>
-      <c r="DN27" s="33"/>
-      <c r="DO27" s="33"/>
-      <c r="DP27" s="33"/>
-      <c r="DQ27" s="33"/>
-      <c r="DR27" s="33"/>
-      <c r="DS27" s="33"/>
-      <c r="DT27" s="33"/>
-      <c r="DU27" s="33"/>
-      <c r="DV27" s="33"/>
-      <c r="DW27" s="33"/>
-      <c r="DX27" s="33"/>
-      <c r="DY27" s="33"/>
-      <c r="DZ27" s="33"/>
-      <c r="EA27" s="33"/>
-      <c r="EB27" s="33"/>
-      <c r="EC27" s="33"/>
-      <c r="ED27" s="33"/>
-      <c r="EE27" s="33"/>
-      <c r="EF27" s="33"/>
-      <c r="EG27" s="33"/>
-      <c r="EH27" s="33"/>
-      <c r="EI27" s="33"/>
-      <c r="EJ27" s="33"/>
-      <c r="EK27" s="33"/>
-      <c r="EL27" s="33"/>
-      <c r="EM27" s="33"/>
-      <c r="EN27" s="33"/>
-      <c r="EO27" s="33"/>
-      <c r="EP27" s="33"/>
-      <c r="EQ27" s="33"/>
-      <c r="ER27" s="33"/>
-      <c r="ES27" s="33"/>
-      <c r="ET27" s="33"/>
-      <c r="EU27" s="33"/>
-      <c r="EV27" s="33"/>
-      <c r="EW27" s="33"/>
-      <c r="EX27" s="33"/>
-      <c r="EY27" s="33"/>
-      <c r="EZ27" s="33"/>
-      <c r="FA27" s="33"/>
-      <c r="FB27" s="33"/>
-      <c r="FC27" s="33"/>
-      <c r="FD27" s="33"/>
-      <c r="FE27" s="33"/>
-      <c r="FF27" s="33"/>
-      <c r="FG27" s="33"/>
-      <c r="FH27" s="33"/>
-      <c r="FI27" s="33"/>
+      <c r="F27" s="52"/>
+      <c r="G27" s="52"/>
+      <c r="H27" s="52"/>
+      <c r="I27" s="52"/>
+      <c r="J27" s="52"/>
+      <c r="K27" s="52"/>
+      <c r="L27" s="52"/>
+      <c r="M27" s="52"/>
+      <c r="N27" s="52"/>
+      <c r="O27" s="52"/>
+      <c r="P27" s="52"/>
+      <c r="Q27" s="52"/>
+      <c r="R27" s="52"/>
+      <c r="S27" s="52"/>
+      <c r="T27" s="52"/>
+      <c r="U27" s="52"/>
+      <c r="V27" s="52"/>
+      <c r="W27" s="52"/>
+      <c r="X27" s="52"/>
+      <c r="Y27" s="52"/>
+      <c r="Z27" s="52"/>
+      <c r="AA27" s="52"/>
+      <c r="AB27" s="52"/>
+      <c r="AC27" s="52"/>
+      <c r="AD27" s="52"/>
+      <c r="AE27" s="52"/>
+      <c r="AF27" s="52"/>
+      <c r="AG27" s="52"/>
+      <c r="AH27" s="52"/>
+      <c r="AI27" s="52"/>
+      <c r="AJ27" s="52"/>
+      <c r="AK27" s="52"/>
+      <c r="AL27" s="52"/>
+      <c r="AM27" s="52"/>
+      <c r="AN27" s="52"/>
+      <c r="AO27" s="52"/>
+      <c r="AP27" s="52"/>
+      <c r="AQ27" s="52"/>
+      <c r="AR27" s="52"/>
+      <c r="AS27" s="52"/>
+      <c r="AT27" s="52"/>
+      <c r="AU27" s="52"/>
+      <c r="AV27" s="52"/>
+      <c r="AW27" s="52"/>
+      <c r="AX27" s="52"/>
+      <c r="AY27" s="52"/>
+      <c r="AZ27" s="52"/>
+      <c r="BA27" s="52"/>
+      <c r="BB27" s="52"/>
+      <c r="BC27" s="52"/>
+      <c r="BD27" s="52"/>
+      <c r="BE27" s="52"/>
+      <c r="BF27" s="52"/>
+      <c r="BG27" s="52"/>
+      <c r="BH27" s="52"/>
+      <c r="BI27" s="52"/>
+      <c r="BJ27" s="52"/>
+      <c r="BK27" s="52"/>
+      <c r="BL27" s="52"/>
+      <c r="BM27" s="52"/>
+      <c r="BN27" s="52"/>
+      <c r="BO27" s="52"/>
+      <c r="BP27" s="52"/>
+      <c r="BQ27" s="52"/>
+      <c r="BR27" s="52"/>
+      <c r="BS27" s="52"/>
+      <c r="BT27" s="52"/>
+      <c r="BU27" s="52"/>
+      <c r="BV27" s="52"/>
+      <c r="BW27" s="52"/>
+      <c r="BX27" s="52"/>
+      <c r="BY27" s="52"/>
+      <c r="BZ27" s="52"/>
+      <c r="CA27" s="52"/>
+      <c r="CB27" s="52"/>
+      <c r="CC27" s="52"/>
+      <c r="CD27" s="52"/>
+      <c r="CE27" s="53"/>
+      <c r="CF27" s="54"/>
+      <c r="CG27" s="54"/>
+      <c r="CH27" s="54"/>
+      <c r="CI27" s="54"/>
+      <c r="CJ27" s="54"/>
+      <c r="CK27" s="54"/>
+      <c r="CL27" s="54"/>
+      <c r="CM27" s="54"/>
+      <c r="CN27" s="54"/>
+      <c r="CO27" s="54"/>
+      <c r="CP27" s="54"/>
+      <c r="CQ27" s="54"/>
+      <c r="CR27" s="54"/>
+      <c r="CS27" s="54"/>
+      <c r="CT27" s="54"/>
+      <c r="CU27" s="54"/>
+      <c r="CV27" s="54"/>
+      <c r="CW27" s="54"/>
+      <c r="CX27" s="54"/>
+      <c r="CY27" s="54"/>
+      <c r="CZ27" s="54"/>
+      <c r="DA27" s="54"/>
+      <c r="DB27" s="54"/>
+      <c r="DC27" s="54"/>
+      <c r="DD27" s="54"/>
+      <c r="DE27" s="54"/>
+      <c r="DF27" s="54"/>
+      <c r="DG27" s="54"/>
+      <c r="DH27" s="54"/>
+      <c r="DI27" s="54"/>
+      <c r="DJ27" s="54"/>
+      <c r="DK27" s="54"/>
+      <c r="DL27" s="54"/>
+      <c r="DM27" s="54"/>
+      <c r="DN27" s="54"/>
+      <c r="DO27" s="54"/>
+      <c r="DP27" s="54"/>
+      <c r="DQ27" s="54"/>
+      <c r="DR27" s="54"/>
+      <c r="DS27" s="54"/>
+      <c r="DT27" s="54"/>
+      <c r="DU27" s="54"/>
+      <c r="DV27" s="54"/>
+      <c r="DW27" s="54"/>
+      <c r="DX27" s="54"/>
+      <c r="DY27" s="54"/>
+      <c r="DZ27" s="54"/>
+      <c r="EA27" s="54"/>
+      <c r="EB27" s="54"/>
+      <c r="EC27" s="54"/>
+      <c r="ED27" s="54"/>
+      <c r="EE27" s="54"/>
+      <c r="EF27" s="54"/>
+      <c r="EG27" s="54"/>
+      <c r="EH27" s="54"/>
+      <c r="EI27" s="54"/>
+      <c r="EJ27" s="54"/>
+      <c r="EK27" s="54"/>
+      <c r="EL27" s="54"/>
+      <c r="EM27" s="54"/>
+      <c r="EN27" s="54"/>
+      <c r="EO27" s="54"/>
+      <c r="EP27" s="54"/>
+      <c r="EQ27" s="54"/>
+      <c r="ER27" s="54"/>
+      <c r="ES27" s="54"/>
+      <c r="ET27" s="54"/>
+      <c r="EU27" s="54"/>
+      <c r="EV27" s="54"/>
+      <c r="EW27" s="54"/>
+      <c r="EX27" s="54"/>
+      <c r="EY27" s="54"/>
+      <c r="EZ27" s="54"/>
+      <c r="FA27" s="54"/>
+      <c r="FB27" s="54"/>
+      <c r="FC27" s="54"/>
+      <c r="FD27" s="54"/>
+      <c r="FE27" s="54"/>
+      <c r="FF27" s="54"/>
+      <c r="FG27" s="54"/>
+      <c r="FH27" s="54"/>
+      <c r="FI27" s="54"/>
     </row>
     <row r="29" spans="1:165" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E29" s="21">
@@ -6327,81 +6327,236 @@
     </row>
   </sheetData>
   <mergeCells count="350">
-    <mergeCell ref="O1:T1"/>
-    <mergeCell ref="U1:X1"/>
-    <mergeCell ref="Y1:AC1"/>
-    <mergeCell ref="AD1:AG1"/>
-    <mergeCell ref="AH1:AM1"/>
-    <mergeCell ref="AN1:AS1"/>
-    <mergeCell ref="AT1:AW1"/>
-    <mergeCell ref="BC8:BC9"/>
-    <mergeCell ref="BD8:BD9"/>
-    <mergeCell ref="BE8:BE9"/>
-    <mergeCell ref="AN8:AN9"/>
-    <mergeCell ref="AO8:AO9"/>
-    <mergeCell ref="AP8:AP9"/>
-    <mergeCell ref="AQ8:AQ9"/>
-    <mergeCell ref="AR8:AR9"/>
-    <mergeCell ref="AS8:AS9"/>
-    <mergeCell ref="AT8:AT9"/>
-    <mergeCell ref="AU8:AU9"/>
-    <mergeCell ref="AV8:AV9"/>
-    <mergeCell ref="AE8:AE9"/>
-    <mergeCell ref="AF8:AF9"/>
-    <mergeCell ref="AG8:AG9"/>
-    <mergeCell ref="AH8:AH9"/>
-    <mergeCell ref="AI8:AI9"/>
-    <mergeCell ref="AJ8:AJ9"/>
-    <mergeCell ref="AK8:AK9"/>
-    <mergeCell ref="AL8:AL9"/>
-    <mergeCell ref="AM8:AM9"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="BO8:BO9"/>
-    <mergeCell ref="BP8:BP9"/>
-    <mergeCell ref="BQ8:BQ9"/>
-    <mergeCell ref="BR8:BR9"/>
-    <mergeCell ref="BS8:BS9"/>
-    <mergeCell ref="BT8:BT9"/>
-    <mergeCell ref="BZ8:BZ9"/>
-    <mergeCell ref="CA8:CA9"/>
-    <mergeCell ref="BH8:BH9"/>
-    <mergeCell ref="BI8:BI9"/>
-    <mergeCell ref="BJ8:BJ9"/>
-    <mergeCell ref="BK8:BK9"/>
-    <mergeCell ref="BL8:BL9"/>
-    <mergeCell ref="BM8:BM9"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AD8:AD9"/>
-    <mergeCell ref="CB8:CB9"/>
-    <mergeCell ref="CC8:CC9"/>
-    <mergeCell ref="CD8:CD9"/>
-    <mergeCell ref="CE8:CE9"/>
-    <mergeCell ref="DU8:DU9"/>
-    <mergeCell ref="EK8:EK9"/>
-    <mergeCell ref="BQ2:BQ7"/>
-    <mergeCell ref="BR2:BR7"/>
-    <mergeCell ref="BS2:BS7"/>
-    <mergeCell ref="BT2:BT7"/>
-    <mergeCell ref="BU2:BU7"/>
-    <mergeCell ref="BV2:BV7"/>
-    <mergeCell ref="ED8:ED9"/>
-    <mergeCell ref="EE8:EE9"/>
-    <mergeCell ref="DW2:DW7"/>
-    <mergeCell ref="EI8:EI9"/>
-    <mergeCell ref="EJ8:EJ9"/>
-    <mergeCell ref="CB2:CB7"/>
-    <mergeCell ref="CC2:CC7"/>
-    <mergeCell ref="CD2:CD7"/>
-    <mergeCell ref="CE2:CE7"/>
-    <mergeCell ref="DU2:DU7"/>
-    <mergeCell ref="DV2:DV7"/>
-    <mergeCell ref="DY8:DY9"/>
+    <mergeCell ref="DR8:DR9"/>
+    <mergeCell ref="DS8:DS9"/>
+    <mergeCell ref="DT8:DT9"/>
+    <mergeCell ref="DH8:DH9"/>
+    <mergeCell ref="DI8:DI9"/>
+    <mergeCell ref="DJ8:DJ9"/>
+    <mergeCell ref="DK8:DK9"/>
+    <mergeCell ref="DL8:DL9"/>
+    <mergeCell ref="DM8:DM9"/>
+    <mergeCell ref="DN8:DN9"/>
+    <mergeCell ref="DO8:DO9"/>
+    <mergeCell ref="DP8:DP9"/>
+    <mergeCell ref="DM2:DM7"/>
+    <mergeCell ref="DN2:DN7"/>
+    <mergeCell ref="DO2:DO7"/>
+    <mergeCell ref="DP2:DP7"/>
+    <mergeCell ref="DQ2:DQ7"/>
+    <mergeCell ref="DR2:DR7"/>
+    <mergeCell ref="DS2:DS7"/>
+    <mergeCell ref="DT2:DT7"/>
+    <mergeCell ref="CF8:CF9"/>
+    <mergeCell ref="CG8:CG9"/>
+    <mergeCell ref="CH8:CH9"/>
+    <mergeCell ref="CI8:CI9"/>
+    <mergeCell ref="CJ8:CJ9"/>
+    <mergeCell ref="CK8:CK9"/>
+    <mergeCell ref="CL8:CL9"/>
+    <mergeCell ref="CM8:CM9"/>
+    <mergeCell ref="CN8:CN9"/>
+    <mergeCell ref="CO8:CO9"/>
+    <mergeCell ref="CP8:CP9"/>
+    <mergeCell ref="CQ8:CQ9"/>
+    <mergeCell ref="CR8:CR9"/>
+    <mergeCell ref="CS8:CS9"/>
+    <mergeCell ref="CT8:CT9"/>
+    <mergeCell ref="CU8:CU9"/>
+    <mergeCell ref="DD2:DD7"/>
+    <mergeCell ref="DE2:DE7"/>
+    <mergeCell ref="DF2:DF7"/>
+    <mergeCell ref="DG2:DG7"/>
+    <mergeCell ref="DH2:DH7"/>
+    <mergeCell ref="DI2:DI7"/>
+    <mergeCell ref="DJ2:DJ7"/>
+    <mergeCell ref="DK2:DK7"/>
+    <mergeCell ref="DL2:DL7"/>
+    <mergeCell ref="CU2:CU7"/>
+    <mergeCell ref="CV2:CV7"/>
+    <mergeCell ref="CW2:CW7"/>
+    <mergeCell ref="CX2:CX7"/>
+    <mergeCell ref="CY2:CY7"/>
+    <mergeCell ref="CZ2:CZ7"/>
+    <mergeCell ref="DA2:DA7"/>
+    <mergeCell ref="DB2:DB7"/>
+    <mergeCell ref="DC2:DC7"/>
+    <mergeCell ref="U2:U7"/>
+    <mergeCell ref="V2:V7"/>
+    <mergeCell ref="CF2:CF7"/>
+    <mergeCell ref="CG2:CG7"/>
+    <mergeCell ref="CH2:CH7"/>
+    <mergeCell ref="CI2:CI7"/>
+    <mergeCell ref="CJ2:CJ7"/>
+    <mergeCell ref="CK2:CK7"/>
+    <mergeCell ref="CL2:CL7"/>
+    <mergeCell ref="FF2:FF7"/>
+    <mergeCell ref="FG2:FG7"/>
+    <mergeCell ref="FH2:FH7"/>
+    <mergeCell ref="FI2:FI7"/>
+    <mergeCell ref="EM2:EM7"/>
+    <mergeCell ref="EN2:EN7"/>
+    <mergeCell ref="EP2:EP7"/>
+    <mergeCell ref="EQ2:EQ7"/>
+    <mergeCell ref="ER2:ER7"/>
+    <mergeCell ref="ES2:ES7"/>
+    <mergeCell ref="ET2:ET7"/>
+    <mergeCell ref="EO2:EO7"/>
+    <mergeCell ref="FC2:FC7"/>
+    <mergeCell ref="FD2:FD7"/>
+    <mergeCell ref="FE2:FE7"/>
+    <mergeCell ref="EV2:EV7"/>
+    <mergeCell ref="EW2:EW7"/>
+    <mergeCell ref="EX2:EX7"/>
+    <mergeCell ref="EY2:EY7"/>
+    <mergeCell ref="EZ2:EZ7"/>
+    <mergeCell ref="W2:W7"/>
+    <mergeCell ref="F27:S27"/>
+    <mergeCell ref="T27:AW27"/>
+    <mergeCell ref="AX27:CD27"/>
+    <mergeCell ref="CE27:FI27"/>
+    <mergeCell ref="EV8:EV9"/>
+    <mergeCell ref="EW8:EW9"/>
+    <mergeCell ref="EX8:EX9"/>
+    <mergeCell ref="EY8:EY9"/>
+    <mergeCell ref="EZ8:EZ9"/>
+    <mergeCell ref="FA8:FA9"/>
+    <mergeCell ref="FB8:FB9"/>
+    <mergeCell ref="FC8:FC9"/>
+    <mergeCell ref="FD8:FD9"/>
+    <mergeCell ref="FE8:FE9"/>
+    <mergeCell ref="EP8:EP9"/>
+    <mergeCell ref="EQ8:EQ9"/>
+    <mergeCell ref="ER8:ER9"/>
+    <mergeCell ref="ES8:ES9"/>
+    <mergeCell ref="ET8:ET9"/>
+    <mergeCell ref="EF8:EF9"/>
+    <mergeCell ref="EG8:EG9"/>
+    <mergeCell ref="EH8:EH9"/>
+    <mergeCell ref="BN8:BN9"/>
+    <mergeCell ref="FA2:FA7"/>
+    <mergeCell ref="FB2:FB7"/>
+    <mergeCell ref="EU2:EU7"/>
+    <mergeCell ref="BD2:BD7"/>
+    <mergeCell ref="BE2:BE7"/>
+    <mergeCell ref="BF2:BF7"/>
+    <mergeCell ref="BG2:BG7"/>
+    <mergeCell ref="BM2:BM7"/>
+    <mergeCell ref="BN2:BN7"/>
+    <mergeCell ref="BO2:BO7"/>
+    <mergeCell ref="BP2:BP7"/>
+    <mergeCell ref="CA2:CA7"/>
+    <mergeCell ref="BW2:BW7"/>
+    <mergeCell ref="BX2:BX7"/>
+    <mergeCell ref="BY2:BY7"/>
+    <mergeCell ref="BZ2:BZ7"/>
+    <mergeCell ref="BH2:BH7"/>
+    <mergeCell ref="BI2:BI7"/>
+    <mergeCell ref="BJ2:BJ7"/>
+    <mergeCell ref="CM2:CM7"/>
+    <mergeCell ref="CN2:CN7"/>
+    <mergeCell ref="CO2:CO7"/>
+    <mergeCell ref="CP2:CP7"/>
+    <mergeCell ref="CQ2:CQ7"/>
+    <mergeCell ref="BL2:BL7"/>
+    <mergeCell ref="BA2:BA7"/>
+    <mergeCell ref="BB2:BB7"/>
+    <mergeCell ref="BC2:BC7"/>
+    <mergeCell ref="AP2:AP7"/>
+    <mergeCell ref="AQ2:AQ7"/>
+    <mergeCell ref="AR2:AR7"/>
+    <mergeCell ref="AS2:AS7"/>
+    <mergeCell ref="AT2:AT7"/>
+    <mergeCell ref="AU2:AU7"/>
+    <mergeCell ref="AV2:AV7"/>
+    <mergeCell ref="AW2:AW7"/>
+    <mergeCell ref="EL2:EL7"/>
+    <mergeCell ref="EJ2:EJ7"/>
+    <mergeCell ref="EK2:EK7"/>
+    <mergeCell ref="EF2:EF7"/>
+    <mergeCell ref="EG2:EG7"/>
+    <mergeCell ref="EH2:EH7"/>
+    <mergeCell ref="EI2:EI7"/>
+    <mergeCell ref="DX2:DX7"/>
+    <mergeCell ref="DY2:DY7"/>
+    <mergeCell ref="DZ2:DZ7"/>
+    <mergeCell ref="EA2:EA7"/>
+    <mergeCell ref="EB2:EB7"/>
+    <mergeCell ref="EC2:EC7"/>
+    <mergeCell ref="ED2:ED7"/>
+    <mergeCell ref="EE2:EE7"/>
+    <mergeCell ref="T2:T7"/>
+    <mergeCell ref="EC8:EC9"/>
+    <mergeCell ref="Y2:Y7"/>
+    <mergeCell ref="Z2:Z7"/>
+    <mergeCell ref="AA2:AA7"/>
+    <mergeCell ref="AB2:AB7"/>
+    <mergeCell ref="AC2:AC7"/>
+    <mergeCell ref="AD2:AD7"/>
+    <mergeCell ref="AE2:AE7"/>
+    <mergeCell ref="AH2:AH7"/>
+    <mergeCell ref="AI2:AI7"/>
+    <mergeCell ref="AJ2:AJ7"/>
+    <mergeCell ref="AK2:AK7"/>
+    <mergeCell ref="AL2:AL7"/>
+    <mergeCell ref="AM2:AM7"/>
+    <mergeCell ref="AN2:AN7"/>
+    <mergeCell ref="AO2:AO7"/>
+    <mergeCell ref="AG2:AG7"/>
+    <mergeCell ref="BK2:BK7"/>
+    <mergeCell ref="X2:X7"/>
+    <mergeCell ref="AF2:AF7"/>
+    <mergeCell ref="AX2:AX7"/>
+    <mergeCell ref="AY2:AY7"/>
+    <mergeCell ref="AZ2:AZ7"/>
+    <mergeCell ref="M2:M7"/>
+    <mergeCell ref="F1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="N2:N7"/>
+    <mergeCell ref="O2:O7"/>
+    <mergeCell ref="P2:P7"/>
+    <mergeCell ref="Q2:Q7"/>
+    <mergeCell ref="R2:R7"/>
+    <mergeCell ref="S2:S7"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="F2:F7"/>
+    <mergeCell ref="G2:G7"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="I2:I7"/>
+    <mergeCell ref="J2:J7"/>
+    <mergeCell ref="K2:K7"/>
+    <mergeCell ref="L2:L7"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:U9"/>
     <mergeCell ref="E26:FI26"/>
     <mergeCell ref="EU8:EU9"/>
     <mergeCell ref="FF8:FF9"/>
@@ -6426,232 +6581,41 @@
     <mergeCell ref="AZ8:AZ9"/>
     <mergeCell ref="BA8:BA9"/>
     <mergeCell ref="BB8:BB9"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="E2:E7"/>
-    <mergeCell ref="F2:F7"/>
-    <mergeCell ref="G2:G7"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="I2:I7"/>
-    <mergeCell ref="J2:J7"/>
-    <mergeCell ref="K2:K7"/>
-    <mergeCell ref="L2:L7"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="M2:M7"/>
-    <mergeCell ref="F1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="N2:N7"/>
-    <mergeCell ref="O2:O7"/>
-    <mergeCell ref="P2:P7"/>
-    <mergeCell ref="Q2:Q7"/>
-    <mergeCell ref="R2:R7"/>
-    <mergeCell ref="S2:S7"/>
-    <mergeCell ref="T2:T7"/>
-    <mergeCell ref="EC8:EC9"/>
-    <mergeCell ref="Y2:Y7"/>
-    <mergeCell ref="Z2:Z7"/>
-    <mergeCell ref="AA2:AA7"/>
-    <mergeCell ref="AB2:AB7"/>
-    <mergeCell ref="AC2:AC7"/>
-    <mergeCell ref="AD2:AD7"/>
-    <mergeCell ref="AE2:AE7"/>
-    <mergeCell ref="AH2:AH7"/>
-    <mergeCell ref="AI2:AI7"/>
-    <mergeCell ref="AJ2:AJ7"/>
-    <mergeCell ref="AK2:AK7"/>
-    <mergeCell ref="AL2:AL7"/>
-    <mergeCell ref="AM2:AM7"/>
-    <mergeCell ref="AN2:AN7"/>
-    <mergeCell ref="AO2:AO7"/>
-    <mergeCell ref="AG2:AG7"/>
-    <mergeCell ref="EL2:EL7"/>
-    <mergeCell ref="EJ2:EJ7"/>
-    <mergeCell ref="EK2:EK7"/>
-    <mergeCell ref="EF2:EF7"/>
-    <mergeCell ref="EG2:EG7"/>
-    <mergeCell ref="EH2:EH7"/>
-    <mergeCell ref="EI2:EI7"/>
-    <mergeCell ref="DX2:DX7"/>
-    <mergeCell ref="DY2:DY7"/>
-    <mergeCell ref="DZ2:DZ7"/>
-    <mergeCell ref="EA2:EA7"/>
-    <mergeCell ref="EB2:EB7"/>
-    <mergeCell ref="EC2:EC7"/>
-    <mergeCell ref="ED2:ED7"/>
-    <mergeCell ref="EE2:EE7"/>
-    <mergeCell ref="BK2:BK7"/>
-    <mergeCell ref="X2:X7"/>
-    <mergeCell ref="AF2:AF7"/>
-    <mergeCell ref="AX2:AX7"/>
-    <mergeCell ref="AY2:AY7"/>
-    <mergeCell ref="AZ2:AZ7"/>
-    <mergeCell ref="BL2:BL7"/>
-    <mergeCell ref="BA2:BA7"/>
-    <mergeCell ref="BB2:BB7"/>
-    <mergeCell ref="BC2:BC7"/>
-    <mergeCell ref="AP2:AP7"/>
-    <mergeCell ref="AQ2:AQ7"/>
-    <mergeCell ref="AR2:AR7"/>
-    <mergeCell ref="AS2:AS7"/>
-    <mergeCell ref="AT2:AT7"/>
-    <mergeCell ref="AU2:AU7"/>
-    <mergeCell ref="AV2:AV7"/>
-    <mergeCell ref="AW2:AW7"/>
+    <mergeCell ref="BQ2:BQ7"/>
+    <mergeCell ref="BR2:BR7"/>
+    <mergeCell ref="BS2:BS7"/>
+    <mergeCell ref="BT2:BT7"/>
+    <mergeCell ref="BU2:BU7"/>
+    <mergeCell ref="BV2:BV7"/>
+    <mergeCell ref="ED8:ED9"/>
+    <mergeCell ref="EE8:EE9"/>
+    <mergeCell ref="DW2:DW7"/>
+    <mergeCell ref="CB2:CB7"/>
+    <mergeCell ref="CC2:CC7"/>
+    <mergeCell ref="CD2:CD7"/>
+    <mergeCell ref="CE2:CE7"/>
+    <mergeCell ref="DU2:DU7"/>
+    <mergeCell ref="DV2:DV7"/>
+    <mergeCell ref="DY8:DY9"/>
     <mergeCell ref="DX8:DX9"/>
     <mergeCell ref="DZ8:DZ9"/>
     <mergeCell ref="EA8:EA9"/>
     <mergeCell ref="BX8:BX9"/>
     <mergeCell ref="BY8:BY9"/>
-    <mergeCell ref="FA2:FA7"/>
-    <mergeCell ref="FB2:FB7"/>
-    <mergeCell ref="EU2:EU7"/>
-    <mergeCell ref="BD2:BD7"/>
-    <mergeCell ref="BE2:BE7"/>
-    <mergeCell ref="BF2:BF7"/>
-    <mergeCell ref="BG2:BG7"/>
-    <mergeCell ref="BM2:BM7"/>
-    <mergeCell ref="BN2:BN7"/>
-    <mergeCell ref="BO2:BO7"/>
-    <mergeCell ref="BP2:BP7"/>
-    <mergeCell ref="CA2:CA7"/>
-    <mergeCell ref="BW2:BW7"/>
-    <mergeCell ref="BX2:BX7"/>
-    <mergeCell ref="BY2:BY7"/>
-    <mergeCell ref="BZ2:BZ7"/>
-    <mergeCell ref="BH2:BH7"/>
-    <mergeCell ref="BI2:BI7"/>
-    <mergeCell ref="BJ2:BJ7"/>
-    <mergeCell ref="W2:W7"/>
-    <mergeCell ref="F27:S27"/>
-    <mergeCell ref="T27:AW27"/>
-    <mergeCell ref="AX27:CD27"/>
-    <mergeCell ref="CE27:FI27"/>
-    <mergeCell ref="EV8:EV9"/>
-    <mergeCell ref="EW8:EW9"/>
-    <mergeCell ref="EX8:EX9"/>
-    <mergeCell ref="EY8:EY9"/>
-    <mergeCell ref="EZ8:EZ9"/>
-    <mergeCell ref="FA8:FA9"/>
-    <mergeCell ref="FB8:FB9"/>
-    <mergeCell ref="FC8:FC9"/>
-    <mergeCell ref="FD8:FD9"/>
-    <mergeCell ref="FE8:FE9"/>
-    <mergeCell ref="EP8:EP9"/>
-    <mergeCell ref="EQ8:EQ9"/>
-    <mergeCell ref="ER8:ER9"/>
-    <mergeCell ref="ES8:ES9"/>
-    <mergeCell ref="ET8:ET9"/>
-    <mergeCell ref="EF8:EF9"/>
-    <mergeCell ref="EG8:EG9"/>
-    <mergeCell ref="EH8:EH9"/>
-    <mergeCell ref="BN8:BN9"/>
-    <mergeCell ref="FF2:FF7"/>
-    <mergeCell ref="FG2:FG7"/>
-    <mergeCell ref="FH2:FH7"/>
-    <mergeCell ref="FI2:FI7"/>
-    <mergeCell ref="EM2:EM7"/>
-    <mergeCell ref="EN2:EN7"/>
-    <mergeCell ref="EP2:EP7"/>
-    <mergeCell ref="EQ2:EQ7"/>
-    <mergeCell ref="ER2:ER7"/>
-    <mergeCell ref="ES2:ES7"/>
-    <mergeCell ref="ET2:ET7"/>
-    <mergeCell ref="EO2:EO7"/>
-    <mergeCell ref="FC2:FC7"/>
-    <mergeCell ref="FD2:FD7"/>
-    <mergeCell ref="FE2:FE7"/>
-    <mergeCell ref="EV2:EV7"/>
-    <mergeCell ref="EW2:EW7"/>
-    <mergeCell ref="EX2:EX7"/>
-    <mergeCell ref="EY2:EY7"/>
-    <mergeCell ref="EZ2:EZ7"/>
-    <mergeCell ref="U2:U7"/>
-    <mergeCell ref="V2:V7"/>
-    <mergeCell ref="CF2:CF7"/>
-    <mergeCell ref="CG2:CG7"/>
-    <mergeCell ref="CH2:CH7"/>
-    <mergeCell ref="CI2:CI7"/>
-    <mergeCell ref="CJ2:CJ7"/>
-    <mergeCell ref="CK2:CK7"/>
-    <mergeCell ref="CL2:CL7"/>
-    <mergeCell ref="CM2:CM7"/>
-    <mergeCell ref="CN2:CN7"/>
-    <mergeCell ref="CO2:CO7"/>
-    <mergeCell ref="CP2:CP7"/>
-    <mergeCell ref="CQ2:CQ7"/>
     <mergeCell ref="CR2:CR7"/>
     <mergeCell ref="CS2:CS7"/>
     <mergeCell ref="CT2:CT7"/>
-    <mergeCell ref="CU2:CU7"/>
-    <mergeCell ref="CV2:CV7"/>
-    <mergeCell ref="CW2:CW7"/>
-    <mergeCell ref="CX2:CX7"/>
-    <mergeCell ref="CY2:CY7"/>
-    <mergeCell ref="CZ2:CZ7"/>
-    <mergeCell ref="DA2:DA7"/>
-    <mergeCell ref="DB2:DB7"/>
-    <mergeCell ref="DC2:DC7"/>
-    <mergeCell ref="DD2:DD7"/>
-    <mergeCell ref="DE2:DE7"/>
-    <mergeCell ref="DF2:DF7"/>
-    <mergeCell ref="DG2:DG7"/>
-    <mergeCell ref="DH2:DH7"/>
-    <mergeCell ref="DI2:DI7"/>
-    <mergeCell ref="DJ2:DJ7"/>
-    <mergeCell ref="DK2:DK7"/>
-    <mergeCell ref="DL2:DL7"/>
-    <mergeCell ref="DM2:DM7"/>
-    <mergeCell ref="DN2:DN7"/>
-    <mergeCell ref="DO2:DO7"/>
-    <mergeCell ref="DP2:DP7"/>
-    <mergeCell ref="DQ2:DQ7"/>
-    <mergeCell ref="DR2:DR7"/>
-    <mergeCell ref="DS2:DS7"/>
-    <mergeCell ref="DT2:DT7"/>
-    <mergeCell ref="CF8:CF9"/>
-    <mergeCell ref="CG8:CG9"/>
-    <mergeCell ref="CH8:CH9"/>
-    <mergeCell ref="CI8:CI9"/>
-    <mergeCell ref="CJ8:CJ9"/>
-    <mergeCell ref="CK8:CK9"/>
-    <mergeCell ref="CL8:CL9"/>
-    <mergeCell ref="CM8:CM9"/>
-    <mergeCell ref="CN8:CN9"/>
-    <mergeCell ref="CO8:CO9"/>
-    <mergeCell ref="CP8:CP9"/>
-    <mergeCell ref="CQ8:CQ9"/>
-    <mergeCell ref="CR8:CR9"/>
-    <mergeCell ref="CS8:CS9"/>
-    <mergeCell ref="CT8:CT9"/>
-    <mergeCell ref="CU8:CU9"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AD8:AD9"/>
+    <mergeCell ref="CB8:CB9"/>
+    <mergeCell ref="CC8:CC9"/>
+    <mergeCell ref="CD8:CD9"/>
+    <mergeCell ref="CE8:CE9"/>
+    <mergeCell ref="DU8:DU9"/>
+    <mergeCell ref="EK8:EK9"/>
+    <mergeCell ref="EI8:EI9"/>
+    <mergeCell ref="EJ8:EJ9"/>
     <mergeCell ref="CV8:CV9"/>
     <mergeCell ref="CW8:CW9"/>
     <mergeCell ref="CX8:CX9"/>
@@ -6665,18 +6629,54 @@
     <mergeCell ref="DF8:DF9"/>
     <mergeCell ref="DG8:DG9"/>
     <mergeCell ref="DQ8:DQ9"/>
-    <mergeCell ref="DR8:DR9"/>
-    <mergeCell ref="DS8:DS9"/>
-    <mergeCell ref="DT8:DT9"/>
-    <mergeCell ref="DH8:DH9"/>
-    <mergeCell ref="DI8:DI9"/>
-    <mergeCell ref="DJ8:DJ9"/>
-    <mergeCell ref="DK8:DK9"/>
-    <mergeCell ref="DL8:DL9"/>
-    <mergeCell ref="DM8:DM9"/>
-    <mergeCell ref="DN8:DN9"/>
-    <mergeCell ref="DO8:DO9"/>
-    <mergeCell ref="DP8:DP9"/>
+    <mergeCell ref="BO8:BO9"/>
+    <mergeCell ref="BP8:BP9"/>
+    <mergeCell ref="BQ8:BQ9"/>
+    <mergeCell ref="BR8:BR9"/>
+    <mergeCell ref="BS8:BS9"/>
+    <mergeCell ref="BT8:BT9"/>
+    <mergeCell ref="BZ8:BZ9"/>
+    <mergeCell ref="CA8:CA9"/>
+    <mergeCell ref="BH8:BH9"/>
+    <mergeCell ref="BI8:BI9"/>
+    <mergeCell ref="BJ8:BJ9"/>
+    <mergeCell ref="BK8:BK9"/>
+    <mergeCell ref="BL8:BL9"/>
+    <mergeCell ref="BM8:BM9"/>
+    <mergeCell ref="BE8:BE9"/>
+    <mergeCell ref="AN8:AN9"/>
+    <mergeCell ref="AO8:AO9"/>
+    <mergeCell ref="AP8:AP9"/>
+    <mergeCell ref="AQ8:AQ9"/>
+    <mergeCell ref="AR8:AR9"/>
+    <mergeCell ref="AS8:AS9"/>
+    <mergeCell ref="AT8:AT9"/>
+    <mergeCell ref="AU8:AU9"/>
+    <mergeCell ref="AV8:AV9"/>
+    <mergeCell ref="O1:T1"/>
+    <mergeCell ref="U1:X1"/>
+    <mergeCell ref="Y1:AC1"/>
+    <mergeCell ref="AD1:AG1"/>
+    <mergeCell ref="AH1:AM1"/>
+    <mergeCell ref="AN1:AS1"/>
+    <mergeCell ref="AT1:AW1"/>
+    <mergeCell ref="BC8:BC9"/>
+    <mergeCell ref="BD8:BD9"/>
+    <mergeCell ref="AE8:AE9"/>
+    <mergeCell ref="AF8:AF9"/>
+    <mergeCell ref="AG8:AG9"/>
+    <mergeCell ref="AH8:AH9"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="AJ8:AJ9"/>
+    <mergeCell ref="AK8:AK9"/>
+    <mergeCell ref="AL8:AL9"/>
+    <mergeCell ref="AM8:AM9"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="W8:W9"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="AA8:AA9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -6709,7 +6709,7 @@
       <c r="H2" s="56"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="35" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="58" t="s">
@@ -6733,7 +6733,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="43"/>
+      <c r="A4" s="35"/>
       <c r="B4" s="60"/>
       <c r="C4" s="61"/>
       <c r="D4" s="63"/>

--- a/Journals/Front-end journal/Markup ჟურნალი.xlsx
+++ b/Journals/Front-end journal/Markup ჟურნალი.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\411\Desktop\12-2024 - web\Mermisi-main\Journals\Front-end journal\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\411\Desktop\12-2024 - web\0 -Mermisi-main\Journals\Front-end journal\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15360" windowHeight="7755"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
   </bookViews>
   <sheets>
     <sheet name="html&amp;css" sheetId="1" r:id="rId1"/>
@@ -109,9 +109,6 @@
     <t>გავაცდინე ეს საათი</t>
   </si>
   <si>
-    <t>წინა მასწავლებელმა ჩაატარა</t>
-  </si>
-  <si>
     <t>მარტი</t>
   </si>
   <si>
@@ -140,6 +137,9 @@
   </si>
   <si>
     <t>ვებტექნოლოგიები,  ჯგუფი: 09-2026</t>
+  </si>
+  <si>
+    <t>თვის დასასრული</t>
   </si>
 </sst>
 </file>
@@ -262,12 +262,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -287,6 +281,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -473,7 +473,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -511,19 +511,39 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="10" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -532,39 +552,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -594,7 +581,16 @@
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -608,14 +604,17 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -644,6 +643,13 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="2" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -878,1973 +884,2033 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:166" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="40"/>
-      <c r="F1" s="24">
+      <c r="A1" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="35"/>
+      <c r="F1" s="30">
         <v>5</v>
       </c>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="24">
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="30">
         <v>4</v>
       </c>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="24">
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="30">
         <v>6</v>
       </c>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
-      <c r="R1" s="25"/>
-      <c r="S1" s="25"/>
-      <c r="T1" s="26"/>
-      <c r="U1" s="24">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="31"/>
+      <c r="R1" s="31"/>
+      <c r="S1" s="31"/>
+      <c r="T1" s="32"/>
+      <c r="U1" s="30">
         <v>4</v>
       </c>
-      <c r="V1" s="25"/>
-      <c r="W1" s="25"/>
-      <c r="X1" s="26"/>
-      <c r="Y1" s="24">
+      <c r="V1" s="31"/>
+      <c r="W1" s="31"/>
+      <c r="X1" s="32"/>
+      <c r="Y1" s="30">
         <v>5</v>
       </c>
-      <c r="Z1" s="25"/>
-      <c r="AA1" s="25"/>
-      <c r="AB1" s="25"/>
-      <c r="AC1" s="26"/>
-      <c r="AD1" s="24">
+      <c r="Z1" s="31"/>
+      <c r="AA1" s="31"/>
+      <c r="AB1" s="31"/>
+      <c r="AC1" s="32"/>
+      <c r="AD1" s="30">
         <v>4</v>
       </c>
-      <c r="AE1" s="25"/>
-      <c r="AF1" s="25"/>
-      <c r="AG1" s="26"/>
-      <c r="AH1" s="24">
+      <c r="AE1" s="31"/>
+      <c r="AF1" s="31"/>
+      <c r="AG1" s="32"/>
+      <c r="AH1" s="30">
         <v>6</v>
       </c>
-      <c r="AI1" s="25"/>
-      <c r="AJ1" s="25"/>
-      <c r="AK1" s="25"/>
-      <c r="AL1" s="25"/>
-      <c r="AM1" s="26"/>
-      <c r="AN1" s="24">
+      <c r="AI1" s="31"/>
+      <c r="AJ1" s="31"/>
+      <c r="AK1" s="31"/>
+      <c r="AL1" s="31"/>
+      <c r="AM1" s="32"/>
+      <c r="AN1" s="30">
         <v>6</v>
       </c>
-      <c r="AO1" s="25"/>
-      <c r="AP1" s="25"/>
-      <c r="AQ1" s="25"/>
-      <c r="AR1" s="25"/>
-      <c r="AS1" s="26"/>
-      <c r="AT1" s="24">
+      <c r="AO1" s="31"/>
+      <c r="AP1" s="31"/>
+      <c r="AQ1" s="31"/>
+      <c r="AR1" s="31"/>
+      <c r="AS1" s="32"/>
+      <c r="AT1" s="30">
         <v>4</v>
       </c>
-      <c r="AU1" s="25"/>
-      <c r="AV1" s="25"/>
-      <c r="AW1" s="26"/>
-      <c r="AX1" s="22"/>
-      <c r="AY1" s="22"/>
-      <c r="AZ1" s="22"/>
-      <c r="BA1" s="22"/>
-      <c r="BB1" s="22"/>
-      <c r="BC1" s="22"/>
-      <c r="BD1" s="22"/>
-      <c r="BE1" s="22"/>
-      <c r="BF1" s="22"/>
-      <c r="BG1" s="22"/>
-      <c r="BH1" s="22"/>
-      <c r="BI1" s="22"/>
-      <c r="BJ1" s="22"/>
-      <c r="BK1" s="22"/>
-      <c r="BL1" s="22"/>
-      <c r="BM1" s="22"/>
-      <c r="BN1" s="22"/>
-      <c r="BO1" s="22"/>
-      <c r="BP1" s="22"/>
-      <c r="BQ1" s="22"/>
-      <c r="BR1" s="22"/>
-      <c r="BS1" s="22"/>
-      <c r="BT1" s="22"/>
-      <c r="BU1" s="22"/>
-      <c r="BV1" s="22"/>
-      <c r="BW1" s="22"/>
-      <c r="BX1" s="22"/>
-      <c r="BY1" s="22"/>
-      <c r="BZ1" s="22"/>
-      <c r="CA1" s="22"/>
-      <c r="CB1" s="22"/>
-      <c r="CC1" s="22"/>
-      <c r="CD1" s="22"/>
-      <c r="CE1" s="22"/>
-      <c r="CF1" s="22"/>
-      <c r="CG1" s="22"/>
-      <c r="CH1" s="22"/>
-      <c r="CI1" s="22"/>
-      <c r="CJ1" s="22"/>
-      <c r="CK1" s="22"/>
-      <c r="CL1" s="22"/>
-      <c r="CM1" s="22"/>
-      <c r="CN1" s="22"/>
-      <c r="CO1" s="22"/>
-      <c r="CP1" s="22"/>
-      <c r="CQ1" s="22"/>
-      <c r="CR1" s="22"/>
-      <c r="CS1" s="22"/>
-      <c r="CT1" s="22"/>
-      <c r="CU1" s="22"/>
-      <c r="CV1" s="22"/>
-      <c r="CW1" s="22"/>
-      <c r="CX1" s="22"/>
-      <c r="CY1" s="22"/>
-      <c r="CZ1" s="22"/>
-      <c r="DA1" s="22"/>
-      <c r="DB1" s="22"/>
-      <c r="DC1" s="22"/>
-      <c r="DD1" s="22"/>
-      <c r="DE1" s="22"/>
-      <c r="DF1" s="22"/>
-      <c r="DG1" s="22"/>
-      <c r="DH1" s="22"/>
-      <c r="DI1" s="22"/>
-      <c r="DJ1" s="22"/>
-      <c r="DK1" s="22"/>
-      <c r="DL1" s="22"/>
-      <c r="DM1" s="22"/>
-      <c r="DN1" s="22"/>
-      <c r="DO1" s="22"/>
-      <c r="DP1" s="22"/>
-      <c r="DQ1" s="22"/>
-      <c r="DR1" s="22"/>
-      <c r="DS1" s="22"/>
-      <c r="DT1" s="22"/>
-      <c r="DU1" s="22"/>
-      <c r="DV1" s="22"/>
-      <c r="DW1" s="22"/>
-      <c r="DX1" s="22"/>
-      <c r="DY1" s="22"/>
-      <c r="DZ1" s="22"/>
-      <c r="EA1" s="22"/>
-      <c r="EB1" s="22"/>
-      <c r="EC1" s="22"/>
-      <c r="ED1" s="22"/>
-      <c r="EE1" s="22"/>
-      <c r="EF1" s="22"/>
-      <c r="EG1" s="22"/>
-      <c r="EH1" s="22"/>
-      <c r="EI1" s="22"/>
-      <c r="EJ1" s="22"/>
-      <c r="EK1" s="22"/>
-      <c r="EL1" s="22"/>
-      <c r="EM1" s="22"/>
-      <c r="EN1" s="22"/>
-      <c r="EO1" s="22"/>
-      <c r="EP1" s="22"/>
-      <c r="EQ1" s="22"/>
-      <c r="ER1" s="22"/>
-      <c r="ES1" s="22"/>
-      <c r="ET1" s="22"/>
-      <c r="EU1" s="22"/>
-      <c r="EV1" s="22"/>
-      <c r="EW1" s="22"/>
-      <c r="EX1" s="23"/>
-      <c r="EY1" s="23"/>
-      <c r="EZ1" s="23"/>
-      <c r="FA1" s="23"/>
-      <c r="FB1" s="23"/>
-      <c r="FC1" s="23"/>
-      <c r="FD1" s="23"/>
-      <c r="FE1" s="23"/>
-      <c r="FF1" s="23"/>
-      <c r="FG1" s="23"/>
-      <c r="FH1" s="23"/>
-      <c r="FI1" s="23"/>
+      <c r="AU1" s="31"/>
+      <c r="AV1" s="31"/>
+      <c r="AW1" s="32"/>
+      <c r="AX1" s="30">
+        <v>3</v>
+      </c>
+      <c r="AY1" s="31"/>
+      <c r="AZ1" s="32"/>
+      <c r="BA1" s="30">
+        <v>4</v>
+      </c>
+      <c r="BB1" s="31"/>
+      <c r="BC1" s="31"/>
+      <c r="BD1" s="32"/>
+      <c r="BE1" s="30">
+        <v>6</v>
+      </c>
+      <c r="BF1" s="31"/>
+      <c r="BG1" s="31"/>
+      <c r="BH1" s="31"/>
+      <c r="BI1" s="31"/>
+      <c r="BJ1" s="32"/>
+      <c r="BK1" s="30">
+        <v>6</v>
+      </c>
+      <c r="BL1" s="31"/>
+      <c r="BM1" s="31"/>
+      <c r="BN1" s="31"/>
+      <c r="BO1" s="31"/>
+      <c r="BP1" s="32"/>
+      <c r="BQ1" s="30">
+        <v>6</v>
+      </c>
+      <c r="BR1" s="31"/>
+      <c r="BS1" s="31"/>
+      <c r="BT1" s="31"/>
+      <c r="BU1" s="31"/>
+      <c r="BV1" s="32"/>
+      <c r="BW1" s="21"/>
+      <c r="BX1" s="21"/>
+      <c r="BY1" s="21"/>
+      <c r="BZ1" s="21"/>
+      <c r="CA1" s="21"/>
+      <c r="CB1" s="21"/>
+      <c r="CC1" s="21"/>
+      <c r="CD1" s="21"/>
+      <c r="CE1" s="21"/>
+      <c r="CF1" s="21"/>
+      <c r="CG1" s="21"/>
+      <c r="CH1" s="21"/>
+      <c r="CI1" s="21"/>
+      <c r="CJ1" s="21"/>
+      <c r="CK1" s="21"/>
+      <c r="CL1" s="21"/>
+      <c r="CM1" s="21"/>
+      <c r="CN1" s="21"/>
+      <c r="CO1" s="21"/>
+      <c r="CP1" s="21"/>
+      <c r="CQ1" s="21"/>
+      <c r="CR1" s="21"/>
+      <c r="CS1" s="21"/>
+      <c r="CT1" s="21"/>
+      <c r="CU1" s="21"/>
+      <c r="CV1" s="21"/>
+      <c r="CW1" s="21"/>
+      <c r="CX1" s="21"/>
+      <c r="CY1" s="21"/>
+      <c r="CZ1" s="21"/>
+      <c r="DA1" s="21"/>
+      <c r="DB1" s="21"/>
+      <c r="DC1" s="21"/>
+      <c r="DD1" s="21"/>
+      <c r="DE1" s="21"/>
+      <c r="DF1" s="21"/>
+      <c r="DG1" s="21"/>
+      <c r="DH1" s="21"/>
+      <c r="DI1" s="21"/>
+      <c r="DJ1" s="21"/>
+      <c r="DK1" s="21"/>
+      <c r="DL1" s="21"/>
+      <c r="DM1" s="21"/>
+      <c r="DN1" s="21"/>
+      <c r="DO1" s="21"/>
+      <c r="DP1" s="21"/>
+      <c r="DQ1" s="21"/>
+      <c r="DR1" s="21"/>
+      <c r="DS1" s="21"/>
+      <c r="DT1" s="21"/>
+      <c r="DU1" s="21"/>
+      <c r="DV1" s="21"/>
+      <c r="DW1" s="21"/>
+      <c r="DX1" s="21"/>
+      <c r="DY1" s="21"/>
+      <c r="DZ1" s="21"/>
+      <c r="EA1" s="21"/>
+      <c r="EB1" s="21"/>
+      <c r="EC1" s="21"/>
+      <c r="ED1" s="21"/>
+      <c r="EE1" s="21"/>
+      <c r="EF1" s="21"/>
+      <c r="EG1" s="21"/>
+      <c r="EH1" s="21"/>
+      <c r="EI1" s="21"/>
+      <c r="EJ1" s="21"/>
+      <c r="EK1" s="21"/>
+      <c r="EL1" s="21"/>
+      <c r="EM1" s="21"/>
+      <c r="EN1" s="21"/>
+      <c r="EO1" s="21"/>
+      <c r="EP1" s="21"/>
+      <c r="EQ1" s="21"/>
+      <c r="ER1" s="21"/>
+      <c r="ES1" s="21"/>
+      <c r="ET1" s="21"/>
+      <c r="EU1" s="21"/>
+      <c r="EV1" s="21"/>
+      <c r="EW1" s="21"/>
+      <c r="EX1" s="22"/>
+      <c r="EY1" s="22"/>
+      <c r="EZ1" s="22"/>
+      <c r="FA1" s="22"/>
+      <c r="FB1" s="22"/>
+      <c r="FC1" s="22"/>
+      <c r="FD1" s="22"/>
+      <c r="FE1" s="22"/>
+      <c r="FF1" s="22"/>
+      <c r="FG1" s="22"/>
+      <c r="FH1" s="22"/>
+      <c r="FI1" s="22"/>
       <c r="FJ1" s="1">
         <f>SUM(F1:FI1)</f>
-        <v>44</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:166" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="41"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="44" t="s">
+      <c r="A2" s="36"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="29">
+      <c r="F2" s="25">
         <v>46307</v>
       </c>
-      <c r="G2" s="29">
+      <c r="G2" s="25">
         <v>46307</v>
       </c>
-      <c r="H2" s="29">
+      <c r="H2" s="25">
         <v>46307</v>
       </c>
-      <c r="I2" s="29">
+      <c r="I2" s="25">
         <v>46307</v>
       </c>
-      <c r="J2" s="29">
+      <c r="J2" s="25">
         <v>46307</v>
       </c>
-      <c r="K2" s="29">
+      <c r="K2" s="25">
         <v>46308</v>
       </c>
-      <c r="L2" s="29">
+      <c r="L2" s="25">
         <v>46308</v>
       </c>
-      <c r="M2" s="29">
+      <c r="M2" s="25">
         <v>46308</v>
       </c>
-      <c r="N2" s="29">
+      <c r="N2" s="25">
         <v>46308</v>
       </c>
-      <c r="O2" s="29">
+      <c r="O2" s="25">
         <v>46310</v>
       </c>
-      <c r="P2" s="29">
+      <c r="P2" s="25">
         <v>46310</v>
       </c>
-      <c r="Q2" s="29">
+      <c r="Q2" s="25">
         <v>46310</v>
       </c>
-      <c r="R2" s="29">
+      <c r="R2" s="25">
         <v>46310</v>
       </c>
-      <c r="S2" s="29">
+      <c r="S2" s="25">
         <v>46310</v>
       </c>
-      <c r="T2" s="29">
+      <c r="T2" s="25">
         <v>46310</v>
       </c>
-      <c r="U2" s="29">
+      <c r="U2" s="25">
         <v>46311</v>
       </c>
-      <c r="V2" s="29">
+      <c r="V2" s="25">
         <v>46311</v>
       </c>
-      <c r="W2" s="29">
+      <c r="W2" s="25">
         <v>46311</v>
       </c>
-      <c r="X2" s="29">
+      <c r="X2" s="25">
         <v>46311</v>
       </c>
-      <c r="Y2" s="29">
+      <c r="Y2" s="25">
         <v>46314</v>
       </c>
-      <c r="Z2" s="29">
+      <c r="Z2" s="25">
         <v>46314</v>
       </c>
-      <c r="AA2" s="29">
+      <c r="AA2" s="25">
         <v>46314</v>
       </c>
-      <c r="AB2" s="29">
+      <c r="AB2" s="25">
         <v>46314</v>
       </c>
-      <c r="AC2" s="29">
+      <c r="AC2" s="25">
         <v>46314</v>
       </c>
-      <c r="AD2" s="29">
+      <c r="AD2" s="25">
         <v>46315</v>
       </c>
-      <c r="AE2" s="29">
+      <c r="AE2" s="25">
         <v>46315</v>
       </c>
-      <c r="AF2" s="29">
+      <c r="AF2" s="25">
         <v>46315</v>
       </c>
-      <c r="AG2" s="29">
+      <c r="AG2" s="25">
         <v>46315</v>
       </c>
-      <c r="AH2" s="29">
+      <c r="AH2" s="25">
         <v>46316</v>
       </c>
-      <c r="AI2" s="29">
+      <c r="AI2" s="25">
         <v>46316</v>
       </c>
-      <c r="AJ2" s="29">
+      <c r="AJ2" s="25">
         <v>46316</v>
       </c>
-      <c r="AK2" s="29">
+      <c r="AK2" s="25">
         <v>46316</v>
       </c>
-      <c r="AL2" s="29">
+      <c r="AL2" s="25">
         <v>46316</v>
       </c>
-      <c r="AM2" s="29">
+      <c r="AM2" s="25">
         <v>46316</v>
       </c>
-      <c r="AN2" s="29">
+      <c r="AN2" s="25">
         <v>46317</v>
       </c>
-      <c r="AO2" s="29">
+      <c r="AO2" s="25">
         <v>46317</v>
       </c>
-      <c r="AP2" s="29">
+      <c r="AP2" s="25">
         <v>46317</v>
       </c>
-      <c r="AQ2" s="29">
+      <c r="AQ2" s="25">
         <v>46317</v>
       </c>
-      <c r="AR2" s="29">
+      <c r="AR2" s="25">
         <v>46317</v>
       </c>
-      <c r="AS2" s="29">
+      <c r="AS2" s="25">
         <v>46317</v>
       </c>
-      <c r="AT2" s="29">
+      <c r="AT2" s="25">
         <v>46318</v>
       </c>
-      <c r="AU2" s="29">
+      <c r="AU2" s="25">
         <v>46318</v>
       </c>
-      <c r="AV2" s="29">
+      <c r="AV2" s="25">
         <v>46318</v>
       </c>
-      <c r="AW2" s="29">
+      <c r="AW2" s="25">
         <v>46318</v>
       </c>
-      <c r="AX2" s="29"/>
-      <c r="AY2" s="29"/>
-      <c r="AZ2" s="29"/>
-      <c r="BA2" s="29"/>
-      <c r="BB2" s="29"/>
-      <c r="BC2" s="29"/>
-      <c r="BD2" s="29"/>
-      <c r="BE2" s="29"/>
-      <c r="BF2" s="29"/>
-      <c r="BG2" s="29"/>
-      <c r="BH2" s="29"/>
-      <c r="BI2" s="29"/>
-      <c r="BJ2" s="29"/>
-      <c r="BK2" s="29"/>
-      <c r="BL2" s="29"/>
-      <c r="BM2" s="29"/>
-      <c r="BN2" s="29"/>
-      <c r="BO2" s="29"/>
-      <c r="BP2" s="29"/>
-      <c r="BQ2" s="29"/>
-      <c r="BR2" s="29"/>
-      <c r="BS2" s="29"/>
-      <c r="BT2" s="29"/>
-      <c r="BU2" s="29"/>
-      <c r="BV2" s="29"/>
-      <c r="BW2" s="29"/>
-      <c r="BX2" s="29"/>
-      <c r="BY2" s="29"/>
-      <c r="BZ2" s="29"/>
-      <c r="CA2" s="29"/>
-      <c r="CB2" s="29"/>
-      <c r="CC2" s="29"/>
-      <c r="CD2" s="29"/>
-      <c r="CE2" s="29"/>
-      <c r="CF2" s="29"/>
-      <c r="CG2" s="29"/>
-      <c r="CH2" s="29"/>
-      <c r="CI2" s="29"/>
-      <c r="CJ2" s="29"/>
-      <c r="CK2" s="29"/>
-      <c r="CL2" s="29"/>
-      <c r="CM2" s="29"/>
-      <c r="CN2" s="29"/>
-      <c r="CO2" s="29"/>
-      <c r="CP2" s="29"/>
-      <c r="CQ2" s="29"/>
-      <c r="CR2" s="29"/>
-      <c r="CS2" s="29"/>
-      <c r="CT2" s="29"/>
-      <c r="CU2" s="29"/>
-      <c r="CV2" s="29"/>
-      <c r="CW2" s="29"/>
-      <c r="CX2" s="29"/>
-      <c r="CY2" s="29"/>
-      <c r="CZ2" s="29"/>
-      <c r="DA2" s="29"/>
-      <c r="DB2" s="29"/>
-      <c r="DC2" s="29"/>
-      <c r="DD2" s="29"/>
-      <c r="DE2" s="29"/>
-      <c r="DF2" s="29"/>
-      <c r="DG2" s="29"/>
-      <c r="DH2" s="29"/>
-      <c r="DI2" s="29"/>
-      <c r="DJ2" s="29"/>
-      <c r="DK2" s="29"/>
-      <c r="DL2" s="29"/>
-      <c r="DM2" s="29"/>
-      <c r="DN2" s="29"/>
-      <c r="DO2" s="29"/>
-      <c r="DP2" s="29"/>
-      <c r="DQ2" s="29"/>
-      <c r="DR2" s="29"/>
-      <c r="DS2" s="29"/>
-      <c r="DT2" s="29"/>
-      <c r="DU2" s="29"/>
-      <c r="DV2" s="29"/>
-      <c r="DW2" s="29"/>
-      <c r="DX2" s="29"/>
-      <c r="DY2" s="29"/>
-      <c r="DZ2" s="29"/>
-      <c r="EA2" s="29"/>
-      <c r="EB2" s="29"/>
-      <c r="EC2" s="29"/>
-      <c r="ED2" s="29"/>
-      <c r="EE2" s="29"/>
-      <c r="EF2" s="29"/>
-      <c r="EG2" s="29"/>
-      <c r="EH2" s="29"/>
-      <c r="EI2" s="29"/>
-      <c r="EJ2" s="29"/>
-      <c r="EK2" s="29"/>
-      <c r="EL2" s="29"/>
-      <c r="EM2" s="29"/>
-      <c r="EN2" s="29"/>
-      <c r="EO2" s="29"/>
-      <c r="EP2" s="29"/>
-      <c r="EQ2" s="29"/>
-      <c r="ER2" s="29"/>
-      <c r="ES2" s="29"/>
-      <c r="ET2" s="29"/>
-      <c r="EU2" s="29"/>
-      <c r="EV2" s="29"/>
-      <c r="EW2" s="29"/>
-      <c r="EX2" s="29"/>
-      <c r="EY2" s="29"/>
-      <c r="EZ2" s="29"/>
-      <c r="FA2" s="29"/>
-      <c r="FB2" s="29"/>
-      <c r="FC2" s="29"/>
-      <c r="FD2" s="29"/>
-      <c r="FE2" s="29"/>
-      <c r="FF2" s="29"/>
-      <c r="FG2" s="29"/>
-      <c r="FH2" s="29"/>
-      <c r="FI2" s="29"/>
+      <c r="AX2" s="25">
+        <v>46321</v>
+      </c>
+      <c r="AY2" s="25">
+        <v>46321</v>
+      </c>
+      <c r="AZ2" s="25">
+        <v>46321</v>
+      </c>
+      <c r="BA2" s="25">
+        <v>46322</v>
+      </c>
+      <c r="BB2" s="25">
+        <v>46322</v>
+      </c>
+      <c r="BC2" s="25">
+        <v>46322</v>
+      </c>
+      <c r="BD2" s="25">
+        <v>46322</v>
+      </c>
+      <c r="BE2" s="25">
+        <v>46323</v>
+      </c>
+      <c r="BF2" s="25">
+        <v>46323</v>
+      </c>
+      <c r="BG2" s="25">
+        <v>46323</v>
+      </c>
+      <c r="BH2" s="25">
+        <v>46323</v>
+      </c>
+      <c r="BI2" s="25">
+        <v>46323</v>
+      </c>
+      <c r="BJ2" s="25">
+        <v>46323</v>
+      </c>
+      <c r="BK2" s="25">
+        <v>46324</v>
+      </c>
+      <c r="BL2" s="25">
+        <v>46324</v>
+      </c>
+      <c r="BM2" s="25">
+        <v>46324</v>
+      </c>
+      <c r="BN2" s="25">
+        <v>46324</v>
+      </c>
+      <c r="BO2" s="25">
+        <v>46324</v>
+      </c>
+      <c r="BP2" s="25">
+        <v>46324</v>
+      </c>
+      <c r="BQ2" s="63">
+        <v>46325</v>
+      </c>
+      <c r="BR2" s="63">
+        <v>46325</v>
+      </c>
+      <c r="BS2" s="63">
+        <v>46325</v>
+      </c>
+      <c r="BT2" s="63">
+        <v>46325</v>
+      </c>
+      <c r="BU2" s="63">
+        <v>46325</v>
+      </c>
+      <c r="BV2" s="63">
+        <v>46325</v>
+      </c>
+      <c r="BW2" s="25"/>
+      <c r="BX2" s="25"/>
+      <c r="BY2" s="25"/>
+      <c r="BZ2" s="25"/>
+      <c r="CA2" s="25"/>
+      <c r="CB2" s="25"/>
+      <c r="CC2" s="25"/>
+      <c r="CD2" s="25"/>
+      <c r="CE2" s="25"/>
+      <c r="CF2" s="25"/>
+      <c r="CG2" s="25"/>
+      <c r="CH2" s="25"/>
+      <c r="CI2" s="25"/>
+      <c r="CJ2" s="25"/>
+      <c r="CK2" s="25"/>
+      <c r="CL2" s="25"/>
+      <c r="CM2" s="25"/>
+      <c r="CN2" s="25"/>
+      <c r="CO2" s="25"/>
+      <c r="CP2" s="25"/>
+      <c r="CQ2" s="25"/>
+      <c r="CR2" s="25"/>
+      <c r="CS2" s="25"/>
+      <c r="CT2" s="25"/>
+      <c r="CU2" s="25"/>
+      <c r="CV2" s="25"/>
+      <c r="CW2" s="25"/>
+      <c r="CX2" s="25"/>
+      <c r="CY2" s="25"/>
+      <c r="CZ2" s="25"/>
+      <c r="DA2" s="25"/>
+      <c r="DB2" s="25"/>
+      <c r="DC2" s="25"/>
+      <c r="DD2" s="25"/>
+      <c r="DE2" s="25"/>
+      <c r="DF2" s="25"/>
+      <c r="DG2" s="25"/>
+      <c r="DH2" s="25"/>
+      <c r="DI2" s="25"/>
+      <c r="DJ2" s="25"/>
+      <c r="DK2" s="25"/>
+      <c r="DL2" s="25"/>
+      <c r="DM2" s="25"/>
+      <c r="DN2" s="25"/>
+      <c r="DO2" s="25"/>
+      <c r="DP2" s="25"/>
+      <c r="DQ2" s="25"/>
+      <c r="DR2" s="25"/>
+      <c r="DS2" s="25"/>
+      <c r="DT2" s="25"/>
+      <c r="DU2" s="25"/>
+      <c r="DV2" s="25"/>
+      <c r="DW2" s="25"/>
+      <c r="DX2" s="25"/>
+      <c r="DY2" s="25"/>
+      <c r="DZ2" s="25"/>
+      <c r="EA2" s="25"/>
+      <c r="EB2" s="25"/>
+      <c r="EC2" s="25"/>
+      <c r="ED2" s="25"/>
+      <c r="EE2" s="25"/>
+      <c r="EF2" s="25"/>
+      <c r="EG2" s="25"/>
+      <c r="EH2" s="25"/>
+      <c r="EI2" s="25"/>
+      <c r="EJ2" s="25"/>
+      <c r="EK2" s="25"/>
+      <c r="EL2" s="25"/>
+      <c r="EM2" s="25"/>
+      <c r="EN2" s="25"/>
+      <c r="EO2" s="25"/>
+      <c r="EP2" s="25"/>
+      <c r="EQ2" s="25"/>
+      <c r="ER2" s="25"/>
+      <c r="ES2" s="25"/>
+      <c r="ET2" s="25"/>
+      <c r="EU2" s="25"/>
+      <c r="EV2" s="25"/>
+      <c r="EW2" s="25"/>
+      <c r="EX2" s="25"/>
+      <c r="EY2" s="25"/>
+      <c r="EZ2" s="25"/>
+      <c r="FA2" s="25"/>
+      <c r="FB2" s="25"/>
+      <c r="FC2" s="25"/>
+      <c r="FD2" s="25"/>
+      <c r="FE2" s="25"/>
+      <c r="FF2" s="25"/>
+      <c r="FG2" s="25"/>
+      <c r="FH2" s="25"/>
+      <c r="FI2" s="25"/>
     </row>
     <row r="3" spans="1:166" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="35" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="29"/>
-      <c r="L3" s="29"/>
-      <c r="M3" s="29"/>
-      <c r="N3" s="29"/>
-      <c r="O3" s="29"/>
-      <c r="P3" s="29"/>
-      <c r="Q3" s="29"/>
-      <c r="R3" s="29"/>
-      <c r="S3" s="29"/>
-      <c r="T3" s="29"/>
-      <c r="U3" s="29"/>
-      <c r="V3" s="29"/>
-      <c r="W3" s="29"/>
-      <c r="X3" s="29"/>
-      <c r="Y3" s="29"/>
-      <c r="Z3" s="29"/>
-      <c r="AA3" s="29"/>
-      <c r="AB3" s="29"/>
-      <c r="AC3" s="29"/>
-      <c r="AD3" s="29"/>
-      <c r="AE3" s="29"/>
-      <c r="AF3" s="29"/>
-      <c r="AG3" s="29"/>
-      <c r="AH3" s="29"/>
-      <c r="AI3" s="29"/>
-      <c r="AJ3" s="29"/>
-      <c r="AK3" s="29"/>
-      <c r="AL3" s="29"/>
-      <c r="AM3" s="29"/>
-      <c r="AN3" s="29"/>
-      <c r="AO3" s="29"/>
-      <c r="AP3" s="29"/>
-      <c r="AQ3" s="29"/>
-      <c r="AR3" s="29"/>
-      <c r="AS3" s="29"/>
-      <c r="AT3" s="29"/>
-      <c r="AU3" s="29"/>
-      <c r="AV3" s="29"/>
-      <c r="AW3" s="29"/>
-      <c r="AX3" s="29"/>
-      <c r="AY3" s="29"/>
-      <c r="AZ3" s="29"/>
-      <c r="BA3" s="29"/>
-      <c r="BB3" s="29"/>
-      <c r="BC3" s="29"/>
-      <c r="BD3" s="29"/>
-      <c r="BE3" s="29"/>
-      <c r="BF3" s="29"/>
-      <c r="BG3" s="29"/>
-      <c r="BH3" s="29"/>
-      <c r="BI3" s="29"/>
-      <c r="BJ3" s="29"/>
-      <c r="BK3" s="29"/>
-      <c r="BL3" s="29"/>
-      <c r="BM3" s="29"/>
-      <c r="BN3" s="29"/>
-      <c r="BO3" s="29"/>
-      <c r="BP3" s="29"/>
-      <c r="BQ3" s="29"/>
-      <c r="BR3" s="29"/>
-      <c r="BS3" s="29"/>
-      <c r="BT3" s="29"/>
-      <c r="BU3" s="29"/>
-      <c r="BV3" s="29"/>
-      <c r="BW3" s="29"/>
-      <c r="BX3" s="29"/>
-      <c r="BY3" s="29"/>
-      <c r="BZ3" s="29"/>
-      <c r="CA3" s="29"/>
-      <c r="CB3" s="29"/>
-      <c r="CC3" s="29"/>
-      <c r="CD3" s="29"/>
-      <c r="CE3" s="29"/>
-      <c r="CF3" s="29"/>
-      <c r="CG3" s="29"/>
-      <c r="CH3" s="29"/>
-      <c r="CI3" s="29"/>
-      <c r="CJ3" s="29"/>
-      <c r="CK3" s="29"/>
-      <c r="CL3" s="29"/>
-      <c r="CM3" s="29"/>
-      <c r="CN3" s="29"/>
-      <c r="CO3" s="29"/>
-      <c r="CP3" s="29"/>
-      <c r="CQ3" s="29"/>
-      <c r="CR3" s="29"/>
-      <c r="CS3" s="29"/>
-      <c r="CT3" s="29"/>
-      <c r="CU3" s="29"/>
-      <c r="CV3" s="29"/>
-      <c r="CW3" s="29"/>
-      <c r="CX3" s="29"/>
-      <c r="CY3" s="29"/>
-      <c r="CZ3" s="29"/>
-      <c r="DA3" s="29"/>
-      <c r="DB3" s="29"/>
-      <c r="DC3" s="29"/>
-      <c r="DD3" s="29"/>
-      <c r="DE3" s="29"/>
-      <c r="DF3" s="29"/>
-      <c r="DG3" s="29"/>
-      <c r="DH3" s="29"/>
-      <c r="DI3" s="29"/>
-      <c r="DJ3" s="29"/>
-      <c r="DK3" s="29"/>
-      <c r="DL3" s="29"/>
-      <c r="DM3" s="29"/>
-      <c r="DN3" s="29"/>
-      <c r="DO3" s="29"/>
-      <c r="DP3" s="29"/>
-      <c r="DQ3" s="29"/>
-      <c r="DR3" s="29"/>
-      <c r="DS3" s="29"/>
-      <c r="DT3" s="29"/>
-      <c r="DU3" s="29"/>
-      <c r="DV3" s="29"/>
-      <c r="DW3" s="29"/>
-      <c r="DX3" s="29"/>
-      <c r="DY3" s="29"/>
-      <c r="DZ3" s="29"/>
-      <c r="EA3" s="29"/>
-      <c r="EB3" s="29"/>
-      <c r="EC3" s="29"/>
-      <c r="ED3" s="29"/>
-      <c r="EE3" s="29"/>
-      <c r="EF3" s="29"/>
-      <c r="EG3" s="29"/>
-      <c r="EH3" s="29"/>
-      <c r="EI3" s="29"/>
-      <c r="EJ3" s="29"/>
-      <c r="EK3" s="29"/>
-      <c r="EL3" s="29"/>
-      <c r="EM3" s="29"/>
-      <c r="EN3" s="29"/>
-      <c r="EO3" s="29"/>
-      <c r="EP3" s="29"/>
-      <c r="EQ3" s="29"/>
-      <c r="ER3" s="29"/>
-      <c r="ES3" s="29"/>
-      <c r="ET3" s="29"/>
-      <c r="EU3" s="29"/>
-      <c r="EV3" s="29"/>
-      <c r="EW3" s="29"/>
-      <c r="EX3" s="29"/>
-      <c r="EY3" s="29"/>
-      <c r="EZ3" s="29"/>
-      <c r="FA3" s="29"/>
-      <c r="FB3" s="29"/>
-      <c r="FC3" s="29"/>
-      <c r="FD3" s="29"/>
-      <c r="FE3" s="29"/>
-      <c r="FF3" s="29"/>
-      <c r="FG3" s="29"/>
-      <c r="FH3" s="29"/>
-      <c r="FI3" s="29"/>
+      <c r="A3" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="25"/>
+      <c r="M3" s="25"/>
+      <c r="N3" s="25"/>
+      <c r="O3" s="25"/>
+      <c r="P3" s="25"/>
+      <c r="Q3" s="25"/>
+      <c r="R3" s="25"/>
+      <c r="S3" s="25"/>
+      <c r="T3" s="25"/>
+      <c r="U3" s="25"/>
+      <c r="V3" s="25"/>
+      <c r="W3" s="25"/>
+      <c r="X3" s="25"/>
+      <c r="Y3" s="25"/>
+      <c r="Z3" s="25"/>
+      <c r="AA3" s="25"/>
+      <c r="AB3" s="25"/>
+      <c r="AC3" s="25"/>
+      <c r="AD3" s="25"/>
+      <c r="AE3" s="25"/>
+      <c r="AF3" s="25"/>
+      <c r="AG3" s="25"/>
+      <c r="AH3" s="25"/>
+      <c r="AI3" s="25"/>
+      <c r="AJ3" s="25"/>
+      <c r="AK3" s="25"/>
+      <c r="AL3" s="25"/>
+      <c r="AM3" s="25"/>
+      <c r="AN3" s="25"/>
+      <c r="AO3" s="25"/>
+      <c r="AP3" s="25"/>
+      <c r="AQ3" s="25"/>
+      <c r="AR3" s="25"/>
+      <c r="AS3" s="25"/>
+      <c r="AT3" s="25"/>
+      <c r="AU3" s="25"/>
+      <c r="AV3" s="25"/>
+      <c r="AW3" s="25"/>
+      <c r="AX3" s="25"/>
+      <c r="AY3" s="25"/>
+      <c r="AZ3" s="25"/>
+      <c r="BA3" s="25"/>
+      <c r="BB3" s="25"/>
+      <c r="BC3" s="25"/>
+      <c r="BD3" s="25"/>
+      <c r="BE3" s="25"/>
+      <c r="BF3" s="25"/>
+      <c r="BG3" s="25"/>
+      <c r="BH3" s="25"/>
+      <c r="BI3" s="25"/>
+      <c r="BJ3" s="25"/>
+      <c r="BK3" s="25"/>
+      <c r="BL3" s="25"/>
+      <c r="BM3" s="25"/>
+      <c r="BN3" s="25"/>
+      <c r="BO3" s="25"/>
+      <c r="BP3" s="25"/>
+      <c r="BQ3" s="63"/>
+      <c r="BR3" s="63"/>
+      <c r="BS3" s="63"/>
+      <c r="BT3" s="63"/>
+      <c r="BU3" s="63"/>
+      <c r="BV3" s="63"/>
+      <c r="BW3" s="25"/>
+      <c r="BX3" s="25"/>
+      <c r="BY3" s="25"/>
+      <c r="BZ3" s="25"/>
+      <c r="CA3" s="25"/>
+      <c r="CB3" s="25"/>
+      <c r="CC3" s="25"/>
+      <c r="CD3" s="25"/>
+      <c r="CE3" s="25"/>
+      <c r="CF3" s="25"/>
+      <c r="CG3" s="25"/>
+      <c r="CH3" s="25"/>
+      <c r="CI3" s="25"/>
+      <c r="CJ3" s="25"/>
+      <c r="CK3" s="25"/>
+      <c r="CL3" s="25"/>
+      <c r="CM3" s="25"/>
+      <c r="CN3" s="25"/>
+      <c r="CO3" s="25"/>
+      <c r="CP3" s="25"/>
+      <c r="CQ3" s="25"/>
+      <c r="CR3" s="25"/>
+      <c r="CS3" s="25"/>
+      <c r="CT3" s="25"/>
+      <c r="CU3" s="25"/>
+      <c r="CV3" s="25"/>
+      <c r="CW3" s="25"/>
+      <c r="CX3" s="25"/>
+      <c r="CY3" s="25"/>
+      <c r="CZ3" s="25"/>
+      <c r="DA3" s="25"/>
+      <c r="DB3" s="25"/>
+      <c r="DC3" s="25"/>
+      <c r="DD3" s="25"/>
+      <c r="DE3" s="25"/>
+      <c r="DF3" s="25"/>
+      <c r="DG3" s="25"/>
+      <c r="DH3" s="25"/>
+      <c r="DI3" s="25"/>
+      <c r="DJ3" s="25"/>
+      <c r="DK3" s="25"/>
+      <c r="DL3" s="25"/>
+      <c r="DM3" s="25"/>
+      <c r="DN3" s="25"/>
+      <c r="DO3" s="25"/>
+      <c r="DP3" s="25"/>
+      <c r="DQ3" s="25"/>
+      <c r="DR3" s="25"/>
+      <c r="DS3" s="25"/>
+      <c r="DT3" s="25"/>
+      <c r="DU3" s="25"/>
+      <c r="DV3" s="25"/>
+      <c r="DW3" s="25"/>
+      <c r="DX3" s="25"/>
+      <c r="DY3" s="25"/>
+      <c r="DZ3" s="25"/>
+      <c r="EA3" s="25"/>
+      <c r="EB3" s="25"/>
+      <c r="EC3" s="25"/>
+      <c r="ED3" s="25"/>
+      <c r="EE3" s="25"/>
+      <c r="EF3" s="25"/>
+      <c r="EG3" s="25"/>
+      <c r="EH3" s="25"/>
+      <c r="EI3" s="25"/>
+      <c r="EJ3" s="25"/>
+      <c r="EK3" s="25"/>
+      <c r="EL3" s="25"/>
+      <c r="EM3" s="25"/>
+      <c r="EN3" s="25"/>
+      <c r="EO3" s="25"/>
+      <c r="EP3" s="25"/>
+      <c r="EQ3" s="25"/>
+      <c r="ER3" s="25"/>
+      <c r="ES3" s="25"/>
+      <c r="ET3" s="25"/>
+      <c r="EU3" s="25"/>
+      <c r="EV3" s="25"/>
+      <c r="EW3" s="25"/>
+      <c r="EX3" s="25"/>
+      <c r="EY3" s="25"/>
+      <c r="EZ3" s="25"/>
+      <c r="FA3" s="25"/>
+      <c r="FB3" s="25"/>
+      <c r="FC3" s="25"/>
+      <c r="FD3" s="25"/>
+      <c r="FE3" s="25"/>
+      <c r="FF3" s="25"/>
+      <c r="FG3" s="25"/>
+      <c r="FH3" s="25"/>
+      <c r="FI3" s="25"/>
     </row>
     <row r="4" spans="1:166" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="32" t="s">
+      <c r="A4" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="43"/>
+      <c r="C4" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="34"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="29"/>
-      <c r="L4" s="29"/>
-      <c r="M4" s="29"/>
-      <c r="N4" s="29"/>
-      <c r="O4" s="29"/>
-      <c r="P4" s="29"/>
-      <c r="Q4" s="29"/>
-      <c r="R4" s="29"/>
-      <c r="S4" s="29"/>
-      <c r="T4" s="29"/>
-      <c r="U4" s="29"/>
-      <c r="V4" s="29"/>
-      <c r="W4" s="29"/>
-      <c r="X4" s="29"/>
-      <c r="Y4" s="29"/>
-      <c r="Z4" s="29"/>
-      <c r="AA4" s="29"/>
-      <c r="AB4" s="29"/>
-      <c r="AC4" s="29"/>
-      <c r="AD4" s="29"/>
-      <c r="AE4" s="29"/>
-      <c r="AF4" s="29"/>
-      <c r="AG4" s="29"/>
-      <c r="AH4" s="29"/>
-      <c r="AI4" s="29"/>
-      <c r="AJ4" s="29"/>
-      <c r="AK4" s="29"/>
-      <c r="AL4" s="29"/>
-      <c r="AM4" s="29"/>
-      <c r="AN4" s="29"/>
-      <c r="AO4" s="29"/>
-      <c r="AP4" s="29"/>
-      <c r="AQ4" s="29"/>
-      <c r="AR4" s="29"/>
-      <c r="AS4" s="29"/>
-      <c r="AT4" s="29"/>
-      <c r="AU4" s="29"/>
-      <c r="AV4" s="29"/>
-      <c r="AW4" s="29"/>
-      <c r="AX4" s="29"/>
-      <c r="AY4" s="29"/>
-      <c r="AZ4" s="29"/>
-      <c r="BA4" s="29"/>
-      <c r="BB4" s="29"/>
-      <c r="BC4" s="29"/>
-      <c r="BD4" s="29"/>
-      <c r="BE4" s="29"/>
-      <c r="BF4" s="29"/>
-      <c r="BG4" s="29"/>
-      <c r="BH4" s="29"/>
-      <c r="BI4" s="29"/>
-      <c r="BJ4" s="29"/>
-      <c r="BK4" s="29"/>
-      <c r="BL4" s="29"/>
-      <c r="BM4" s="29"/>
-      <c r="BN4" s="29"/>
-      <c r="BO4" s="29"/>
-      <c r="BP4" s="29"/>
-      <c r="BQ4" s="29"/>
-      <c r="BR4" s="29"/>
-      <c r="BS4" s="29"/>
-      <c r="BT4" s="29"/>
-      <c r="BU4" s="29"/>
-      <c r="BV4" s="29"/>
-      <c r="BW4" s="29"/>
-      <c r="BX4" s="29"/>
-      <c r="BY4" s="29"/>
-      <c r="BZ4" s="29"/>
-      <c r="CA4" s="29"/>
-      <c r="CB4" s="29"/>
-      <c r="CC4" s="29"/>
-      <c r="CD4" s="29"/>
-      <c r="CE4" s="29"/>
-      <c r="CF4" s="29"/>
-      <c r="CG4" s="29"/>
-      <c r="CH4" s="29"/>
-      <c r="CI4" s="29"/>
-      <c r="CJ4" s="29"/>
-      <c r="CK4" s="29"/>
-      <c r="CL4" s="29"/>
-      <c r="CM4" s="29"/>
-      <c r="CN4" s="29"/>
-      <c r="CO4" s="29"/>
-      <c r="CP4" s="29"/>
-      <c r="CQ4" s="29"/>
-      <c r="CR4" s="29"/>
-      <c r="CS4" s="29"/>
-      <c r="CT4" s="29"/>
-      <c r="CU4" s="29"/>
-      <c r="CV4" s="29"/>
-      <c r="CW4" s="29"/>
-      <c r="CX4" s="29"/>
-      <c r="CY4" s="29"/>
-      <c r="CZ4" s="29"/>
-      <c r="DA4" s="29"/>
-      <c r="DB4" s="29"/>
-      <c r="DC4" s="29"/>
-      <c r="DD4" s="29"/>
-      <c r="DE4" s="29"/>
-      <c r="DF4" s="29"/>
-      <c r="DG4" s="29"/>
-      <c r="DH4" s="29"/>
-      <c r="DI4" s="29"/>
-      <c r="DJ4" s="29"/>
-      <c r="DK4" s="29"/>
-      <c r="DL4" s="29"/>
-      <c r="DM4" s="29"/>
-      <c r="DN4" s="29"/>
-      <c r="DO4" s="29"/>
-      <c r="DP4" s="29"/>
-      <c r="DQ4" s="29"/>
-      <c r="DR4" s="29"/>
-      <c r="DS4" s="29"/>
-      <c r="DT4" s="29"/>
-      <c r="DU4" s="29"/>
-      <c r="DV4" s="29"/>
-      <c r="DW4" s="29"/>
-      <c r="DX4" s="29"/>
-      <c r="DY4" s="29"/>
-      <c r="DZ4" s="29"/>
-      <c r="EA4" s="29"/>
-      <c r="EB4" s="29"/>
-      <c r="EC4" s="29"/>
-      <c r="ED4" s="29"/>
-      <c r="EE4" s="29"/>
-      <c r="EF4" s="29"/>
-      <c r="EG4" s="29"/>
-      <c r="EH4" s="29"/>
-      <c r="EI4" s="29"/>
-      <c r="EJ4" s="29"/>
-      <c r="EK4" s="29"/>
-      <c r="EL4" s="29"/>
-      <c r="EM4" s="29"/>
-      <c r="EN4" s="29"/>
-      <c r="EO4" s="29"/>
-      <c r="EP4" s="29"/>
-      <c r="EQ4" s="29"/>
-      <c r="ER4" s="29"/>
-      <c r="ES4" s="29"/>
-      <c r="ET4" s="29"/>
-      <c r="EU4" s="29"/>
-      <c r="EV4" s="29"/>
-      <c r="EW4" s="29"/>
-      <c r="EX4" s="29"/>
-      <c r="EY4" s="29"/>
-      <c r="EZ4" s="29"/>
-      <c r="FA4" s="29"/>
-      <c r="FB4" s="29"/>
-      <c r="FC4" s="29"/>
-      <c r="FD4" s="29"/>
-      <c r="FE4" s="29"/>
-      <c r="FF4" s="29"/>
-      <c r="FG4" s="29"/>
-      <c r="FH4" s="29"/>
-      <c r="FI4" s="29"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+      <c r="M4" s="25"/>
+      <c r="N4" s="25"/>
+      <c r="O4" s="25"/>
+      <c r="P4" s="25"/>
+      <c r="Q4" s="25"/>
+      <c r="R4" s="25"/>
+      <c r="S4" s="25"/>
+      <c r="T4" s="25"/>
+      <c r="U4" s="25"/>
+      <c r="V4" s="25"/>
+      <c r="W4" s="25"/>
+      <c r="X4" s="25"/>
+      <c r="Y4" s="25"/>
+      <c r="Z4" s="25"/>
+      <c r="AA4" s="25"/>
+      <c r="AB4" s="25"/>
+      <c r="AC4" s="25"/>
+      <c r="AD4" s="25"/>
+      <c r="AE4" s="25"/>
+      <c r="AF4" s="25"/>
+      <c r="AG4" s="25"/>
+      <c r="AH4" s="25"/>
+      <c r="AI4" s="25"/>
+      <c r="AJ4" s="25"/>
+      <c r="AK4" s="25"/>
+      <c r="AL4" s="25"/>
+      <c r="AM4" s="25"/>
+      <c r="AN4" s="25"/>
+      <c r="AO4" s="25"/>
+      <c r="AP4" s="25"/>
+      <c r="AQ4" s="25"/>
+      <c r="AR4" s="25"/>
+      <c r="AS4" s="25"/>
+      <c r="AT4" s="25"/>
+      <c r="AU4" s="25"/>
+      <c r="AV4" s="25"/>
+      <c r="AW4" s="25"/>
+      <c r="AX4" s="25"/>
+      <c r="AY4" s="25"/>
+      <c r="AZ4" s="25"/>
+      <c r="BA4" s="25"/>
+      <c r="BB4" s="25"/>
+      <c r="BC4" s="25"/>
+      <c r="BD4" s="25"/>
+      <c r="BE4" s="25"/>
+      <c r="BF4" s="25"/>
+      <c r="BG4" s="25"/>
+      <c r="BH4" s="25"/>
+      <c r="BI4" s="25"/>
+      <c r="BJ4" s="25"/>
+      <c r="BK4" s="25"/>
+      <c r="BL4" s="25"/>
+      <c r="BM4" s="25"/>
+      <c r="BN4" s="25"/>
+      <c r="BO4" s="25"/>
+      <c r="BP4" s="25"/>
+      <c r="BQ4" s="63"/>
+      <c r="BR4" s="63"/>
+      <c r="BS4" s="63"/>
+      <c r="BT4" s="63"/>
+      <c r="BU4" s="63"/>
+      <c r="BV4" s="63"/>
+      <c r="BW4" s="25"/>
+      <c r="BX4" s="25"/>
+      <c r="BY4" s="25"/>
+      <c r="BZ4" s="25"/>
+      <c r="CA4" s="25"/>
+      <c r="CB4" s="25"/>
+      <c r="CC4" s="25"/>
+      <c r="CD4" s="25"/>
+      <c r="CE4" s="25"/>
+      <c r="CF4" s="25"/>
+      <c r="CG4" s="25"/>
+      <c r="CH4" s="25"/>
+      <c r="CI4" s="25"/>
+      <c r="CJ4" s="25"/>
+      <c r="CK4" s="25"/>
+      <c r="CL4" s="25"/>
+      <c r="CM4" s="25"/>
+      <c r="CN4" s="25"/>
+      <c r="CO4" s="25"/>
+      <c r="CP4" s="25"/>
+      <c r="CQ4" s="25"/>
+      <c r="CR4" s="25"/>
+      <c r="CS4" s="25"/>
+      <c r="CT4" s="25"/>
+      <c r="CU4" s="25"/>
+      <c r="CV4" s="25"/>
+      <c r="CW4" s="25"/>
+      <c r="CX4" s="25"/>
+      <c r="CY4" s="25"/>
+      <c r="CZ4" s="25"/>
+      <c r="DA4" s="25"/>
+      <c r="DB4" s="25"/>
+      <c r="DC4" s="25"/>
+      <c r="DD4" s="25"/>
+      <c r="DE4" s="25"/>
+      <c r="DF4" s="25"/>
+      <c r="DG4" s="25"/>
+      <c r="DH4" s="25"/>
+      <c r="DI4" s="25"/>
+      <c r="DJ4" s="25"/>
+      <c r="DK4" s="25"/>
+      <c r="DL4" s="25"/>
+      <c r="DM4" s="25"/>
+      <c r="DN4" s="25"/>
+      <c r="DO4" s="25"/>
+      <c r="DP4" s="25"/>
+      <c r="DQ4" s="25"/>
+      <c r="DR4" s="25"/>
+      <c r="DS4" s="25"/>
+      <c r="DT4" s="25"/>
+      <c r="DU4" s="25"/>
+      <c r="DV4" s="25"/>
+      <c r="DW4" s="25"/>
+      <c r="DX4" s="25"/>
+      <c r="DY4" s="25"/>
+      <c r="DZ4" s="25"/>
+      <c r="EA4" s="25"/>
+      <c r="EB4" s="25"/>
+      <c r="EC4" s="25"/>
+      <c r="ED4" s="25"/>
+      <c r="EE4" s="25"/>
+      <c r="EF4" s="25"/>
+      <c r="EG4" s="25"/>
+      <c r="EH4" s="25"/>
+      <c r="EI4" s="25"/>
+      <c r="EJ4" s="25"/>
+      <c r="EK4" s="25"/>
+      <c r="EL4" s="25"/>
+      <c r="EM4" s="25"/>
+      <c r="EN4" s="25"/>
+      <c r="EO4" s="25"/>
+      <c r="EP4" s="25"/>
+      <c r="EQ4" s="25"/>
+      <c r="ER4" s="25"/>
+      <c r="ES4" s="25"/>
+      <c r="ET4" s="25"/>
+      <c r="EU4" s="25"/>
+      <c r="EV4" s="25"/>
+      <c r="EW4" s="25"/>
+      <c r="EX4" s="25"/>
+      <c r="EY4" s="25"/>
+      <c r="EZ4" s="25"/>
+      <c r="FA4" s="25"/>
+      <c r="FB4" s="25"/>
+      <c r="FC4" s="25"/>
+      <c r="FD4" s="25"/>
+      <c r="FE4" s="25"/>
+      <c r="FF4" s="25"/>
+      <c r="FG4" s="25"/>
+      <c r="FH4" s="25"/>
+      <c r="FI4" s="25"/>
     </row>
     <row r="5" spans="1:166" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="48"/>
-      <c r="C5" s="49">
+      <c r="B5" s="46"/>
+      <c r="C5" s="47">
         <v>140</v>
       </c>
-      <c r="D5" s="50"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="29"/>
-      <c r="P5" s="29"/>
-      <c r="Q5" s="29"/>
-      <c r="R5" s="29"/>
-      <c r="S5" s="29"/>
-      <c r="T5" s="29"/>
-      <c r="U5" s="29"/>
-      <c r="V5" s="29"/>
-      <c r="W5" s="29"/>
-      <c r="X5" s="29"/>
-      <c r="Y5" s="29"/>
-      <c r="Z5" s="29"/>
-      <c r="AA5" s="29"/>
-      <c r="AB5" s="29"/>
-      <c r="AC5" s="29"/>
-      <c r="AD5" s="29"/>
-      <c r="AE5" s="29"/>
-      <c r="AF5" s="29"/>
-      <c r="AG5" s="29"/>
-      <c r="AH5" s="29"/>
-      <c r="AI5" s="29"/>
-      <c r="AJ5" s="29"/>
-      <c r="AK5" s="29"/>
-      <c r="AL5" s="29"/>
-      <c r="AM5" s="29"/>
-      <c r="AN5" s="29"/>
-      <c r="AO5" s="29"/>
-      <c r="AP5" s="29"/>
-      <c r="AQ5" s="29"/>
-      <c r="AR5" s="29"/>
-      <c r="AS5" s="29"/>
-      <c r="AT5" s="29"/>
-      <c r="AU5" s="29"/>
-      <c r="AV5" s="29"/>
-      <c r="AW5" s="29"/>
-      <c r="AX5" s="29"/>
-      <c r="AY5" s="29"/>
-      <c r="AZ5" s="29"/>
-      <c r="BA5" s="29"/>
-      <c r="BB5" s="29"/>
-      <c r="BC5" s="29"/>
-      <c r="BD5" s="29"/>
-      <c r="BE5" s="29"/>
-      <c r="BF5" s="29"/>
-      <c r="BG5" s="29"/>
-      <c r="BH5" s="29"/>
-      <c r="BI5" s="29"/>
-      <c r="BJ5" s="29"/>
-      <c r="BK5" s="29"/>
-      <c r="BL5" s="29"/>
-      <c r="BM5" s="29"/>
-      <c r="BN5" s="29"/>
-      <c r="BO5" s="29"/>
-      <c r="BP5" s="29"/>
-      <c r="BQ5" s="29"/>
-      <c r="BR5" s="29"/>
-      <c r="BS5" s="29"/>
-      <c r="BT5" s="29"/>
-      <c r="BU5" s="29"/>
-      <c r="BV5" s="29"/>
-      <c r="BW5" s="29"/>
-      <c r="BX5" s="29"/>
-      <c r="BY5" s="29"/>
-      <c r="BZ5" s="29"/>
-      <c r="CA5" s="29"/>
-      <c r="CB5" s="29"/>
-      <c r="CC5" s="29"/>
-      <c r="CD5" s="29"/>
-      <c r="CE5" s="29"/>
-      <c r="CF5" s="29"/>
-      <c r="CG5" s="29"/>
-      <c r="CH5" s="29"/>
-      <c r="CI5" s="29"/>
-      <c r="CJ5" s="29"/>
-      <c r="CK5" s="29"/>
-      <c r="CL5" s="29"/>
-      <c r="CM5" s="29"/>
-      <c r="CN5" s="29"/>
-      <c r="CO5" s="29"/>
-      <c r="CP5" s="29"/>
-      <c r="CQ5" s="29"/>
-      <c r="CR5" s="29"/>
-      <c r="CS5" s="29"/>
-      <c r="CT5" s="29"/>
-      <c r="CU5" s="29"/>
-      <c r="CV5" s="29"/>
-      <c r="CW5" s="29"/>
-      <c r="CX5" s="29"/>
-      <c r="CY5" s="29"/>
-      <c r="CZ5" s="29"/>
-      <c r="DA5" s="29"/>
-      <c r="DB5" s="29"/>
-      <c r="DC5" s="29"/>
-      <c r="DD5" s="29"/>
-      <c r="DE5" s="29"/>
-      <c r="DF5" s="29"/>
-      <c r="DG5" s="29"/>
-      <c r="DH5" s="29"/>
-      <c r="DI5" s="29"/>
-      <c r="DJ5" s="29"/>
-      <c r="DK5" s="29"/>
-      <c r="DL5" s="29"/>
-      <c r="DM5" s="29"/>
-      <c r="DN5" s="29"/>
-      <c r="DO5" s="29"/>
-      <c r="DP5" s="29"/>
-      <c r="DQ5" s="29"/>
-      <c r="DR5" s="29"/>
-      <c r="DS5" s="29"/>
-      <c r="DT5" s="29"/>
-      <c r="DU5" s="29"/>
-      <c r="DV5" s="29"/>
-      <c r="DW5" s="29"/>
-      <c r="DX5" s="29"/>
-      <c r="DY5" s="29"/>
-      <c r="DZ5" s="29"/>
-      <c r="EA5" s="29"/>
-      <c r="EB5" s="29"/>
-      <c r="EC5" s="29"/>
-      <c r="ED5" s="29"/>
-      <c r="EE5" s="29"/>
-      <c r="EF5" s="29"/>
-      <c r="EG5" s="29"/>
-      <c r="EH5" s="29"/>
-      <c r="EI5" s="29"/>
-      <c r="EJ5" s="29"/>
-      <c r="EK5" s="29"/>
-      <c r="EL5" s="29"/>
-      <c r="EM5" s="29"/>
-      <c r="EN5" s="29"/>
-      <c r="EO5" s="29"/>
-      <c r="EP5" s="29"/>
-      <c r="EQ5" s="29"/>
-      <c r="ER5" s="29"/>
-      <c r="ES5" s="29"/>
-      <c r="ET5" s="29"/>
-      <c r="EU5" s="29"/>
-      <c r="EV5" s="29"/>
-      <c r="EW5" s="29"/>
-      <c r="EX5" s="29"/>
-      <c r="EY5" s="29"/>
-      <c r="EZ5" s="29"/>
-      <c r="FA5" s="29"/>
-      <c r="FB5" s="29"/>
-      <c r="FC5" s="29"/>
-      <c r="FD5" s="29"/>
-      <c r="FE5" s="29"/>
-      <c r="FF5" s="29"/>
-      <c r="FG5" s="29"/>
-      <c r="FH5" s="29"/>
-      <c r="FI5" s="29"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="25"/>
+      <c r="M5" s="25"/>
+      <c r="N5" s="25"/>
+      <c r="O5" s="25"/>
+      <c r="P5" s="25"/>
+      <c r="Q5" s="25"/>
+      <c r="R5" s="25"/>
+      <c r="S5" s="25"/>
+      <c r="T5" s="25"/>
+      <c r="U5" s="25"/>
+      <c r="V5" s="25"/>
+      <c r="W5" s="25"/>
+      <c r="X5" s="25"/>
+      <c r="Y5" s="25"/>
+      <c r="Z5" s="25"/>
+      <c r="AA5" s="25"/>
+      <c r="AB5" s="25"/>
+      <c r="AC5" s="25"/>
+      <c r="AD5" s="25"/>
+      <c r="AE5" s="25"/>
+      <c r="AF5" s="25"/>
+      <c r="AG5" s="25"/>
+      <c r="AH5" s="25"/>
+      <c r="AI5" s="25"/>
+      <c r="AJ5" s="25"/>
+      <c r="AK5" s="25"/>
+      <c r="AL5" s="25"/>
+      <c r="AM5" s="25"/>
+      <c r="AN5" s="25"/>
+      <c r="AO5" s="25"/>
+      <c r="AP5" s="25"/>
+      <c r="AQ5" s="25"/>
+      <c r="AR5" s="25"/>
+      <c r="AS5" s="25"/>
+      <c r="AT5" s="25"/>
+      <c r="AU5" s="25"/>
+      <c r="AV5" s="25"/>
+      <c r="AW5" s="25"/>
+      <c r="AX5" s="25"/>
+      <c r="AY5" s="25"/>
+      <c r="AZ5" s="25"/>
+      <c r="BA5" s="25"/>
+      <c r="BB5" s="25"/>
+      <c r="BC5" s="25"/>
+      <c r="BD5" s="25"/>
+      <c r="BE5" s="25"/>
+      <c r="BF5" s="25"/>
+      <c r="BG5" s="25"/>
+      <c r="BH5" s="25"/>
+      <c r="BI5" s="25"/>
+      <c r="BJ5" s="25"/>
+      <c r="BK5" s="25"/>
+      <c r="BL5" s="25"/>
+      <c r="BM5" s="25"/>
+      <c r="BN5" s="25"/>
+      <c r="BO5" s="25"/>
+      <c r="BP5" s="25"/>
+      <c r="BQ5" s="63"/>
+      <c r="BR5" s="63"/>
+      <c r="BS5" s="63"/>
+      <c r="BT5" s="63"/>
+      <c r="BU5" s="63"/>
+      <c r="BV5" s="63"/>
+      <c r="BW5" s="25"/>
+      <c r="BX5" s="25"/>
+      <c r="BY5" s="25"/>
+      <c r="BZ5" s="25"/>
+      <c r="CA5" s="25"/>
+      <c r="CB5" s="25"/>
+      <c r="CC5" s="25"/>
+      <c r="CD5" s="25"/>
+      <c r="CE5" s="25"/>
+      <c r="CF5" s="25"/>
+      <c r="CG5" s="25"/>
+      <c r="CH5" s="25"/>
+      <c r="CI5" s="25"/>
+      <c r="CJ5" s="25"/>
+      <c r="CK5" s="25"/>
+      <c r="CL5" s="25"/>
+      <c r="CM5" s="25"/>
+      <c r="CN5" s="25"/>
+      <c r="CO5" s="25"/>
+      <c r="CP5" s="25"/>
+      <c r="CQ5" s="25"/>
+      <c r="CR5" s="25"/>
+      <c r="CS5" s="25"/>
+      <c r="CT5" s="25"/>
+      <c r="CU5" s="25"/>
+      <c r="CV5" s="25"/>
+      <c r="CW5" s="25"/>
+      <c r="CX5" s="25"/>
+      <c r="CY5" s="25"/>
+      <c r="CZ5" s="25"/>
+      <c r="DA5" s="25"/>
+      <c r="DB5" s="25"/>
+      <c r="DC5" s="25"/>
+      <c r="DD5" s="25"/>
+      <c r="DE5" s="25"/>
+      <c r="DF5" s="25"/>
+      <c r="DG5" s="25"/>
+      <c r="DH5" s="25"/>
+      <c r="DI5" s="25"/>
+      <c r="DJ5" s="25"/>
+      <c r="DK5" s="25"/>
+      <c r="DL5" s="25"/>
+      <c r="DM5" s="25"/>
+      <c r="DN5" s="25"/>
+      <c r="DO5" s="25"/>
+      <c r="DP5" s="25"/>
+      <c r="DQ5" s="25"/>
+      <c r="DR5" s="25"/>
+      <c r="DS5" s="25"/>
+      <c r="DT5" s="25"/>
+      <c r="DU5" s="25"/>
+      <c r="DV5" s="25"/>
+      <c r="DW5" s="25"/>
+      <c r="DX5" s="25"/>
+      <c r="DY5" s="25"/>
+      <c r="DZ5" s="25"/>
+      <c r="EA5" s="25"/>
+      <c r="EB5" s="25"/>
+      <c r="EC5" s="25"/>
+      <c r="ED5" s="25"/>
+      <c r="EE5" s="25"/>
+      <c r="EF5" s="25"/>
+      <c r="EG5" s="25"/>
+      <c r="EH5" s="25"/>
+      <c r="EI5" s="25"/>
+      <c r="EJ5" s="25"/>
+      <c r="EK5" s="25"/>
+      <c r="EL5" s="25"/>
+      <c r="EM5" s="25"/>
+      <c r="EN5" s="25"/>
+      <c r="EO5" s="25"/>
+      <c r="EP5" s="25"/>
+      <c r="EQ5" s="25"/>
+      <c r="ER5" s="25"/>
+      <c r="ES5" s="25"/>
+      <c r="ET5" s="25"/>
+      <c r="EU5" s="25"/>
+      <c r="EV5" s="25"/>
+      <c r="EW5" s="25"/>
+      <c r="EX5" s="25"/>
+      <c r="EY5" s="25"/>
+      <c r="EZ5" s="25"/>
+      <c r="FA5" s="25"/>
+      <c r="FB5" s="25"/>
+      <c r="FC5" s="25"/>
+      <c r="FD5" s="25"/>
+      <c r="FE5" s="25"/>
+      <c r="FF5" s="25"/>
+      <c r="FG5" s="25"/>
+      <c r="FH5" s="25"/>
+      <c r="FI5" s="25"/>
     </row>
     <row r="6" spans="1:166" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="48" t="s">
+      <c r="A6" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="49">
+      <c r="B6" s="46"/>
+      <c r="C6" s="47">
         <v>25</v>
       </c>
-      <c r="D6" s="50"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="29"/>
-      <c r="L6" s="29"/>
-      <c r="M6" s="29"/>
-      <c r="N6" s="29"/>
-      <c r="O6" s="29"/>
-      <c r="P6" s="29"/>
-      <c r="Q6" s="29"/>
-      <c r="R6" s="29"/>
-      <c r="S6" s="29"/>
-      <c r="T6" s="29"/>
-      <c r="U6" s="29"/>
-      <c r="V6" s="29"/>
-      <c r="W6" s="29"/>
-      <c r="X6" s="29"/>
-      <c r="Y6" s="29"/>
-      <c r="Z6" s="29"/>
-      <c r="AA6" s="29"/>
-      <c r="AB6" s="29"/>
-      <c r="AC6" s="29"/>
-      <c r="AD6" s="29"/>
-      <c r="AE6" s="29"/>
-      <c r="AF6" s="29"/>
-      <c r="AG6" s="29"/>
-      <c r="AH6" s="29"/>
-      <c r="AI6" s="29"/>
-      <c r="AJ6" s="29"/>
-      <c r="AK6" s="29"/>
-      <c r="AL6" s="29"/>
-      <c r="AM6" s="29"/>
-      <c r="AN6" s="29"/>
-      <c r="AO6" s="29"/>
-      <c r="AP6" s="29"/>
-      <c r="AQ6" s="29"/>
-      <c r="AR6" s="29"/>
-      <c r="AS6" s="29"/>
-      <c r="AT6" s="29"/>
-      <c r="AU6" s="29"/>
-      <c r="AV6" s="29"/>
-      <c r="AW6" s="29"/>
-      <c r="AX6" s="29"/>
-      <c r="AY6" s="29"/>
-      <c r="AZ6" s="29"/>
-      <c r="BA6" s="29"/>
-      <c r="BB6" s="29"/>
-      <c r="BC6" s="29"/>
-      <c r="BD6" s="29"/>
-      <c r="BE6" s="29"/>
-      <c r="BF6" s="29"/>
-      <c r="BG6" s="29"/>
-      <c r="BH6" s="29"/>
-      <c r="BI6" s="29"/>
-      <c r="BJ6" s="29"/>
-      <c r="BK6" s="29"/>
-      <c r="BL6" s="29"/>
-      <c r="BM6" s="29"/>
-      <c r="BN6" s="29"/>
-      <c r="BO6" s="29"/>
-      <c r="BP6" s="29"/>
-      <c r="BQ6" s="29"/>
-      <c r="BR6" s="29"/>
-      <c r="BS6" s="29"/>
-      <c r="BT6" s="29"/>
-      <c r="BU6" s="29"/>
-      <c r="BV6" s="29"/>
-      <c r="BW6" s="29"/>
-      <c r="BX6" s="29"/>
-      <c r="BY6" s="29"/>
-      <c r="BZ6" s="29"/>
-      <c r="CA6" s="29"/>
-      <c r="CB6" s="29"/>
-      <c r="CC6" s="29"/>
-      <c r="CD6" s="29"/>
-      <c r="CE6" s="29"/>
-      <c r="CF6" s="29"/>
-      <c r="CG6" s="29"/>
-      <c r="CH6" s="29"/>
-      <c r="CI6" s="29"/>
-      <c r="CJ6" s="29"/>
-      <c r="CK6" s="29"/>
-      <c r="CL6" s="29"/>
-      <c r="CM6" s="29"/>
-      <c r="CN6" s="29"/>
-      <c r="CO6" s="29"/>
-      <c r="CP6" s="29"/>
-      <c r="CQ6" s="29"/>
-      <c r="CR6" s="29"/>
-      <c r="CS6" s="29"/>
-      <c r="CT6" s="29"/>
-      <c r="CU6" s="29"/>
-      <c r="CV6" s="29"/>
-      <c r="CW6" s="29"/>
-      <c r="CX6" s="29"/>
-      <c r="CY6" s="29"/>
-      <c r="CZ6" s="29"/>
-      <c r="DA6" s="29"/>
-      <c r="DB6" s="29"/>
-      <c r="DC6" s="29"/>
-      <c r="DD6" s="29"/>
-      <c r="DE6" s="29"/>
-      <c r="DF6" s="29"/>
-      <c r="DG6" s="29"/>
-      <c r="DH6" s="29"/>
-      <c r="DI6" s="29"/>
-      <c r="DJ6" s="29"/>
-      <c r="DK6" s="29"/>
-      <c r="DL6" s="29"/>
-      <c r="DM6" s="29"/>
-      <c r="DN6" s="29"/>
-      <c r="DO6" s="29"/>
-      <c r="DP6" s="29"/>
-      <c r="DQ6" s="29"/>
-      <c r="DR6" s="29"/>
-      <c r="DS6" s="29"/>
-      <c r="DT6" s="29"/>
-      <c r="DU6" s="29"/>
-      <c r="DV6" s="29"/>
-      <c r="DW6" s="29"/>
-      <c r="DX6" s="29"/>
-      <c r="DY6" s="29"/>
-      <c r="DZ6" s="29"/>
-      <c r="EA6" s="29"/>
-      <c r="EB6" s="29"/>
-      <c r="EC6" s="29"/>
-      <c r="ED6" s="29"/>
-      <c r="EE6" s="29"/>
-      <c r="EF6" s="29"/>
-      <c r="EG6" s="29"/>
-      <c r="EH6" s="29"/>
-      <c r="EI6" s="29"/>
-      <c r="EJ6" s="29"/>
-      <c r="EK6" s="29"/>
-      <c r="EL6" s="29"/>
-      <c r="EM6" s="29"/>
-      <c r="EN6" s="29"/>
-      <c r="EO6" s="29"/>
-      <c r="EP6" s="29"/>
-      <c r="EQ6" s="29"/>
-      <c r="ER6" s="29"/>
-      <c r="ES6" s="29"/>
-      <c r="ET6" s="29"/>
-      <c r="EU6" s="29"/>
-      <c r="EV6" s="29"/>
-      <c r="EW6" s="29"/>
-      <c r="EX6" s="29"/>
-      <c r="EY6" s="29"/>
-      <c r="EZ6" s="29"/>
-      <c r="FA6" s="29"/>
-      <c r="FB6" s="29"/>
-      <c r="FC6" s="29"/>
-      <c r="FD6" s="29"/>
-      <c r="FE6" s="29"/>
-      <c r="FF6" s="29"/>
-      <c r="FG6" s="29"/>
-      <c r="FH6" s="29"/>
-      <c r="FI6" s="29"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="L6" s="25"/>
+      <c r="M6" s="25"/>
+      <c r="N6" s="25"/>
+      <c r="O6" s="25"/>
+      <c r="P6" s="25"/>
+      <c r="Q6" s="25"/>
+      <c r="R6" s="25"/>
+      <c r="S6" s="25"/>
+      <c r="T6" s="25"/>
+      <c r="U6" s="25"/>
+      <c r="V6" s="25"/>
+      <c r="W6" s="25"/>
+      <c r="X6" s="25"/>
+      <c r="Y6" s="25"/>
+      <c r="Z6" s="25"/>
+      <c r="AA6" s="25"/>
+      <c r="AB6" s="25"/>
+      <c r="AC6" s="25"/>
+      <c r="AD6" s="25"/>
+      <c r="AE6" s="25"/>
+      <c r="AF6" s="25"/>
+      <c r="AG6" s="25"/>
+      <c r="AH6" s="25"/>
+      <c r="AI6" s="25"/>
+      <c r="AJ6" s="25"/>
+      <c r="AK6" s="25"/>
+      <c r="AL6" s="25"/>
+      <c r="AM6" s="25"/>
+      <c r="AN6" s="25"/>
+      <c r="AO6" s="25"/>
+      <c r="AP6" s="25"/>
+      <c r="AQ6" s="25"/>
+      <c r="AR6" s="25"/>
+      <c r="AS6" s="25"/>
+      <c r="AT6" s="25"/>
+      <c r="AU6" s="25"/>
+      <c r="AV6" s="25"/>
+      <c r="AW6" s="25"/>
+      <c r="AX6" s="25"/>
+      <c r="AY6" s="25"/>
+      <c r="AZ6" s="25"/>
+      <c r="BA6" s="25"/>
+      <c r="BB6" s="25"/>
+      <c r="BC6" s="25"/>
+      <c r="BD6" s="25"/>
+      <c r="BE6" s="25"/>
+      <c r="BF6" s="25"/>
+      <c r="BG6" s="25"/>
+      <c r="BH6" s="25"/>
+      <c r="BI6" s="25"/>
+      <c r="BJ6" s="25"/>
+      <c r="BK6" s="25"/>
+      <c r="BL6" s="25"/>
+      <c r="BM6" s="25"/>
+      <c r="BN6" s="25"/>
+      <c r="BO6" s="25"/>
+      <c r="BP6" s="25"/>
+      <c r="BQ6" s="63"/>
+      <c r="BR6" s="63"/>
+      <c r="BS6" s="63"/>
+      <c r="BT6" s="63"/>
+      <c r="BU6" s="63"/>
+      <c r="BV6" s="63"/>
+      <c r="BW6" s="25"/>
+      <c r="BX6" s="25"/>
+      <c r="BY6" s="25"/>
+      <c r="BZ6" s="25"/>
+      <c r="CA6" s="25"/>
+      <c r="CB6" s="25"/>
+      <c r="CC6" s="25"/>
+      <c r="CD6" s="25"/>
+      <c r="CE6" s="25"/>
+      <c r="CF6" s="25"/>
+      <c r="CG6" s="25"/>
+      <c r="CH6" s="25"/>
+      <c r="CI6" s="25"/>
+      <c r="CJ6" s="25"/>
+      <c r="CK6" s="25"/>
+      <c r="CL6" s="25"/>
+      <c r="CM6" s="25"/>
+      <c r="CN6" s="25"/>
+      <c r="CO6" s="25"/>
+      <c r="CP6" s="25"/>
+      <c r="CQ6" s="25"/>
+      <c r="CR6" s="25"/>
+      <c r="CS6" s="25"/>
+      <c r="CT6" s="25"/>
+      <c r="CU6" s="25"/>
+      <c r="CV6" s="25"/>
+      <c r="CW6" s="25"/>
+      <c r="CX6" s="25"/>
+      <c r="CY6" s="25"/>
+      <c r="CZ6" s="25"/>
+      <c r="DA6" s="25"/>
+      <c r="DB6" s="25"/>
+      <c r="DC6" s="25"/>
+      <c r="DD6" s="25"/>
+      <c r="DE6" s="25"/>
+      <c r="DF6" s="25"/>
+      <c r="DG6" s="25"/>
+      <c r="DH6" s="25"/>
+      <c r="DI6" s="25"/>
+      <c r="DJ6" s="25"/>
+      <c r="DK6" s="25"/>
+      <c r="DL6" s="25"/>
+      <c r="DM6" s="25"/>
+      <c r="DN6" s="25"/>
+      <c r="DO6" s="25"/>
+      <c r="DP6" s="25"/>
+      <c r="DQ6" s="25"/>
+      <c r="DR6" s="25"/>
+      <c r="DS6" s="25"/>
+      <c r="DT6" s="25"/>
+      <c r="DU6" s="25"/>
+      <c r="DV6" s="25"/>
+      <c r="DW6" s="25"/>
+      <c r="DX6" s="25"/>
+      <c r="DY6" s="25"/>
+      <c r="DZ6" s="25"/>
+      <c r="EA6" s="25"/>
+      <c r="EB6" s="25"/>
+      <c r="EC6" s="25"/>
+      <c r="ED6" s="25"/>
+      <c r="EE6" s="25"/>
+      <c r="EF6" s="25"/>
+      <c r="EG6" s="25"/>
+      <c r="EH6" s="25"/>
+      <c r="EI6" s="25"/>
+      <c r="EJ6" s="25"/>
+      <c r="EK6" s="25"/>
+      <c r="EL6" s="25"/>
+      <c r="EM6" s="25"/>
+      <c r="EN6" s="25"/>
+      <c r="EO6" s="25"/>
+      <c r="EP6" s="25"/>
+      <c r="EQ6" s="25"/>
+      <c r="ER6" s="25"/>
+      <c r="ES6" s="25"/>
+      <c r="ET6" s="25"/>
+      <c r="EU6" s="25"/>
+      <c r="EV6" s="25"/>
+      <c r="EW6" s="25"/>
+      <c r="EX6" s="25"/>
+      <c r="EY6" s="25"/>
+      <c r="EZ6" s="25"/>
+      <c r="FA6" s="25"/>
+      <c r="FB6" s="25"/>
+      <c r="FC6" s="25"/>
+      <c r="FD6" s="25"/>
+      <c r="FE6" s="25"/>
+      <c r="FF6" s="25"/>
+      <c r="FG6" s="25"/>
+      <c r="FH6" s="25"/>
+      <c r="FI6" s="25"/>
     </row>
     <row r="7" spans="1:166" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="51" t="s">
+      <c r="A7" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="51"/>
-      <c r="C7" s="49">
+      <c r="B7" s="49"/>
+      <c r="C7" s="47">
         <v>10</v>
       </c>
-      <c r="D7" s="50"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="30"/>
-      <c r="K7" s="30"/>
-      <c r="L7" s="30"/>
-      <c r="M7" s="30"/>
-      <c r="N7" s="30"/>
-      <c r="O7" s="30"/>
-      <c r="P7" s="30"/>
-      <c r="Q7" s="30"/>
-      <c r="R7" s="30"/>
-      <c r="S7" s="30"/>
-      <c r="T7" s="30"/>
-      <c r="U7" s="30"/>
-      <c r="V7" s="30"/>
-      <c r="W7" s="30"/>
-      <c r="X7" s="30"/>
-      <c r="Y7" s="30"/>
-      <c r="Z7" s="30"/>
-      <c r="AA7" s="30"/>
-      <c r="AB7" s="30"/>
-      <c r="AC7" s="30"/>
-      <c r="AD7" s="30"/>
-      <c r="AE7" s="30"/>
-      <c r="AF7" s="30"/>
-      <c r="AG7" s="30"/>
-      <c r="AH7" s="30"/>
-      <c r="AI7" s="30"/>
-      <c r="AJ7" s="30"/>
-      <c r="AK7" s="30"/>
-      <c r="AL7" s="30"/>
-      <c r="AM7" s="30"/>
-      <c r="AN7" s="30"/>
-      <c r="AO7" s="30"/>
-      <c r="AP7" s="30"/>
-      <c r="AQ7" s="30"/>
-      <c r="AR7" s="30"/>
-      <c r="AS7" s="30"/>
-      <c r="AT7" s="30"/>
-      <c r="AU7" s="30"/>
-      <c r="AV7" s="30"/>
-      <c r="AW7" s="30"/>
-      <c r="AX7" s="30"/>
-      <c r="AY7" s="30"/>
-      <c r="AZ7" s="30"/>
-      <c r="BA7" s="30"/>
-      <c r="BB7" s="30"/>
-      <c r="BC7" s="30"/>
-      <c r="BD7" s="30"/>
-      <c r="BE7" s="30"/>
-      <c r="BF7" s="30"/>
-      <c r="BG7" s="30"/>
-      <c r="BH7" s="30"/>
-      <c r="BI7" s="30"/>
-      <c r="BJ7" s="30"/>
-      <c r="BK7" s="30"/>
-      <c r="BL7" s="30"/>
-      <c r="BM7" s="30"/>
-      <c r="BN7" s="30"/>
-      <c r="BO7" s="30"/>
-      <c r="BP7" s="30"/>
-      <c r="BQ7" s="30"/>
-      <c r="BR7" s="30"/>
-      <c r="BS7" s="30"/>
-      <c r="BT7" s="30"/>
-      <c r="BU7" s="30"/>
-      <c r="BV7" s="30"/>
-      <c r="BW7" s="30"/>
-      <c r="BX7" s="30"/>
-      <c r="BY7" s="30"/>
-      <c r="BZ7" s="30"/>
-      <c r="CA7" s="30"/>
-      <c r="CB7" s="30"/>
-      <c r="CC7" s="30"/>
-      <c r="CD7" s="30"/>
-      <c r="CE7" s="30"/>
-      <c r="CF7" s="30"/>
-      <c r="CG7" s="30"/>
-      <c r="CH7" s="30"/>
-      <c r="CI7" s="30"/>
-      <c r="CJ7" s="30"/>
-      <c r="CK7" s="30"/>
-      <c r="CL7" s="30"/>
-      <c r="CM7" s="30"/>
-      <c r="CN7" s="30"/>
-      <c r="CO7" s="30"/>
-      <c r="CP7" s="30"/>
-      <c r="CQ7" s="30"/>
-      <c r="CR7" s="30"/>
-      <c r="CS7" s="30"/>
-      <c r="CT7" s="30"/>
-      <c r="CU7" s="30"/>
-      <c r="CV7" s="30"/>
-      <c r="CW7" s="30"/>
-      <c r="CX7" s="30"/>
-      <c r="CY7" s="30"/>
-      <c r="CZ7" s="30"/>
-      <c r="DA7" s="30"/>
-      <c r="DB7" s="30"/>
-      <c r="DC7" s="30"/>
-      <c r="DD7" s="30"/>
-      <c r="DE7" s="30"/>
-      <c r="DF7" s="30"/>
-      <c r="DG7" s="30"/>
-      <c r="DH7" s="30"/>
-      <c r="DI7" s="30"/>
-      <c r="DJ7" s="30"/>
-      <c r="DK7" s="30"/>
-      <c r="DL7" s="30"/>
-      <c r="DM7" s="30"/>
-      <c r="DN7" s="30"/>
-      <c r="DO7" s="30"/>
-      <c r="DP7" s="30"/>
-      <c r="DQ7" s="30"/>
-      <c r="DR7" s="30"/>
-      <c r="DS7" s="30"/>
-      <c r="DT7" s="30"/>
-      <c r="DU7" s="30"/>
-      <c r="DV7" s="30"/>
-      <c r="DW7" s="30"/>
-      <c r="DX7" s="30"/>
-      <c r="DY7" s="30"/>
-      <c r="DZ7" s="30"/>
-      <c r="EA7" s="30"/>
-      <c r="EB7" s="30"/>
-      <c r="EC7" s="30"/>
-      <c r="ED7" s="30"/>
-      <c r="EE7" s="30"/>
-      <c r="EF7" s="30"/>
-      <c r="EG7" s="30"/>
-      <c r="EH7" s="30"/>
-      <c r="EI7" s="30"/>
-      <c r="EJ7" s="30"/>
-      <c r="EK7" s="30"/>
-      <c r="EL7" s="30"/>
-      <c r="EM7" s="30"/>
-      <c r="EN7" s="30"/>
-      <c r="EO7" s="30"/>
-      <c r="EP7" s="30"/>
-      <c r="EQ7" s="30"/>
-      <c r="ER7" s="30"/>
-      <c r="ES7" s="30"/>
-      <c r="ET7" s="30"/>
-      <c r="EU7" s="30"/>
-      <c r="EV7" s="30"/>
-      <c r="EW7" s="30"/>
-      <c r="EX7" s="30"/>
-      <c r="EY7" s="30"/>
-      <c r="EZ7" s="30"/>
-      <c r="FA7" s="30"/>
-      <c r="FB7" s="30"/>
-      <c r="FC7" s="30"/>
-      <c r="FD7" s="30"/>
-      <c r="FE7" s="30"/>
-      <c r="FF7" s="30"/>
-      <c r="FG7" s="30"/>
-      <c r="FH7" s="30"/>
-      <c r="FI7" s="30"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="26"/>
+      <c r="N7" s="26"/>
+      <c r="O7" s="26"/>
+      <c r="P7" s="26"/>
+      <c r="Q7" s="26"/>
+      <c r="R7" s="26"/>
+      <c r="S7" s="26"/>
+      <c r="T7" s="26"/>
+      <c r="U7" s="26"/>
+      <c r="V7" s="26"/>
+      <c r="W7" s="26"/>
+      <c r="X7" s="26"/>
+      <c r="Y7" s="26"/>
+      <c r="Z7" s="26"/>
+      <c r="AA7" s="26"/>
+      <c r="AB7" s="26"/>
+      <c r="AC7" s="26"/>
+      <c r="AD7" s="26"/>
+      <c r="AE7" s="26"/>
+      <c r="AF7" s="26"/>
+      <c r="AG7" s="26"/>
+      <c r="AH7" s="26"/>
+      <c r="AI7" s="26"/>
+      <c r="AJ7" s="26"/>
+      <c r="AK7" s="26"/>
+      <c r="AL7" s="26"/>
+      <c r="AM7" s="26"/>
+      <c r="AN7" s="26"/>
+      <c r="AO7" s="26"/>
+      <c r="AP7" s="26"/>
+      <c r="AQ7" s="26"/>
+      <c r="AR7" s="26"/>
+      <c r="AS7" s="26"/>
+      <c r="AT7" s="26"/>
+      <c r="AU7" s="26"/>
+      <c r="AV7" s="26"/>
+      <c r="AW7" s="26"/>
+      <c r="AX7" s="26"/>
+      <c r="AY7" s="26"/>
+      <c r="AZ7" s="26"/>
+      <c r="BA7" s="26"/>
+      <c r="BB7" s="26"/>
+      <c r="BC7" s="26"/>
+      <c r="BD7" s="26"/>
+      <c r="BE7" s="26"/>
+      <c r="BF7" s="26"/>
+      <c r="BG7" s="26"/>
+      <c r="BH7" s="26"/>
+      <c r="BI7" s="26"/>
+      <c r="BJ7" s="26"/>
+      <c r="BK7" s="26"/>
+      <c r="BL7" s="26"/>
+      <c r="BM7" s="26"/>
+      <c r="BN7" s="26"/>
+      <c r="BO7" s="26"/>
+      <c r="BP7" s="26"/>
+      <c r="BQ7" s="64"/>
+      <c r="BR7" s="64"/>
+      <c r="BS7" s="64"/>
+      <c r="BT7" s="64"/>
+      <c r="BU7" s="64"/>
+      <c r="BV7" s="64"/>
+      <c r="BW7" s="26"/>
+      <c r="BX7" s="26"/>
+      <c r="BY7" s="26"/>
+      <c r="BZ7" s="26"/>
+      <c r="CA7" s="26"/>
+      <c r="CB7" s="26"/>
+      <c r="CC7" s="26"/>
+      <c r="CD7" s="26"/>
+      <c r="CE7" s="26"/>
+      <c r="CF7" s="26"/>
+      <c r="CG7" s="26"/>
+      <c r="CH7" s="26"/>
+      <c r="CI7" s="26"/>
+      <c r="CJ7" s="26"/>
+      <c r="CK7" s="26"/>
+      <c r="CL7" s="26"/>
+      <c r="CM7" s="26"/>
+      <c r="CN7" s="26"/>
+      <c r="CO7" s="26"/>
+      <c r="CP7" s="26"/>
+      <c r="CQ7" s="26"/>
+      <c r="CR7" s="26"/>
+      <c r="CS7" s="26"/>
+      <c r="CT7" s="26"/>
+      <c r="CU7" s="26"/>
+      <c r="CV7" s="26"/>
+      <c r="CW7" s="26"/>
+      <c r="CX7" s="26"/>
+      <c r="CY7" s="26"/>
+      <c r="CZ7" s="26"/>
+      <c r="DA7" s="26"/>
+      <c r="DB7" s="26"/>
+      <c r="DC7" s="26"/>
+      <c r="DD7" s="26"/>
+      <c r="DE7" s="26"/>
+      <c r="DF7" s="26"/>
+      <c r="DG7" s="26"/>
+      <c r="DH7" s="26"/>
+      <c r="DI7" s="26"/>
+      <c r="DJ7" s="26"/>
+      <c r="DK7" s="26"/>
+      <c r="DL7" s="26"/>
+      <c r="DM7" s="26"/>
+      <c r="DN7" s="26"/>
+      <c r="DO7" s="26"/>
+      <c r="DP7" s="26"/>
+      <c r="DQ7" s="26"/>
+      <c r="DR7" s="26"/>
+      <c r="DS7" s="26"/>
+      <c r="DT7" s="26"/>
+      <c r="DU7" s="26"/>
+      <c r="DV7" s="26"/>
+      <c r="DW7" s="26"/>
+      <c r="DX7" s="26"/>
+      <c r="DY7" s="26"/>
+      <c r="DZ7" s="26"/>
+      <c r="EA7" s="26"/>
+      <c r="EB7" s="26"/>
+      <c r="EC7" s="26"/>
+      <c r="ED7" s="26"/>
+      <c r="EE7" s="26"/>
+      <c r="EF7" s="26"/>
+      <c r="EG7" s="26"/>
+      <c r="EH7" s="26"/>
+      <c r="EI7" s="26"/>
+      <c r="EJ7" s="26"/>
+      <c r="EK7" s="26"/>
+      <c r="EL7" s="26"/>
+      <c r="EM7" s="26"/>
+      <c r="EN7" s="26"/>
+      <c r="EO7" s="26"/>
+      <c r="EP7" s="26"/>
+      <c r="EQ7" s="26"/>
+      <c r="ER7" s="26"/>
+      <c r="ES7" s="26"/>
+      <c r="ET7" s="26"/>
+      <c r="EU7" s="26"/>
+      <c r="EV7" s="26"/>
+      <c r="EW7" s="26"/>
+      <c r="EX7" s="26"/>
+      <c r="EY7" s="26"/>
+      <c r="EZ7" s="26"/>
+      <c r="FA7" s="26"/>
+      <c r="FB7" s="26"/>
+      <c r="FC7" s="26"/>
+      <c r="FD7" s="26"/>
+      <c r="FE7" s="26"/>
+      <c r="FF7" s="26"/>
+      <c r="FG7" s="26"/>
+      <c r="FH7" s="26"/>
+      <c r="FI7" s="26"/>
     </row>
     <row r="8" spans="1:166" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="31">
+      <c r="B8" s="50"/>
+      <c r="C8" s="51">
         <f>SUM(C5:D7)</f>
         <v>175</v>
       </c>
-      <c r="D8" s="34"/>
+      <c r="D8" s="45"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="27">
-        <v>1</v>
-      </c>
-      <c r="G8" s="27">
+      <c r="F8" s="23">
+        <v>1</v>
+      </c>
+      <c r="G8" s="23">
         <v>2</v>
       </c>
-      <c r="H8" s="27">
+      <c r="H8" s="23">
         <v>3</v>
       </c>
-      <c r="I8" s="27">
+      <c r="I8" s="23">
         <v>4</v>
       </c>
-      <c r="J8" s="27">
+      <c r="J8" s="23">
         <v>5</v>
       </c>
-      <c r="K8" s="27">
+      <c r="K8" s="23">
         <v>6</v>
       </c>
-      <c r="L8" s="27">
+      <c r="L8" s="23">
         <v>7</v>
       </c>
-      <c r="M8" s="27">
+      <c r="M8" s="23">
         <v>8</v>
       </c>
-      <c r="N8" s="27">
+      <c r="N8" s="23">
         <v>9</v>
       </c>
-      <c r="O8" s="27">
+      <c r="O8" s="23">
         <v>10</v>
       </c>
-      <c r="P8" s="27">
+      <c r="P8" s="23">
         <v>11</v>
       </c>
-      <c r="Q8" s="27">
+      <c r="Q8" s="23">
         <v>12</v>
       </c>
-      <c r="R8" s="27">
+      <c r="R8" s="23">
         <v>13</v>
       </c>
-      <c r="S8" s="27">
+      <c r="S8" s="23">
         <v>14</v>
       </c>
-      <c r="T8" s="27">
+      <c r="T8" s="23">
         <v>15</v>
       </c>
-      <c r="U8" s="27">
+      <c r="U8" s="23">
         <v>16</v>
       </c>
-      <c r="V8" s="27">
+      <c r="V8" s="23">
         <v>17</v>
       </c>
-      <c r="W8" s="27">
+      <c r="W8" s="23">
         <v>18</v>
       </c>
-      <c r="X8" s="27">
+      <c r="X8" s="23">
         <v>19</v>
       </c>
-      <c r="Y8" s="27">
+      <c r="Y8" s="23">
         <v>20</v>
       </c>
-      <c r="Z8" s="27">
+      <c r="Z8" s="23">
         <v>21</v>
       </c>
-      <c r="AA8" s="27">
+      <c r="AA8" s="23">
         <v>22</v>
       </c>
-      <c r="AB8" s="27">
+      <c r="AB8" s="23">
         <v>23</v>
       </c>
-      <c r="AC8" s="27">
+      <c r="AC8" s="23">
         <v>24</v>
       </c>
-      <c r="AD8" s="27">
+      <c r="AD8" s="23">
         <v>25</v>
       </c>
-      <c r="AE8" s="27">
+      <c r="AE8" s="23">
         <v>26</v>
       </c>
-      <c r="AF8" s="27">
+      <c r="AF8" s="23">
         <v>27</v>
       </c>
-      <c r="AG8" s="27">
+      <c r="AG8" s="23">
         <v>28</v>
       </c>
-      <c r="AH8" s="27">
+      <c r="AH8" s="23">
         <v>29</v>
       </c>
-      <c r="AI8" s="27">
+      <c r="AI8" s="23">
         <v>30</v>
       </c>
-      <c r="AJ8" s="27">
+      <c r="AJ8" s="23">
         <v>31</v>
       </c>
-      <c r="AK8" s="27">
+      <c r="AK8" s="23">
         <v>32</v>
       </c>
-      <c r="AL8" s="27">
+      <c r="AL8" s="23">
         <v>33</v>
       </c>
-      <c r="AM8" s="27">
+      <c r="AM8" s="23">
         <v>34</v>
       </c>
-      <c r="AN8" s="27">
+      <c r="AN8" s="23">
         <v>35</v>
       </c>
-      <c r="AO8" s="27">
+      <c r="AO8" s="23">
         <v>36</v>
       </c>
-      <c r="AP8" s="27">
+      <c r="AP8" s="23">
         <v>37</v>
       </c>
-      <c r="AQ8" s="27">
+      <c r="AQ8" s="23">
         <v>38</v>
       </c>
-      <c r="AR8" s="27">
+      <c r="AR8" s="23">
         <v>39</v>
       </c>
-      <c r="AS8" s="27">
+      <c r="AS8" s="23">
         <v>40</v>
       </c>
-      <c r="AT8" s="27">
+      <c r="AT8" s="23">
         <v>41</v>
       </c>
-      <c r="AU8" s="27">
+      <c r="AU8" s="23">
         <v>42</v>
       </c>
-      <c r="AV8" s="27">
+      <c r="AV8" s="23">
         <v>43</v>
       </c>
-      <c r="AW8" s="27">
+      <c r="AW8" s="23">
         <v>44</v>
       </c>
-      <c r="AX8" s="27">
+      <c r="AX8" s="23">
         <v>45</v>
       </c>
-      <c r="AY8" s="27">
+      <c r="AY8" s="23">
         <v>46</v>
       </c>
-      <c r="AZ8" s="27">
+      <c r="AZ8" s="23">
         <v>47</v>
       </c>
-      <c r="BA8" s="27">
+      <c r="BA8" s="23">
         <v>48</v>
       </c>
-      <c r="BB8" s="27">
+      <c r="BB8" s="23">
         <v>49</v>
       </c>
-      <c r="BC8" s="27">
+      <c r="BC8" s="23">
         <v>50</v>
       </c>
-      <c r="BD8" s="27">
+      <c r="BD8" s="23">
         <v>51</v>
       </c>
-      <c r="BE8" s="27">
+      <c r="BE8" s="23">
         <v>52</v>
       </c>
-      <c r="BF8" s="27">
+      <c r="BF8" s="23">
         <v>53</v>
       </c>
-      <c r="BG8" s="27">
+      <c r="BG8" s="23">
         <v>54</v>
       </c>
-      <c r="BH8" s="27">
+      <c r="BH8" s="23">
         <v>55</v>
       </c>
-      <c r="BI8" s="27">
+      <c r="BI8" s="23">
         <v>56</v>
       </c>
-      <c r="BJ8" s="27">
+      <c r="BJ8" s="23">
         <v>57</v>
       </c>
-      <c r="BK8" s="27">
+      <c r="BK8" s="23">
         <v>58</v>
       </c>
-      <c r="BL8" s="27">
+      <c r="BL8" s="23">
         <v>59</v>
       </c>
-      <c r="BM8" s="27">
+      <c r="BM8" s="23">
         <v>60</v>
       </c>
-      <c r="BN8" s="27">
+      <c r="BN8" s="23">
         <v>61</v>
       </c>
-      <c r="BO8" s="27">
+      <c r="BO8" s="23">
         <v>62</v>
       </c>
-      <c r="BP8" s="27">
+      <c r="BP8" s="23">
         <v>63</v>
       </c>
-      <c r="BQ8" s="27">
+      <c r="BQ8" s="23">
         <v>64</v>
       </c>
-      <c r="BR8" s="27">
+      <c r="BR8" s="23">
         <v>65</v>
       </c>
-      <c r="BS8" s="27">
+      <c r="BS8" s="23">
         <v>66</v>
       </c>
-      <c r="BT8" s="27">
+      <c r="BT8" s="23">
         <v>67</v>
       </c>
-      <c r="BU8" s="27">
+      <c r="BU8" s="23">
         <v>68</v>
       </c>
-      <c r="BV8" s="27">
+      <c r="BV8" s="23">
         <v>69</v>
       </c>
-      <c r="BW8" s="27">
+      <c r="BW8" s="23">
         <v>70</v>
       </c>
-      <c r="BX8" s="27">
+      <c r="BX8" s="23">
         <v>71</v>
       </c>
-      <c r="BY8" s="27">
+      <c r="BY8" s="23">
         <v>72</v>
       </c>
-      <c r="BZ8" s="27">
+      <c r="BZ8" s="23">
         <v>73</v>
       </c>
-      <c r="CA8" s="27">
+      <c r="CA8" s="23">
         <v>74</v>
       </c>
-      <c r="CB8" s="27">
+      <c r="CB8" s="23">
         <v>75</v>
       </c>
-      <c r="CC8" s="27">
+      <c r="CC8" s="23">
         <v>76</v>
       </c>
-      <c r="CD8" s="27">
+      <c r="CD8" s="23">
         <v>77</v>
       </c>
-      <c r="CE8" s="27">
+      <c r="CE8" s="23">
         <v>78</v>
       </c>
-      <c r="CF8" s="27">
+      <c r="CF8" s="23">
         <v>79</v>
       </c>
-      <c r="CG8" s="27">
+      <c r="CG8" s="23">
         <v>80</v>
       </c>
-      <c r="CH8" s="27">
+      <c r="CH8" s="23">
         <v>81</v>
       </c>
-      <c r="CI8" s="27">
+      <c r="CI8" s="23">
         <v>82</v>
       </c>
-      <c r="CJ8" s="27">
+      <c r="CJ8" s="23">
         <v>83</v>
       </c>
-      <c r="CK8" s="27">
+      <c r="CK8" s="23">
         <v>84</v>
       </c>
-      <c r="CL8" s="27">
+      <c r="CL8" s="23">
         <v>85</v>
       </c>
-      <c r="CM8" s="27">
+      <c r="CM8" s="23">
         <v>86</v>
       </c>
-      <c r="CN8" s="27">
+      <c r="CN8" s="23">
         <v>87</v>
       </c>
-      <c r="CO8" s="27">
+      <c r="CO8" s="23">
         <v>88</v>
       </c>
-      <c r="CP8" s="27">
+      <c r="CP8" s="23">
         <v>89</v>
       </c>
-      <c r="CQ8" s="27">
+      <c r="CQ8" s="23">
         <v>90</v>
       </c>
-      <c r="CR8" s="27">
+      <c r="CR8" s="23">
         <v>91</v>
       </c>
-      <c r="CS8" s="27">
+      <c r="CS8" s="23">
         <v>92</v>
       </c>
-      <c r="CT8" s="27">
+      <c r="CT8" s="23">
         <v>93</v>
       </c>
-      <c r="CU8" s="27">
+      <c r="CU8" s="23">
         <v>94</v>
       </c>
-      <c r="CV8" s="27">
+      <c r="CV8" s="23">
         <v>95</v>
       </c>
-      <c r="CW8" s="27">
+      <c r="CW8" s="23">
         <v>96</v>
       </c>
-      <c r="CX8" s="27">
+      <c r="CX8" s="23">
         <v>97</v>
       </c>
-      <c r="CY8" s="27">
+      <c r="CY8" s="23">
         <v>98</v>
       </c>
-      <c r="CZ8" s="27">
+      <c r="CZ8" s="23">
         <v>99</v>
       </c>
-      <c r="DA8" s="27">
+      <c r="DA8" s="23">
         <v>100</v>
       </c>
-      <c r="DB8" s="27">
+      <c r="DB8" s="23">
         <v>101</v>
       </c>
-      <c r="DC8" s="27">
+      <c r="DC8" s="23">
         <v>102</v>
       </c>
-      <c r="DD8" s="27">
+      <c r="DD8" s="23">
         <v>103</v>
       </c>
-      <c r="DE8" s="27">
+      <c r="DE8" s="23">
         <v>104</v>
       </c>
-      <c r="DF8" s="27">
+      <c r="DF8" s="23">
         <v>105</v>
       </c>
-      <c r="DG8" s="27">
+      <c r="DG8" s="23">
         <v>106</v>
       </c>
-      <c r="DH8" s="27">
+      <c r="DH8" s="23">
         <v>107</v>
       </c>
-      <c r="DI8" s="27">
+      <c r="DI8" s="23">
         <v>108</v>
       </c>
-      <c r="DJ8" s="27">
+      <c r="DJ8" s="23">
         <v>109</v>
       </c>
-      <c r="DK8" s="27">
+      <c r="DK8" s="23">
         <v>110</v>
       </c>
-      <c r="DL8" s="27">
+      <c r="DL8" s="23">
         <v>111</v>
       </c>
-      <c r="DM8" s="27">
+      <c r="DM8" s="23">
         <v>112</v>
       </c>
-      <c r="DN8" s="27">
+      <c r="DN8" s="23">
         <v>113</v>
       </c>
-      <c r="DO8" s="27">
+      <c r="DO8" s="23">
         <v>114</v>
       </c>
-      <c r="DP8" s="27">
+      <c r="DP8" s="23">
         <v>115</v>
       </c>
-      <c r="DQ8" s="27">
+      <c r="DQ8" s="23">
         <v>116</v>
       </c>
-      <c r="DR8" s="27">
+      <c r="DR8" s="23">
         <v>117</v>
       </c>
-      <c r="DS8" s="27">
+      <c r="DS8" s="23">
         <v>118</v>
       </c>
-      <c r="DT8" s="27">
+      <c r="DT8" s="23">
         <v>119</v>
       </c>
-      <c r="DU8" s="27">
+      <c r="DU8" s="23">
         <v>120</v>
       </c>
-      <c r="DV8" s="27">
+      <c r="DV8" s="23">
         <v>121</v>
       </c>
-      <c r="DW8" s="27">
+      <c r="DW8" s="23">
         <v>122</v>
       </c>
-      <c r="DX8" s="27">
+      <c r="DX8" s="23">
         <v>123</v>
       </c>
-      <c r="DY8" s="27">
+      <c r="DY8" s="23">
         <v>124</v>
       </c>
-      <c r="DZ8" s="27">
+      <c r="DZ8" s="23">
         <v>125</v>
       </c>
-      <c r="EA8" s="27">
+      <c r="EA8" s="23">
         <v>126</v>
       </c>
-      <c r="EB8" s="27">
+      <c r="EB8" s="23">
         <v>127</v>
       </c>
-      <c r="EC8" s="27">
+      <c r="EC8" s="23">
         <v>128</v>
       </c>
-      <c r="ED8" s="27">
+      <c r="ED8" s="23">
         <v>129</v>
       </c>
-      <c r="EE8" s="27">
+      <c r="EE8" s="23">
         <v>130</v>
       </c>
-      <c r="EF8" s="27">
+      <c r="EF8" s="23">
         <v>131</v>
       </c>
-      <c r="EG8" s="27">
+      <c r="EG8" s="23">
         <v>132</v>
       </c>
-      <c r="EH8" s="27">
+      <c r="EH8" s="23">
         <v>133</v>
       </c>
-      <c r="EI8" s="27">
+      <c r="EI8" s="23">
         <v>134</v>
       </c>
-      <c r="EJ8" s="27">
+      <c r="EJ8" s="23">
         <v>135</v>
       </c>
-      <c r="EK8" s="27">
+      <c r="EK8" s="23">
         <v>136</v>
       </c>
-      <c r="EL8" s="27">
+      <c r="EL8" s="23">
         <v>137</v>
       </c>
-      <c r="EM8" s="27">
+      <c r="EM8" s="23">
         <v>138</v>
       </c>
-      <c r="EN8" s="27">
+      <c r="EN8" s="23">
         <v>139</v>
       </c>
-      <c r="EO8" s="27">
+      <c r="EO8" s="23">
         <v>140</v>
       </c>
-      <c r="EP8" s="27">
+      <c r="EP8" s="23">
         <v>141</v>
       </c>
-      <c r="EQ8" s="27">
+      <c r="EQ8" s="23">
         <v>142</v>
       </c>
-      <c r="ER8" s="27">
+      <c r="ER8" s="23">
         <v>143</v>
       </c>
-      <c r="ES8" s="27">
+      <c r="ES8" s="23">
         <v>144</v>
       </c>
-      <c r="ET8" s="27">
+      <c r="ET8" s="23">
         <v>145</v>
       </c>
-      <c r="EU8" s="27">
+      <c r="EU8" s="23">
         <v>146</v>
       </c>
-      <c r="EV8" s="27">
+      <c r="EV8" s="23">
         <v>147</v>
       </c>
-      <c r="EW8" s="27">
+      <c r="EW8" s="23">
         <v>148</v>
       </c>
-      <c r="EX8" s="27">
+      <c r="EX8" s="23">
         <v>149</v>
       </c>
-      <c r="EY8" s="27">
+      <c r="EY8" s="23">
         <v>150</v>
       </c>
-      <c r="EZ8" s="27">
+      <c r="EZ8" s="23">
         <v>151</v>
       </c>
-      <c r="FA8" s="27">
+      <c r="FA8" s="23">
         <v>152</v>
       </c>
-      <c r="FB8" s="27">
+      <c r="FB8" s="23">
         <v>153</v>
       </c>
-      <c r="FC8" s="27">
+      <c r="FC8" s="23">
         <v>154</v>
       </c>
-      <c r="FD8" s="27">
+      <c r="FD8" s="23">
         <v>155</v>
       </c>
-      <c r="FE8" s="27">
+      <c r="FE8" s="23">
         <v>156</v>
       </c>
-      <c r="FF8" s="27">
+      <c r="FF8" s="23">
         <v>157</v>
       </c>
-      <c r="FG8" s="27">
+      <c r="FG8" s="23">
         <v>158</v>
       </c>
-      <c r="FH8" s="27">
+      <c r="FH8" s="23">
         <v>159</v>
       </c>
-      <c r="FI8" s="27">
+      <c r="FI8" s="23">
         <v>160</v>
       </c>
     </row>
     <row r="9" spans="1:166" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="35" t="s">
+      <c r="A9" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="36" t="s">
+      <c r="B9" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="37" t="s">
+      <c r="C9" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="36"/>
+      <c r="D9" s="52"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="28"/>
-      <c r="J9" s="28"/>
-      <c r="K9" s="28"/>
-      <c r="L9" s="28"/>
-      <c r="M9" s="28"/>
-      <c r="N9" s="28"/>
-      <c r="O9" s="28"/>
-      <c r="P9" s="28"/>
-      <c r="Q9" s="28"/>
-      <c r="R9" s="28"/>
-      <c r="S9" s="28"/>
-      <c r="T9" s="28"/>
-      <c r="U9" s="28"/>
-      <c r="V9" s="28"/>
-      <c r="W9" s="28"/>
-      <c r="X9" s="28"/>
-      <c r="Y9" s="28"/>
-      <c r="Z9" s="28"/>
-      <c r="AA9" s="28"/>
-      <c r="AB9" s="28"/>
-      <c r="AC9" s="28"/>
-      <c r="AD9" s="28"/>
-      <c r="AE9" s="28"/>
-      <c r="AF9" s="28"/>
-      <c r="AG9" s="28"/>
-      <c r="AH9" s="28"/>
-      <c r="AI9" s="28"/>
-      <c r="AJ9" s="28"/>
-      <c r="AK9" s="28"/>
-      <c r="AL9" s="28"/>
-      <c r="AM9" s="28"/>
-      <c r="AN9" s="28"/>
-      <c r="AO9" s="28"/>
-      <c r="AP9" s="28"/>
-      <c r="AQ9" s="28"/>
-      <c r="AR9" s="28"/>
-      <c r="AS9" s="28"/>
-      <c r="AT9" s="28"/>
-      <c r="AU9" s="28"/>
-      <c r="AV9" s="28"/>
-      <c r="AW9" s="28"/>
-      <c r="AX9" s="28"/>
-      <c r="AY9" s="28"/>
-      <c r="AZ9" s="28"/>
-      <c r="BA9" s="28"/>
-      <c r="BB9" s="28"/>
-      <c r="BC9" s="28"/>
-      <c r="BD9" s="28"/>
-      <c r="BE9" s="28"/>
-      <c r="BF9" s="28"/>
-      <c r="BG9" s="28"/>
-      <c r="BH9" s="28"/>
-      <c r="BI9" s="28"/>
-      <c r="BJ9" s="28"/>
-      <c r="BK9" s="28"/>
-      <c r="BL9" s="28"/>
-      <c r="BM9" s="28"/>
-      <c r="BN9" s="28"/>
-      <c r="BO9" s="28"/>
-      <c r="BP9" s="28"/>
-      <c r="BQ9" s="28"/>
-      <c r="BR9" s="28"/>
-      <c r="BS9" s="28"/>
-      <c r="BT9" s="28"/>
-      <c r="BU9" s="28"/>
-      <c r="BV9" s="28"/>
-      <c r="BW9" s="28"/>
-      <c r="BX9" s="28"/>
-      <c r="BY9" s="28"/>
-      <c r="BZ9" s="28"/>
-      <c r="CA9" s="28"/>
-      <c r="CB9" s="28"/>
-      <c r="CC9" s="28"/>
-      <c r="CD9" s="28"/>
-      <c r="CE9" s="28"/>
-      <c r="CF9" s="28"/>
-      <c r="CG9" s="28"/>
-      <c r="CH9" s="28"/>
-      <c r="CI9" s="28"/>
-      <c r="CJ9" s="28"/>
-      <c r="CK9" s="28"/>
-      <c r="CL9" s="28"/>
-      <c r="CM9" s="28"/>
-      <c r="CN9" s="28"/>
-      <c r="CO9" s="28"/>
-      <c r="CP9" s="28"/>
-      <c r="CQ9" s="28"/>
-      <c r="CR9" s="28"/>
-      <c r="CS9" s="28"/>
-      <c r="CT9" s="28"/>
-      <c r="CU9" s="28"/>
-      <c r="CV9" s="28"/>
-      <c r="CW9" s="28"/>
-      <c r="CX9" s="28"/>
-      <c r="CY9" s="28"/>
-      <c r="CZ9" s="28"/>
-      <c r="DA9" s="28"/>
-      <c r="DB9" s="28"/>
-      <c r="DC9" s="28"/>
-      <c r="DD9" s="28"/>
-      <c r="DE9" s="28"/>
-      <c r="DF9" s="28"/>
-      <c r="DG9" s="28"/>
-      <c r="DH9" s="28"/>
-      <c r="DI9" s="28"/>
-      <c r="DJ9" s="28"/>
-      <c r="DK9" s="28"/>
-      <c r="DL9" s="28"/>
-      <c r="DM9" s="28"/>
-      <c r="DN9" s="28"/>
-      <c r="DO9" s="28"/>
-      <c r="DP9" s="28"/>
-      <c r="DQ9" s="28"/>
-      <c r="DR9" s="28"/>
-      <c r="DS9" s="28"/>
-      <c r="DT9" s="28"/>
-      <c r="DU9" s="28"/>
-      <c r="DV9" s="28"/>
-      <c r="DW9" s="28"/>
-      <c r="DX9" s="28"/>
-      <c r="DY9" s="28"/>
-      <c r="DZ9" s="28"/>
-      <c r="EA9" s="28"/>
-      <c r="EB9" s="28"/>
-      <c r="EC9" s="28"/>
-      <c r="ED9" s="28"/>
-      <c r="EE9" s="28"/>
-      <c r="EF9" s="28"/>
-      <c r="EG9" s="28"/>
-      <c r="EH9" s="28"/>
-      <c r="EI9" s="28"/>
-      <c r="EJ9" s="28"/>
-      <c r="EK9" s="28"/>
-      <c r="EL9" s="28"/>
-      <c r="EM9" s="28"/>
-      <c r="EN9" s="28"/>
-      <c r="EO9" s="28"/>
-      <c r="EP9" s="28"/>
-      <c r="EQ9" s="28"/>
-      <c r="ER9" s="28"/>
-      <c r="ES9" s="28"/>
-      <c r="ET9" s="28"/>
-      <c r="EU9" s="28"/>
-      <c r="EV9" s="28"/>
-      <c r="EW9" s="28"/>
-      <c r="EX9" s="28"/>
-      <c r="EY9" s="28"/>
-      <c r="EZ9" s="28"/>
-      <c r="FA9" s="28"/>
-      <c r="FB9" s="28"/>
-      <c r="FC9" s="28"/>
-      <c r="FD9" s="28"/>
-      <c r="FE9" s="28"/>
-      <c r="FF9" s="28"/>
-      <c r="FG9" s="28"/>
-      <c r="FH9" s="28"/>
-      <c r="FI9" s="28"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="24"/>
+      <c r="M9" s="24"/>
+      <c r="N9" s="24"/>
+      <c r="O9" s="24"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="24"/>
+      <c r="R9" s="24"/>
+      <c r="S9" s="24"/>
+      <c r="T9" s="24"/>
+      <c r="U9" s="24"/>
+      <c r="V9" s="24"/>
+      <c r="W9" s="24"/>
+      <c r="X9" s="24"/>
+      <c r="Y9" s="24"/>
+      <c r="Z9" s="24"/>
+      <c r="AA9" s="24"/>
+      <c r="AB9" s="24"/>
+      <c r="AC9" s="24"/>
+      <c r="AD9" s="24"/>
+      <c r="AE9" s="24"/>
+      <c r="AF9" s="24"/>
+      <c r="AG9" s="24"/>
+      <c r="AH9" s="24"/>
+      <c r="AI9" s="24"/>
+      <c r="AJ9" s="24"/>
+      <c r="AK9" s="24"/>
+      <c r="AL9" s="24"/>
+      <c r="AM9" s="24"/>
+      <c r="AN9" s="24"/>
+      <c r="AO9" s="24"/>
+      <c r="AP9" s="24"/>
+      <c r="AQ9" s="24"/>
+      <c r="AR9" s="24"/>
+      <c r="AS9" s="24"/>
+      <c r="AT9" s="24"/>
+      <c r="AU9" s="24"/>
+      <c r="AV9" s="24"/>
+      <c r="AW9" s="24"/>
+      <c r="AX9" s="24"/>
+      <c r="AY9" s="24"/>
+      <c r="AZ9" s="24"/>
+      <c r="BA9" s="24"/>
+      <c r="BB9" s="24"/>
+      <c r="BC9" s="24"/>
+      <c r="BD9" s="24"/>
+      <c r="BE9" s="24"/>
+      <c r="BF9" s="24"/>
+      <c r="BG9" s="24"/>
+      <c r="BH9" s="24"/>
+      <c r="BI9" s="24"/>
+      <c r="BJ9" s="24"/>
+      <c r="BK9" s="24"/>
+      <c r="BL9" s="24"/>
+      <c r="BM9" s="24"/>
+      <c r="BN9" s="24"/>
+      <c r="BO9" s="24"/>
+      <c r="BP9" s="24"/>
+      <c r="BQ9" s="24"/>
+      <c r="BR9" s="24"/>
+      <c r="BS9" s="24"/>
+      <c r="BT9" s="24"/>
+      <c r="BU9" s="24"/>
+      <c r="BV9" s="24"/>
+      <c r="BW9" s="24"/>
+      <c r="BX9" s="24"/>
+      <c r="BY9" s="24"/>
+      <c r="BZ9" s="24"/>
+      <c r="CA9" s="24"/>
+      <c r="CB9" s="24"/>
+      <c r="CC9" s="24"/>
+      <c r="CD9" s="24"/>
+      <c r="CE9" s="24"/>
+      <c r="CF9" s="24"/>
+      <c r="CG9" s="24"/>
+      <c r="CH9" s="24"/>
+      <c r="CI9" s="24"/>
+      <c r="CJ9" s="24"/>
+      <c r="CK9" s="24"/>
+      <c r="CL9" s="24"/>
+      <c r="CM9" s="24"/>
+      <c r="CN9" s="24"/>
+      <c r="CO9" s="24"/>
+      <c r="CP9" s="24"/>
+      <c r="CQ9" s="24"/>
+      <c r="CR9" s="24"/>
+      <c r="CS9" s="24"/>
+      <c r="CT9" s="24"/>
+      <c r="CU9" s="24"/>
+      <c r="CV9" s="24"/>
+      <c r="CW9" s="24"/>
+      <c r="CX9" s="24"/>
+      <c r="CY9" s="24"/>
+      <c r="CZ9" s="24"/>
+      <c r="DA9" s="24"/>
+      <c r="DB9" s="24"/>
+      <c r="DC9" s="24"/>
+      <c r="DD9" s="24"/>
+      <c r="DE9" s="24"/>
+      <c r="DF9" s="24"/>
+      <c r="DG9" s="24"/>
+      <c r="DH9" s="24"/>
+      <c r="DI9" s="24"/>
+      <c r="DJ9" s="24"/>
+      <c r="DK9" s="24"/>
+      <c r="DL9" s="24"/>
+      <c r="DM9" s="24"/>
+      <c r="DN9" s="24"/>
+      <c r="DO9" s="24"/>
+      <c r="DP9" s="24"/>
+      <c r="DQ9" s="24"/>
+      <c r="DR9" s="24"/>
+      <c r="DS9" s="24"/>
+      <c r="DT9" s="24"/>
+      <c r="DU9" s="24"/>
+      <c r="DV9" s="24"/>
+      <c r="DW9" s="24"/>
+      <c r="DX9" s="24"/>
+      <c r="DY9" s="24"/>
+      <c r="DZ9" s="24"/>
+      <c r="EA9" s="24"/>
+      <c r="EB9" s="24"/>
+      <c r="EC9" s="24"/>
+      <c r="ED9" s="24"/>
+      <c r="EE9" s="24"/>
+      <c r="EF9" s="24"/>
+      <c r="EG9" s="24"/>
+      <c r="EH9" s="24"/>
+      <c r="EI9" s="24"/>
+      <c r="EJ9" s="24"/>
+      <c r="EK9" s="24"/>
+      <c r="EL9" s="24"/>
+      <c r="EM9" s="24"/>
+      <c r="EN9" s="24"/>
+      <c r="EO9" s="24"/>
+      <c r="EP9" s="24"/>
+      <c r="EQ9" s="24"/>
+      <c r="ER9" s="24"/>
+      <c r="ES9" s="24"/>
+      <c r="ET9" s="24"/>
+      <c r="EU9" s="24"/>
+      <c r="EV9" s="24"/>
+      <c r="EW9" s="24"/>
+      <c r="EX9" s="24"/>
+      <c r="EY9" s="24"/>
+      <c r="EZ9" s="24"/>
+      <c r="FA9" s="24"/>
+      <c r="FB9" s="24"/>
+      <c r="FC9" s="24"/>
+      <c r="FD9" s="24"/>
+      <c r="FE9" s="24"/>
+      <c r="FF9" s="24"/>
+      <c r="FG9" s="24"/>
+      <c r="FH9" s="24"/>
+      <c r="FI9" s="24"/>
     </row>
     <row r="10" spans="1:166" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="35"/>
-      <c r="B10" s="36"/>
+      <c r="A10" s="42"/>
+      <c r="B10" s="52"/>
       <c r="C10" s="6"/>
       <c r="D10" s="4" t="s">
         <v>10</v>
@@ -3341,7 +3407,7 @@
         <v>18</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D11" s="11">
         <f t="shared" ref="D11:D26" si="0">COUNT(F11:FI11)</f>
@@ -5979,332 +6045,332 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E26" s="31"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="32"/>
-      <c r="J26" s="32"/>
-      <c r="K26" s="32"/>
-      <c r="L26" s="32"/>
-      <c r="M26" s="32"/>
-      <c r="N26" s="32"/>
-      <c r="O26" s="32"/>
-      <c r="P26" s="32"/>
-      <c r="Q26" s="32"/>
-      <c r="R26" s="32"/>
-      <c r="S26" s="32"/>
-      <c r="T26" s="32"/>
-      <c r="U26" s="32"/>
-      <c r="V26" s="32"/>
-      <c r="W26" s="32"/>
-      <c r="X26" s="32"/>
-      <c r="Y26" s="32"/>
-      <c r="Z26" s="32"/>
-      <c r="AA26" s="32"/>
-      <c r="AB26" s="32"/>
-      <c r="AC26" s="32"/>
-      <c r="AD26" s="32"/>
-      <c r="AE26" s="32"/>
-      <c r="AF26" s="32"/>
-      <c r="AG26" s="32"/>
-      <c r="AH26" s="32"/>
-      <c r="AI26" s="32"/>
-      <c r="AJ26" s="32"/>
-      <c r="AK26" s="32"/>
-      <c r="AL26" s="32"/>
-      <c r="AM26" s="32"/>
-      <c r="AN26" s="32"/>
-      <c r="AO26" s="32"/>
-      <c r="AP26" s="32"/>
-      <c r="AQ26" s="32"/>
-      <c r="AR26" s="32"/>
-      <c r="AS26" s="32"/>
-      <c r="AT26" s="32"/>
-      <c r="AU26" s="32"/>
-      <c r="AV26" s="32"/>
-      <c r="AW26" s="32"/>
-      <c r="AX26" s="32"/>
-      <c r="AY26" s="32"/>
-      <c r="AZ26" s="32"/>
-      <c r="BA26" s="32"/>
-      <c r="BB26" s="32"/>
-      <c r="BC26" s="32"/>
-      <c r="BD26" s="32"/>
-      <c r="BE26" s="32"/>
-      <c r="BF26" s="32"/>
-      <c r="BG26" s="32"/>
-      <c r="BH26" s="32"/>
-      <c r="BI26" s="32"/>
-      <c r="BJ26" s="32"/>
-      <c r="BK26" s="32"/>
-      <c r="BL26" s="32"/>
-      <c r="BM26" s="32"/>
-      <c r="BN26" s="32"/>
-      <c r="BO26" s="32"/>
-      <c r="BP26" s="32"/>
-      <c r="BQ26" s="32"/>
-      <c r="BR26" s="32"/>
-      <c r="BS26" s="32"/>
-      <c r="BT26" s="32"/>
-      <c r="BU26" s="32"/>
-      <c r="BV26" s="32"/>
-      <c r="BW26" s="32"/>
-      <c r="BX26" s="32"/>
-      <c r="BY26" s="32"/>
-      <c r="BZ26" s="32"/>
-      <c r="CA26" s="32"/>
-      <c r="CB26" s="32"/>
-      <c r="CC26" s="32"/>
-      <c r="CD26" s="32"/>
-      <c r="CE26" s="32"/>
-      <c r="CF26" s="32"/>
-      <c r="CG26" s="32"/>
-      <c r="CH26" s="32"/>
-      <c r="CI26" s="32"/>
-      <c r="CJ26" s="32"/>
-      <c r="CK26" s="32"/>
-      <c r="CL26" s="32"/>
-      <c r="CM26" s="32"/>
-      <c r="CN26" s="32"/>
-      <c r="CO26" s="32"/>
-      <c r="CP26" s="32"/>
-      <c r="CQ26" s="32"/>
-      <c r="CR26" s="32"/>
-      <c r="CS26" s="32"/>
-      <c r="CT26" s="32"/>
-      <c r="CU26" s="32"/>
-      <c r="CV26" s="32"/>
-      <c r="CW26" s="32"/>
-      <c r="CX26" s="32"/>
-      <c r="CY26" s="32"/>
-      <c r="CZ26" s="32"/>
-      <c r="DA26" s="32"/>
-      <c r="DB26" s="32"/>
-      <c r="DC26" s="32"/>
-      <c r="DD26" s="32"/>
-      <c r="DE26" s="32"/>
-      <c r="DF26" s="32"/>
-      <c r="DG26" s="32"/>
-      <c r="DH26" s="32"/>
-      <c r="DI26" s="32"/>
-      <c r="DJ26" s="32"/>
-      <c r="DK26" s="32"/>
-      <c r="DL26" s="32"/>
-      <c r="DM26" s="32"/>
-      <c r="DN26" s="32"/>
-      <c r="DO26" s="32"/>
-      <c r="DP26" s="32"/>
-      <c r="DQ26" s="32"/>
-      <c r="DR26" s="32"/>
-      <c r="DS26" s="32"/>
-      <c r="DT26" s="32"/>
-      <c r="DU26" s="32"/>
-      <c r="DV26" s="32"/>
-      <c r="DW26" s="32"/>
-      <c r="DX26" s="32"/>
-      <c r="DY26" s="32"/>
-      <c r="DZ26" s="32"/>
-      <c r="EA26" s="32"/>
-      <c r="EB26" s="32"/>
-      <c r="EC26" s="32"/>
-      <c r="ED26" s="32"/>
-      <c r="EE26" s="32"/>
-      <c r="EF26" s="32"/>
-      <c r="EG26" s="32"/>
-      <c r="EH26" s="32"/>
-      <c r="EI26" s="32"/>
-      <c r="EJ26" s="32"/>
-      <c r="EK26" s="32"/>
-      <c r="EL26" s="32"/>
-      <c r="EM26" s="32"/>
-      <c r="EN26" s="32"/>
-      <c r="EO26" s="32"/>
-      <c r="EP26" s="32"/>
-      <c r="EQ26" s="32"/>
-      <c r="ER26" s="32"/>
-      <c r="ES26" s="32"/>
-      <c r="ET26" s="32"/>
-      <c r="EU26" s="32"/>
-      <c r="EV26" s="32"/>
-      <c r="EW26" s="32"/>
-      <c r="EX26" s="32"/>
-      <c r="EY26" s="32"/>
-      <c r="EZ26" s="32"/>
-      <c r="FA26" s="32"/>
-      <c r="FB26" s="32"/>
-      <c r="FC26" s="32"/>
-      <c r="FD26" s="32"/>
-      <c r="FE26" s="32"/>
-      <c r="FF26" s="32"/>
-      <c r="FG26" s="32"/>
-      <c r="FH26" s="32"/>
-      <c r="FI26" s="32"/>
+      <c r="E26" s="51"/>
+      <c r="F26" s="44"/>
+      <c r="G26" s="44"/>
+      <c r="H26" s="44"/>
+      <c r="I26" s="44"/>
+      <c r="J26" s="44"/>
+      <c r="K26" s="44"/>
+      <c r="L26" s="44"/>
+      <c r="M26" s="44"/>
+      <c r="N26" s="44"/>
+      <c r="O26" s="44"/>
+      <c r="P26" s="44"/>
+      <c r="Q26" s="44"/>
+      <c r="R26" s="44"/>
+      <c r="S26" s="44"/>
+      <c r="T26" s="44"/>
+      <c r="U26" s="44"/>
+      <c r="V26" s="44"/>
+      <c r="W26" s="44"/>
+      <c r="X26" s="44"/>
+      <c r="Y26" s="44"/>
+      <c r="Z26" s="44"/>
+      <c r="AA26" s="44"/>
+      <c r="AB26" s="44"/>
+      <c r="AC26" s="44"/>
+      <c r="AD26" s="44"/>
+      <c r="AE26" s="44"/>
+      <c r="AF26" s="44"/>
+      <c r="AG26" s="44"/>
+      <c r="AH26" s="44"/>
+      <c r="AI26" s="44"/>
+      <c r="AJ26" s="44"/>
+      <c r="AK26" s="44"/>
+      <c r="AL26" s="44"/>
+      <c r="AM26" s="44"/>
+      <c r="AN26" s="44"/>
+      <c r="AO26" s="44"/>
+      <c r="AP26" s="44"/>
+      <c r="AQ26" s="44"/>
+      <c r="AR26" s="44"/>
+      <c r="AS26" s="44"/>
+      <c r="AT26" s="44"/>
+      <c r="AU26" s="44"/>
+      <c r="AV26" s="44"/>
+      <c r="AW26" s="44"/>
+      <c r="AX26" s="44"/>
+      <c r="AY26" s="44"/>
+      <c r="AZ26" s="44"/>
+      <c r="BA26" s="44"/>
+      <c r="BB26" s="44"/>
+      <c r="BC26" s="44"/>
+      <c r="BD26" s="44"/>
+      <c r="BE26" s="44"/>
+      <c r="BF26" s="44"/>
+      <c r="BG26" s="44"/>
+      <c r="BH26" s="44"/>
+      <c r="BI26" s="44"/>
+      <c r="BJ26" s="44"/>
+      <c r="BK26" s="44"/>
+      <c r="BL26" s="44"/>
+      <c r="BM26" s="44"/>
+      <c r="BN26" s="44"/>
+      <c r="BO26" s="44"/>
+      <c r="BP26" s="44"/>
+      <c r="BQ26" s="44"/>
+      <c r="BR26" s="44"/>
+      <c r="BS26" s="44"/>
+      <c r="BT26" s="44"/>
+      <c r="BU26" s="44"/>
+      <c r="BV26" s="44"/>
+      <c r="BW26" s="44"/>
+      <c r="BX26" s="44"/>
+      <c r="BY26" s="44"/>
+      <c r="BZ26" s="44"/>
+      <c r="CA26" s="44"/>
+      <c r="CB26" s="44"/>
+      <c r="CC26" s="44"/>
+      <c r="CD26" s="44"/>
+      <c r="CE26" s="44"/>
+      <c r="CF26" s="44"/>
+      <c r="CG26" s="44"/>
+      <c r="CH26" s="44"/>
+      <c r="CI26" s="44"/>
+      <c r="CJ26" s="44"/>
+      <c r="CK26" s="44"/>
+      <c r="CL26" s="44"/>
+      <c r="CM26" s="44"/>
+      <c r="CN26" s="44"/>
+      <c r="CO26" s="44"/>
+      <c r="CP26" s="44"/>
+      <c r="CQ26" s="44"/>
+      <c r="CR26" s="44"/>
+      <c r="CS26" s="44"/>
+      <c r="CT26" s="44"/>
+      <c r="CU26" s="44"/>
+      <c r="CV26" s="44"/>
+      <c r="CW26" s="44"/>
+      <c r="CX26" s="44"/>
+      <c r="CY26" s="44"/>
+      <c r="CZ26" s="44"/>
+      <c r="DA26" s="44"/>
+      <c r="DB26" s="44"/>
+      <c r="DC26" s="44"/>
+      <c r="DD26" s="44"/>
+      <c r="DE26" s="44"/>
+      <c r="DF26" s="44"/>
+      <c r="DG26" s="44"/>
+      <c r="DH26" s="44"/>
+      <c r="DI26" s="44"/>
+      <c r="DJ26" s="44"/>
+      <c r="DK26" s="44"/>
+      <c r="DL26" s="44"/>
+      <c r="DM26" s="44"/>
+      <c r="DN26" s="44"/>
+      <c r="DO26" s="44"/>
+      <c r="DP26" s="44"/>
+      <c r="DQ26" s="44"/>
+      <c r="DR26" s="44"/>
+      <c r="DS26" s="44"/>
+      <c r="DT26" s="44"/>
+      <c r="DU26" s="44"/>
+      <c r="DV26" s="44"/>
+      <c r="DW26" s="44"/>
+      <c r="DX26" s="44"/>
+      <c r="DY26" s="44"/>
+      <c r="DZ26" s="44"/>
+      <c r="EA26" s="44"/>
+      <c r="EB26" s="44"/>
+      <c r="EC26" s="44"/>
+      <c r="ED26" s="44"/>
+      <c r="EE26" s="44"/>
+      <c r="EF26" s="44"/>
+      <c r="EG26" s="44"/>
+      <c r="EH26" s="44"/>
+      <c r="EI26" s="44"/>
+      <c r="EJ26" s="44"/>
+      <c r="EK26" s="44"/>
+      <c r="EL26" s="44"/>
+      <c r="EM26" s="44"/>
+      <c r="EN26" s="44"/>
+      <c r="EO26" s="44"/>
+      <c r="EP26" s="44"/>
+      <c r="EQ26" s="44"/>
+      <c r="ER26" s="44"/>
+      <c r="ES26" s="44"/>
+      <c r="ET26" s="44"/>
+      <c r="EU26" s="44"/>
+      <c r="EV26" s="44"/>
+      <c r="EW26" s="44"/>
+      <c r="EX26" s="44"/>
+      <c r="EY26" s="44"/>
+      <c r="EZ26" s="44"/>
+      <c r="FA26" s="44"/>
+      <c r="FB26" s="44"/>
+      <c r="FC26" s="44"/>
+      <c r="FD26" s="44"/>
+      <c r="FE26" s="44"/>
+      <c r="FF26" s="44"/>
+      <c r="FG26" s="44"/>
+      <c r="FH26" s="44"/>
+      <c r="FI26" s="44"/>
     </row>
     <row r="27" spans="1:165" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F27" s="52"/>
-      <c r="G27" s="52"/>
-      <c r="H27" s="52"/>
-      <c r="I27" s="52"/>
-      <c r="J27" s="52"/>
-      <c r="K27" s="52"/>
-      <c r="L27" s="52"/>
-      <c r="M27" s="52"/>
-      <c r="N27" s="52"/>
-      <c r="O27" s="52"/>
-      <c r="P27" s="52"/>
-      <c r="Q27" s="52"/>
-      <c r="R27" s="52"/>
-      <c r="S27" s="52"/>
-      <c r="T27" s="52"/>
-      <c r="U27" s="52"/>
-      <c r="V27" s="52"/>
-      <c r="W27" s="52"/>
-      <c r="X27" s="52"/>
-      <c r="Y27" s="52"/>
-      <c r="Z27" s="52"/>
-      <c r="AA27" s="52"/>
-      <c r="AB27" s="52"/>
-      <c r="AC27" s="52"/>
-      <c r="AD27" s="52"/>
-      <c r="AE27" s="52"/>
-      <c r="AF27" s="52"/>
-      <c r="AG27" s="52"/>
-      <c r="AH27" s="52"/>
-      <c r="AI27" s="52"/>
-      <c r="AJ27" s="52"/>
-      <c r="AK27" s="52"/>
-      <c r="AL27" s="52"/>
-      <c r="AM27" s="52"/>
-      <c r="AN27" s="52"/>
-      <c r="AO27" s="52"/>
-      <c r="AP27" s="52"/>
-      <c r="AQ27" s="52"/>
-      <c r="AR27" s="52"/>
-      <c r="AS27" s="52"/>
-      <c r="AT27" s="52"/>
-      <c r="AU27" s="52"/>
-      <c r="AV27" s="52"/>
-      <c r="AW27" s="52"/>
-      <c r="AX27" s="52"/>
-      <c r="AY27" s="52"/>
-      <c r="AZ27" s="52"/>
-      <c r="BA27" s="52"/>
-      <c r="BB27" s="52"/>
-      <c r="BC27" s="52"/>
-      <c r="BD27" s="52"/>
-      <c r="BE27" s="52"/>
-      <c r="BF27" s="52"/>
-      <c r="BG27" s="52"/>
-      <c r="BH27" s="52"/>
-      <c r="BI27" s="52"/>
-      <c r="BJ27" s="52"/>
-      <c r="BK27" s="52"/>
-      <c r="BL27" s="52"/>
-      <c r="BM27" s="52"/>
-      <c r="BN27" s="52"/>
-      <c r="BO27" s="52"/>
-      <c r="BP27" s="52"/>
-      <c r="BQ27" s="52"/>
-      <c r="BR27" s="52"/>
-      <c r="BS27" s="52"/>
-      <c r="BT27" s="52"/>
-      <c r="BU27" s="52"/>
-      <c r="BV27" s="52"/>
-      <c r="BW27" s="52"/>
-      <c r="BX27" s="52"/>
-      <c r="BY27" s="52"/>
-      <c r="BZ27" s="52"/>
-      <c r="CA27" s="52"/>
-      <c r="CB27" s="52"/>
-      <c r="CC27" s="52"/>
-      <c r="CD27" s="52"/>
-      <c r="CE27" s="53"/>
-      <c r="CF27" s="54"/>
-      <c r="CG27" s="54"/>
-      <c r="CH27" s="54"/>
-      <c r="CI27" s="54"/>
-      <c r="CJ27" s="54"/>
-      <c r="CK27" s="54"/>
-      <c r="CL27" s="54"/>
-      <c r="CM27" s="54"/>
-      <c r="CN27" s="54"/>
-      <c r="CO27" s="54"/>
-      <c r="CP27" s="54"/>
-      <c r="CQ27" s="54"/>
-      <c r="CR27" s="54"/>
-      <c r="CS27" s="54"/>
-      <c r="CT27" s="54"/>
-      <c r="CU27" s="54"/>
-      <c r="CV27" s="54"/>
-      <c r="CW27" s="54"/>
-      <c r="CX27" s="54"/>
-      <c r="CY27" s="54"/>
-      <c r="CZ27" s="54"/>
-      <c r="DA27" s="54"/>
-      <c r="DB27" s="54"/>
-      <c r="DC27" s="54"/>
-      <c r="DD27" s="54"/>
-      <c r="DE27" s="54"/>
-      <c r="DF27" s="54"/>
-      <c r="DG27" s="54"/>
-      <c r="DH27" s="54"/>
-      <c r="DI27" s="54"/>
-      <c r="DJ27" s="54"/>
-      <c r="DK27" s="54"/>
-      <c r="DL27" s="54"/>
-      <c r="DM27" s="54"/>
-      <c r="DN27" s="54"/>
-      <c r="DO27" s="54"/>
-      <c r="DP27" s="54"/>
-      <c r="DQ27" s="54"/>
-      <c r="DR27" s="54"/>
-      <c r="DS27" s="54"/>
-      <c r="DT27" s="54"/>
-      <c r="DU27" s="54"/>
-      <c r="DV27" s="54"/>
-      <c r="DW27" s="54"/>
-      <c r="DX27" s="54"/>
-      <c r="DY27" s="54"/>
-      <c r="DZ27" s="54"/>
-      <c r="EA27" s="54"/>
-      <c r="EB27" s="54"/>
-      <c r="EC27" s="54"/>
-      <c r="ED27" s="54"/>
-      <c r="EE27" s="54"/>
-      <c r="EF27" s="54"/>
-      <c r="EG27" s="54"/>
-      <c r="EH27" s="54"/>
-      <c r="EI27" s="54"/>
-      <c r="EJ27" s="54"/>
-      <c r="EK27" s="54"/>
-      <c r="EL27" s="54"/>
-      <c r="EM27" s="54"/>
-      <c r="EN27" s="54"/>
-      <c r="EO27" s="54"/>
-      <c r="EP27" s="54"/>
-      <c r="EQ27" s="54"/>
-      <c r="ER27" s="54"/>
-      <c r="ES27" s="54"/>
-      <c r="ET27" s="54"/>
-      <c r="EU27" s="54"/>
-      <c r="EV27" s="54"/>
-      <c r="EW27" s="54"/>
-      <c r="EX27" s="54"/>
-      <c r="EY27" s="54"/>
-      <c r="EZ27" s="54"/>
-      <c r="FA27" s="54"/>
-      <c r="FB27" s="54"/>
-      <c r="FC27" s="54"/>
-      <c r="FD27" s="54"/>
-      <c r="FE27" s="54"/>
-      <c r="FF27" s="54"/>
-      <c r="FG27" s="54"/>
-      <c r="FH27" s="54"/>
-      <c r="FI27" s="54"/>
+      <c r="F27" s="27"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="27"/>
+      <c r="I27" s="27"/>
+      <c r="J27" s="27"/>
+      <c r="K27" s="27"/>
+      <c r="L27" s="27"/>
+      <c r="M27" s="27"/>
+      <c r="N27" s="27"/>
+      <c r="O27" s="27"/>
+      <c r="P27" s="27"/>
+      <c r="Q27" s="27"/>
+      <c r="R27" s="27"/>
+      <c r="S27" s="27"/>
+      <c r="T27" s="27"/>
+      <c r="U27" s="27"/>
+      <c r="V27" s="27"/>
+      <c r="W27" s="27"/>
+      <c r="X27" s="27"/>
+      <c r="Y27" s="27"/>
+      <c r="Z27" s="27"/>
+      <c r="AA27" s="27"/>
+      <c r="AB27" s="27"/>
+      <c r="AC27" s="27"/>
+      <c r="AD27" s="27"/>
+      <c r="AE27" s="27"/>
+      <c r="AF27" s="27"/>
+      <c r="AG27" s="27"/>
+      <c r="AH27" s="27"/>
+      <c r="AI27" s="27"/>
+      <c r="AJ27" s="27"/>
+      <c r="AK27" s="27"/>
+      <c r="AL27" s="27"/>
+      <c r="AM27" s="27"/>
+      <c r="AN27" s="27"/>
+      <c r="AO27" s="27"/>
+      <c r="AP27" s="27"/>
+      <c r="AQ27" s="27"/>
+      <c r="AR27" s="27"/>
+      <c r="AS27" s="27"/>
+      <c r="AT27" s="27"/>
+      <c r="AU27" s="27"/>
+      <c r="AV27" s="27"/>
+      <c r="AW27" s="27"/>
+      <c r="AX27" s="27"/>
+      <c r="AY27" s="27"/>
+      <c r="AZ27" s="27"/>
+      <c r="BA27" s="27"/>
+      <c r="BB27" s="27"/>
+      <c r="BC27" s="27"/>
+      <c r="BD27" s="27"/>
+      <c r="BE27" s="27"/>
+      <c r="BF27" s="27"/>
+      <c r="BG27" s="27"/>
+      <c r="BH27" s="27"/>
+      <c r="BI27" s="27"/>
+      <c r="BJ27" s="27"/>
+      <c r="BK27" s="27"/>
+      <c r="BL27" s="27"/>
+      <c r="BM27" s="27"/>
+      <c r="BN27" s="27"/>
+      <c r="BO27" s="27"/>
+      <c r="BP27" s="27"/>
+      <c r="BQ27" s="27"/>
+      <c r="BR27" s="27"/>
+      <c r="BS27" s="27"/>
+      <c r="BT27" s="27"/>
+      <c r="BU27" s="27"/>
+      <c r="BV27" s="27"/>
+      <c r="BW27" s="27"/>
+      <c r="BX27" s="27"/>
+      <c r="BY27" s="27"/>
+      <c r="BZ27" s="27"/>
+      <c r="CA27" s="27"/>
+      <c r="CB27" s="27"/>
+      <c r="CC27" s="27"/>
+      <c r="CD27" s="27"/>
+      <c r="CE27" s="28"/>
+      <c r="CF27" s="29"/>
+      <c r="CG27" s="29"/>
+      <c r="CH27" s="29"/>
+      <c r="CI27" s="29"/>
+      <c r="CJ27" s="29"/>
+      <c r="CK27" s="29"/>
+      <c r="CL27" s="29"/>
+      <c r="CM27" s="29"/>
+      <c r="CN27" s="29"/>
+      <c r="CO27" s="29"/>
+      <c r="CP27" s="29"/>
+      <c r="CQ27" s="29"/>
+      <c r="CR27" s="29"/>
+      <c r="CS27" s="29"/>
+      <c r="CT27" s="29"/>
+      <c r="CU27" s="29"/>
+      <c r="CV27" s="29"/>
+      <c r="CW27" s="29"/>
+      <c r="CX27" s="29"/>
+      <c r="CY27" s="29"/>
+      <c r="CZ27" s="29"/>
+      <c r="DA27" s="29"/>
+      <c r="DB27" s="29"/>
+      <c r="DC27" s="29"/>
+      <c r="DD27" s="29"/>
+      <c r="DE27" s="29"/>
+      <c r="DF27" s="29"/>
+      <c r="DG27" s="29"/>
+      <c r="DH27" s="29"/>
+      <c r="DI27" s="29"/>
+      <c r="DJ27" s="29"/>
+      <c r="DK27" s="29"/>
+      <c r="DL27" s="29"/>
+      <c r="DM27" s="29"/>
+      <c r="DN27" s="29"/>
+      <c r="DO27" s="29"/>
+      <c r="DP27" s="29"/>
+      <c r="DQ27" s="29"/>
+      <c r="DR27" s="29"/>
+      <c r="DS27" s="29"/>
+      <c r="DT27" s="29"/>
+      <c r="DU27" s="29"/>
+      <c r="DV27" s="29"/>
+      <c r="DW27" s="29"/>
+      <c r="DX27" s="29"/>
+      <c r="DY27" s="29"/>
+      <c r="DZ27" s="29"/>
+      <c r="EA27" s="29"/>
+      <c r="EB27" s="29"/>
+      <c r="EC27" s="29"/>
+      <c r="ED27" s="29"/>
+      <c r="EE27" s="29"/>
+      <c r="EF27" s="29"/>
+      <c r="EG27" s="29"/>
+      <c r="EH27" s="29"/>
+      <c r="EI27" s="29"/>
+      <c r="EJ27" s="29"/>
+      <c r="EK27" s="29"/>
+      <c r="EL27" s="29"/>
+      <c r="EM27" s="29"/>
+      <c r="EN27" s="29"/>
+      <c r="EO27" s="29"/>
+      <c r="EP27" s="29"/>
+      <c r="EQ27" s="29"/>
+      <c r="ER27" s="29"/>
+      <c r="ES27" s="29"/>
+      <c r="ET27" s="29"/>
+      <c r="EU27" s="29"/>
+      <c r="EV27" s="29"/>
+      <c r="EW27" s="29"/>
+      <c r="EX27" s="29"/>
+      <c r="EY27" s="29"/>
+      <c r="EZ27" s="29"/>
+      <c r="FA27" s="29"/>
+      <c r="FB27" s="29"/>
+      <c r="FC27" s="29"/>
+      <c r="FD27" s="29"/>
+      <c r="FE27" s="29"/>
+      <c r="FF27" s="29"/>
+      <c r="FG27" s="29"/>
+      <c r="FH27" s="29"/>
+      <c r="FI27" s="29"/>
     </row>
     <row r="29" spans="1:165" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E29" s="21">
+      <c r="E29" s="20">
         <f>SUM(E11:E18)/8</f>
         <v>0</v>
       </c>
@@ -6314,31 +6380,338 @@
       </c>
     </row>
     <row r="30" spans="1:165" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AJ30" s="17"/>
+      <c r="AJ30" s="65"/>
       <c r="AK30" s="16" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" spans="1:165" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AJ31" s="20"/>
+      <c r="AJ31" s="19"/>
       <c r="AK31" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="350">
-    <mergeCell ref="DR8:DR9"/>
-    <mergeCell ref="DS8:DS9"/>
-    <mergeCell ref="DT8:DT9"/>
-    <mergeCell ref="DH8:DH9"/>
-    <mergeCell ref="DI8:DI9"/>
-    <mergeCell ref="DJ8:DJ9"/>
-    <mergeCell ref="DK8:DK9"/>
-    <mergeCell ref="DL8:DL9"/>
-    <mergeCell ref="DM8:DM9"/>
-    <mergeCell ref="DN8:DN9"/>
-    <mergeCell ref="DO8:DO9"/>
-    <mergeCell ref="DP8:DP9"/>
+  <mergeCells count="355">
+    <mergeCell ref="BA1:BD1"/>
+    <mergeCell ref="BE1:BJ1"/>
+    <mergeCell ref="BK1:BP1"/>
+    <mergeCell ref="BQ1:BV1"/>
+    <mergeCell ref="U1:X1"/>
+    <mergeCell ref="Y1:AC1"/>
+    <mergeCell ref="AD1:AG1"/>
+    <mergeCell ref="AH1:AM1"/>
+    <mergeCell ref="AN1:AS1"/>
+    <mergeCell ref="AT1:AW1"/>
+    <mergeCell ref="BC8:BC9"/>
+    <mergeCell ref="BD8:BD9"/>
+    <mergeCell ref="AE8:AE9"/>
+    <mergeCell ref="AF8:AF9"/>
+    <mergeCell ref="AG8:AG9"/>
+    <mergeCell ref="AH8:AH9"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="AJ8:AJ9"/>
+    <mergeCell ref="AK8:AK9"/>
+    <mergeCell ref="AL8:AL9"/>
+    <mergeCell ref="AM8:AM9"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="W8:W9"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AX1:AZ1"/>
+    <mergeCell ref="BH8:BH9"/>
+    <mergeCell ref="BI8:BI9"/>
+    <mergeCell ref="BJ8:BJ9"/>
+    <mergeCell ref="BK8:BK9"/>
+    <mergeCell ref="BL8:BL9"/>
+    <mergeCell ref="BM8:BM9"/>
+    <mergeCell ref="BE8:BE9"/>
+    <mergeCell ref="AN8:AN9"/>
+    <mergeCell ref="AO8:AO9"/>
+    <mergeCell ref="AP8:AP9"/>
+    <mergeCell ref="AQ8:AQ9"/>
+    <mergeCell ref="AR8:AR9"/>
+    <mergeCell ref="AS8:AS9"/>
+    <mergeCell ref="AT8:AT9"/>
+    <mergeCell ref="AU8:AU9"/>
+    <mergeCell ref="AV8:AV9"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AD8:AD9"/>
+    <mergeCell ref="CB8:CB9"/>
+    <mergeCell ref="CC8:CC9"/>
+    <mergeCell ref="CD8:CD9"/>
+    <mergeCell ref="CE8:CE9"/>
+    <mergeCell ref="DU8:DU9"/>
+    <mergeCell ref="EK8:EK9"/>
+    <mergeCell ref="EI8:EI9"/>
+    <mergeCell ref="EJ8:EJ9"/>
+    <mergeCell ref="CV8:CV9"/>
+    <mergeCell ref="CW8:CW9"/>
+    <mergeCell ref="CX8:CX9"/>
+    <mergeCell ref="CY8:CY9"/>
+    <mergeCell ref="CZ8:CZ9"/>
+    <mergeCell ref="DA8:DA9"/>
+    <mergeCell ref="DB8:DB9"/>
+    <mergeCell ref="DC8:DC9"/>
+    <mergeCell ref="DD8:DD9"/>
+    <mergeCell ref="DE8:DE9"/>
+    <mergeCell ref="DF8:DF9"/>
+    <mergeCell ref="DG8:DG9"/>
+    <mergeCell ref="DQ8:DQ9"/>
+    <mergeCell ref="ED8:ED9"/>
+    <mergeCell ref="EE8:EE9"/>
+    <mergeCell ref="DW2:DW7"/>
+    <mergeCell ref="CB2:CB7"/>
+    <mergeCell ref="CC2:CC7"/>
+    <mergeCell ref="CD2:CD7"/>
+    <mergeCell ref="CE2:CE7"/>
+    <mergeCell ref="DU2:DU7"/>
+    <mergeCell ref="DV2:DV7"/>
+    <mergeCell ref="DY8:DY9"/>
+    <mergeCell ref="DX8:DX9"/>
+    <mergeCell ref="DZ8:DZ9"/>
+    <mergeCell ref="EA8:EA9"/>
+    <mergeCell ref="CR2:CR7"/>
+    <mergeCell ref="CS2:CS7"/>
+    <mergeCell ref="CT2:CT7"/>
+    <mergeCell ref="DV8:DV9"/>
+    <mergeCell ref="DW8:DW9"/>
+    <mergeCell ref="AW8:AW9"/>
+    <mergeCell ref="AX8:AX9"/>
+    <mergeCell ref="AY8:AY9"/>
+    <mergeCell ref="AZ8:AZ9"/>
+    <mergeCell ref="BA8:BA9"/>
+    <mergeCell ref="BB8:BB9"/>
+    <mergeCell ref="BQ2:BQ7"/>
+    <mergeCell ref="BR2:BR7"/>
+    <mergeCell ref="BS2:BS7"/>
+    <mergeCell ref="BT2:BT7"/>
+    <mergeCell ref="BU2:BU7"/>
+    <mergeCell ref="BV2:BV7"/>
+    <mergeCell ref="BX8:BX9"/>
+    <mergeCell ref="BY8:BY9"/>
+    <mergeCell ref="BO8:BO9"/>
+    <mergeCell ref="BP8:BP9"/>
+    <mergeCell ref="BQ8:BQ9"/>
+    <mergeCell ref="BR8:BR9"/>
+    <mergeCell ref="BS8:BS9"/>
+    <mergeCell ref="BT8:BT9"/>
+    <mergeCell ref="BZ8:BZ9"/>
+    <mergeCell ref="CA8:CA9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="E26:FI26"/>
+    <mergeCell ref="EU8:EU9"/>
+    <mergeCell ref="FF8:FF9"/>
+    <mergeCell ref="FG8:FG9"/>
+    <mergeCell ref="FH8:FH9"/>
+    <mergeCell ref="FI8:FI9"/>
+    <mergeCell ref="EN8:EN9"/>
+    <mergeCell ref="EO8:EO9"/>
+    <mergeCell ref="EB8:EB9"/>
+    <mergeCell ref="EL8:EL9"/>
+    <mergeCell ref="EM8:EM9"/>
+    <mergeCell ref="BU8:BU9"/>
+    <mergeCell ref="BV8:BV9"/>
+    <mergeCell ref="BW8:BW9"/>
+    <mergeCell ref="BF8:BF9"/>
+    <mergeCell ref="BG8:BG9"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="F2:F7"/>
+    <mergeCell ref="G2:G7"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="I2:I7"/>
+    <mergeCell ref="J2:J7"/>
+    <mergeCell ref="K2:K7"/>
+    <mergeCell ref="L2:L7"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="M2:M7"/>
+    <mergeCell ref="F1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="N2:N7"/>
+    <mergeCell ref="O2:O7"/>
+    <mergeCell ref="P2:P7"/>
+    <mergeCell ref="Q2:Q7"/>
+    <mergeCell ref="R2:R7"/>
+    <mergeCell ref="S2:S7"/>
+    <mergeCell ref="O1:T1"/>
+    <mergeCell ref="T2:T7"/>
+    <mergeCell ref="EC8:EC9"/>
+    <mergeCell ref="Y2:Y7"/>
+    <mergeCell ref="Z2:Z7"/>
+    <mergeCell ref="AA2:AA7"/>
+    <mergeCell ref="AB2:AB7"/>
+    <mergeCell ref="AC2:AC7"/>
+    <mergeCell ref="AD2:AD7"/>
+    <mergeCell ref="AE2:AE7"/>
+    <mergeCell ref="AH2:AH7"/>
+    <mergeCell ref="AI2:AI7"/>
+    <mergeCell ref="AJ2:AJ7"/>
+    <mergeCell ref="AK2:AK7"/>
+    <mergeCell ref="AL2:AL7"/>
+    <mergeCell ref="AM2:AM7"/>
+    <mergeCell ref="AN2:AN7"/>
+    <mergeCell ref="AO2:AO7"/>
+    <mergeCell ref="AG2:AG7"/>
+    <mergeCell ref="BK2:BK7"/>
+    <mergeCell ref="X2:X7"/>
+    <mergeCell ref="AF2:AF7"/>
+    <mergeCell ref="AX2:AX7"/>
+    <mergeCell ref="AY2:AY7"/>
+    <mergeCell ref="AZ2:AZ7"/>
+    <mergeCell ref="AP2:AP7"/>
+    <mergeCell ref="AQ2:AQ7"/>
+    <mergeCell ref="AR2:AR7"/>
+    <mergeCell ref="AS2:AS7"/>
+    <mergeCell ref="AT2:AT7"/>
+    <mergeCell ref="AU2:AU7"/>
+    <mergeCell ref="AV2:AV7"/>
+    <mergeCell ref="AW2:AW7"/>
+    <mergeCell ref="EL2:EL7"/>
+    <mergeCell ref="EJ2:EJ7"/>
+    <mergeCell ref="EK2:EK7"/>
+    <mergeCell ref="EF2:EF7"/>
+    <mergeCell ref="EG2:EG7"/>
+    <mergeCell ref="EH2:EH7"/>
+    <mergeCell ref="EI2:EI7"/>
+    <mergeCell ref="DX2:DX7"/>
+    <mergeCell ref="DY2:DY7"/>
+    <mergeCell ref="DZ2:DZ7"/>
+    <mergeCell ref="EA2:EA7"/>
+    <mergeCell ref="EB2:EB7"/>
+    <mergeCell ref="EC2:EC7"/>
+    <mergeCell ref="ED2:ED7"/>
+    <mergeCell ref="EE2:EE7"/>
+    <mergeCell ref="BI2:BI7"/>
+    <mergeCell ref="BJ2:BJ7"/>
+    <mergeCell ref="CM2:CM7"/>
+    <mergeCell ref="CN2:CN7"/>
+    <mergeCell ref="CO2:CO7"/>
+    <mergeCell ref="CP2:CP7"/>
+    <mergeCell ref="CQ2:CQ7"/>
+    <mergeCell ref="BL2:BL7"/>
+    <mergeCell ref="BA2:BA7"/>
+    <mergeCell ref="BB2:BB7"/>
+    <mergeCell ref="BC2:BC7"/>
+    <mergeCell ref="F27:S27"/>
+    <mergeCell ref="T27:AW27"/>
+    <mergeCell ref="AX27:CD27"/>
+    <mergeCell ref="CE27:FI27"/>
+    <mergeCell ref="EV8:EV9"/>
+    <mergeCell ref="EW8:EW9"/>
+    <mergeCell ref="EX8:EX9"/>
+    <mergeCell ref="EY8:EY9"/>
+    <mergeCell ref="EZ8:EZ9"/>
+    <mergeCell ref="FA8:FA9"/>
+    <mergeCell ref="FB8:FB9"/>
+    <mergeCell ref="FC8:FC9"/>
+    <mergeCell ref="FD8:FD9"/>
+    <mergeCell ref="FE8:FE9"/>
+    <mergeCell ref="EP8:EP9"/>
+    <mergeCell ref="EQ8:EQ9"/>
+    <mergeCell ref="ER8:ER9"/>
+    <mergeCell ref="ES8:ES9"/>
+    <mergeCell ref="ET8:ET9"/>
+    <mergeCell ref="EF8:EF9"/>
+    <mergeCell ref="EG8:EG9"/>
+    <mergeCell ref="EH8:EH9"/>
+    <mergeCell ref="BN8:BN9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="FF2:FF7"/>
+    <mergeCell ref="FG2:FG7"/>
+    <mergeCell ref="FH2:FH7"/>
+    <mergeCell ref="FI2:FI7"/>
+    <mergeCell ref="EM2:EM7"/>
+    <mergeCell ref="EN2:EN7"/>
+    <mergeCell ref="EP2:EP7"/>
+    <mergeCell ref="EQ2:EQ7"/>
+    <mergeCell ref="ER2:ER7"/>
+    <mergeCell ref="ES2:ES7"/>
+    <mergeCell ref="ET2:ET7"/>
+    <mergeCell ref="EO2:EO7"/>
+    <mergeCell ref="FC2:FC7"/>
+    <mergeCell ref="FD2:FD7"/>
+    <mergeCell ref="FE2:FE7"/>
+    <mergeCell ref="EV2:EV7"/>
+    <mergeCell ref="EW2:EW7"/>
+    <mergeCell ref="EX2:EX7"/>
+    <mergeCell ref="EY2:EY7"/>
+    <mergeCell ref="EZ2:EZ7"/>
+    <mergeCell ref="FA2:FA7"/>
+    <mergeCell ref="FB2:FB7"/>
+    <mergeCell ref="EU2:EU7"/>
+    <mergeCell ref="U2:U7"/>
+    <mergeCell ref="V2:V7"/>
+    <mergeCell ref="CF2:CF7"/>
+    <mergeCell ref="CG2:CG7"/>
+    <mergeCell ref="CH2:CH7"/>
+    <mergeCell ref="CI2:CI7"/>
+    <mergeCell ref="CJ2:CJ7"/>
+    <mergeCell ref="CK2:CK7"/>
+    <mergeCell ref="CL2:CL7"/>
+    <mergeCell ref="W2:W7"/>
+    <mergeCell ref="BD2:BD7"/>
+    <mergeCell ref="BE2:BE7"/>
+    <mergeCell ref="BF2:BF7"/>
+    <mergeCell ref="BG2:BG7"/>
+    <mergeCell ref="BM2:BM7"/>
+    <mergeCell ref="BN2:BN7"/>
+    <mergeCell ref="BO2:BO7"/>
+    <mergeCell ref="BP2:BP7"/>
+    <mergeCell ref="CA2:CA7"/>
+    <mergeCell ref="BW2:BW7"/>
+    <mergeCell ref="BX2:BX7"/>
+    <mergeCell ref="BY2:BY7"/>
+    <mergeCell ref="BZ2:BZ7"/>
+    <mergeCell ref="BH2:BH7"/>
+    <mergeCell ref="CU2:CU7"/>
+    <mergeCell ref="CV2:CV7"/>
+    <mergeCell ref="CW2:CW7"/>
+    <mergeCell ref="CX2:CX7"/>
+    <mergeCell ref="CY2:CY7"/>
+    <mergeCell ref="CZ2:CZ7"/>
+    <mergeCell ref="DA2:DA7"/>
+    <mergeCell ref="DB2:DB7"/>
+    <mergeCell ref="DC2:DC7"/>
+    <mergeCell ref="DD2:DD7"/>
+    <mergeCell ref="DE2:DE7"/>
+    <mergeCell ref="DF2:DF7"/>
+    <mergeCell ref="DG2:DG7"/>
+    <mergeCell ref="DH2:DH7"/>
+    <mergeCell ref="DI2:DI7"/>
+    <mergeCell ref="DJ2:DJ7"/>
+    <mergeCell ref="DK2:DK7"/>
+    <mergeCell ref="DL2:DL7"/>
     <mergeCell ref="DM2:DM7"/>
     <mergeCell ref="DN2:DN7"/>
     <mergeCell ref="DO2:DO7"/>
@@ -6363,320 +6736,18 @@
     <mergeCell ref="CS8:CS9"/>
     <mergeCell ref="CT8:CT9"/>
     <mergeCell ref="CU8:CU9"/>
-    <mergeCell ref="DD2:DD7"/>
-    <mergeCell ref="DE2:DE7"/>
-    <mergeCell ref="DF2:DF7"/>
-    <mergeCell ref="DG2:DG7"/>
-    <mergeCell ref="DH2:DH7"/>
-    <mergeCell ref="DI2:DI7"/>
-    <mergeCell ref="DJ2:DJ7"/>
-    <mergeCell ref="DK2:DK7"/>
-    <mergeCell ref="DL2:DL7"/>
-    <mergeCell ref="CU2:CU7"/>
-    <mergeCell ref="CV2:CV7"/>
-    <mergeCell ref="CW2:CW7"/>
-    <mergeCell ref="CX2:CX7"/>
-    <mergeCell ref="CY2:CY7"/>
-    <mergeCell ref="CZ2:CZ7"/>
-    <mergeCell ref="DA2:DA7"/>
-    <mergeCell ref="DB2:DB7"/>
-    <mergeCell ref="DC2:DC7"/>
-    <mergeCell ref="U2:U7"/>
-    <mergeCell ref="V2:V7"/>
-    <mergeCell ref="CF2:CF7"/>
-    <mergeCell ref="CG2:CG7"/>
-    <mergeCell ref="CH2:CH7"/>
-    <mergeCell ref="CI2:CI7"/>
-    <mergeCell ref="CJ2:CJ7"/>
-    <mergeCell ref="CK2:CK7"/>
-    <mergeCell ref="CL2:CL7"/>
-    <mergeCell ref="FF2:FF7"/>
-    <mergeCell ref="FG2:FG7"/>
-    <mergeCell ref="FH2:FH7"/>
-    <mergeCell ref="FI2:FI7"/>
-    <mergeCell ref="EM2:EM7"/>
-    <mergeCell ref="EN2:EN7"/>
-    <mergeCell ref="EP2:EP7"/>
-    <mergeCell ref="EQ2:EQ7"/>
-    <mergeCell ref="ER2:ER7"/>
-    <mergeCell ref="ES2:ES7"/>
-    <mergeCell ref="ET2:ET7"/>
-    <mergeCell ref="EO2:EO7"/>
-    <mergeCell ref="FC2:FC7"/>
-    <mergeCell ref="FD2:FD7"/>
-    <mergeCell ref="FE2:FE7"/>
-    <mergeCell ref="EV2:EV7"/>
-    <mergeCell ref="EW2:EW7"/>
-    <mergeCell ref="EX2:EX7"/>
-    <mergeCell ref="EY2:EY7"/>
-    <mergeCell ref="EZ2:EZ7"/>
-    <mergeCell ref="W2:W7"/>
-    <mergeCell ref="F27:S27"/>
-    <mergeCell ref="T27:AW27"/>
-    <mergeCell ref="AX27:CD27"/>
-    <mergeCell ref="CE27:FI27"/>
-    <mergeCell ref="EV8:EV9"/>
-    <mergeCell ref="EW8:EW9"/>
-    <mergeCell ref="EX8:EX9"/>
-    <mergeCell ref="EY8:EY9"/>
-    <mergeCell ref="EZ8:EZ9"/>
-    <mergeCell ref="FA8:FA9"/>
-    <mergeCell ref="FB8:FB9"/>
-    <mergeCell ref="FC8:FC9"/>
-    <mergeCell ref="FD8:FD9"/>
-    <mergeCell ref="FE8:FE9"/>
-    <mergeCell ref="EP8:EP9"/>
-    <mergeCell ref="EQ8:EQ9"/>
-    <mergeCell ref="ER8:ER9"/>
-    <mergeCell ref="ES8:ES9"/>
-    <mergeCell ref="ET8:ET9"/>
-    <mergeCell ref="EF8:EF9"/>
-    <mergeCell ref="EG8:EG9"/>
-    <mergeCell ref="EH8:EH9"/>
-    <mergeCell ref="BN8:BN9"/>
-    <mergeCell ref="FA2:FA7"/>
-    <mergeCell ref="FB2:FB7"/>
-    <mergeCell ref="EU2:EU7"/>
-    <mergeCell ref="BD2:BD7"/>
-    <mergeCell ref="BE2:BE7"/>
-    <mergeCell ref="BF2:BF7"/>
-    <mergeCell ref="BG2:BG7"/>
-    <mergeCell ref="BM2:BM7"/>
-    <mergeCell ref="BN2:BN7"/>
-    <mergeCell ref="BO2:BO7"/>
-    <mergeCell ref="BP2:BP7"/>
-    <mergeCell ref="CA2:CA7"/>
-    <mergeCell ref="BW2:BW7"/>
-    <mergeCell ref="BX2:BX7"/>
-    <mergeCell ref="BY2:BY7"/>
-    <mergeCell ref="BZ2:BZ7"/>
-    <mergeCell ref="BH2:BH7"/>
-    <mergeCell ref="BI2:BI7"/>
-    <mergeCell ref="BJ2:BJ7"/>
-    <mergeCell ref="CM2:CM7"/>
-    <mergeCell ref="CN2:CN7"/>
-    <mergeCell ref="CO2:CO7"/>
-    <mergeCell ref="CP2:CP7"/>
-    <mergeCell ref="CQ2:CQ7"/>
-    <mergeCell ref="BL2:BL7"/>
-    <mergeCell ref="BA2:BA7"/>
-    <mergeCell ref="BB2:BB7"/>
-    <mergeCell ref="BC2:BC7"/>
-    <mergeCell ref="AP2:AP7"/>
-    <mergeCell ref="AQ2:AQ7"/>
-    <mergeCell ref="AR2:AR7"/>
-    <mergeCell ref="AS2:AS7"/>
-    <mergeCell ref="AT2:AT7"/>
-    <mergeCell ref="AU2:AU7"/>
-    <mergeCell ref="AV2:AV7"/>
-    <mergeCell ref="AW2:AW7"/>
-    <mergeCell ref="EL2:EL7"/>
-    <mergeCell ref="EJ2:EJ7"/>
-    <mergeCell ref="EK2:EK7"/>
-    <mergeCell ref="EF2:EF7"/>
-    <mergeCell ref="EG2:EG7"/>
-    <mergeCell ref="EH2:EH7"/>
-    <mergeCell ref="EI2:EI7"/>
-    <mergeCell ref="DX2:DX7"/>
-    <mergeCell ref="DY2:DY7"/>
-    <mergeCell ref="DZ2:DZ7"/>
-    <mergeCell ref="EA2:EA7"/>
-    <mergeCell ref="EB2:EB7"/>
-    <mergeCell ref="EC2:EC7"/>
-    <mergeCell ref="ED2:ED7"/>
-    <mergeCell ref="EE2:EE7"/>
-    <mergeCell ref="T2:T7"/>
-    <mergeCell ref="EC8:EC9"/>
-    <mergeCell ref="Y2:Y7"/>
-    <mergeCell ref="Z2:Z7"/>
-    <mergeCell ref="AA2:AA7"/>
-    <mergeCell ref="AB2:AB7"/>
-    <mergeCell ref="AC2:AC7"/>
-    <mergeCell ref="AD2:AD7"/>
-    <mergeCell ref="AE2:AE7"/>
-    <mergeCell ref="AH2:AH7"/>
-    <mergeCell ref="AI2:AI7"/>
-    <mergeCell ref="AJ2:AJ7"/>
-    <mergeCell ref="AK2:AK7"/>
-    <mergeCell ref="AL2:AL7"/>
-    <mergeCell ref="AM2:AM7"/>
-    <mergeCell ref="AN2:AN7"/>
-    <mergeCell ref="AO2:AO7"/>
-    <mergeCell ref="AG2:AG7"/>
-    <mergeCell ref="BK2:BK7"/>
-    <mergeCell ref="X2:X7"/>
-    <mergeCell ref="AF2:AF7"/>
-    <mergeCell ref="AX2:AX7"/>
-    <mergeCell ref="AY2:AY7"/>
-    <mergeCell ref="AZ2:AZ7"/>
-    <mergeCell ref="M2:M7"/>
-    <mergeCell ref="F1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="N2:N7"/>
-    <mergeCell ref="O2:O7"/>
-    <mergeCell ref="P2:P7"/>
-    <mergeCell ref="Q2:Q7"/>
-    <mergeCell ref="R2:R7"/>
-    <mergeCell ref="S2:S7"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="E2:E7"/>
-    <mergeCell ref="F2:F7"/>
-    <mergeCell ref="G2:G7"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="I2:I7"/>
-    <mergeCell ref="J2:J7"/>
-    <mergeCell ref="K2:K7"/>
-    <mergeCell ref="L2:L7"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="E26:FI26"/>
-    <mergeCell ref="EU8:EU9"/>
-    <mergeCell ref="FF8:FF9"/>
-    <mergeCell ref="FG8:FG9"/>
-    <mergeCell ref="FH8:FH9"/>
-    <mergeCell ref="FI8:FI9"/>
-    <mergeCell ref="EN8:EN9"/>
-    <mergeCell ref="EO8:EO9"/>
-    <mergeCell ref="EB8:EB9"/>
-    <mergeCell ref="EL8:EL9"/>
-    <mergeCell ref="EM8:EM9"/>
-    <mergeCell ref="BU8:BU9"/>
-    <mergeCell ref="BV8:BV9"/>
-    <mergeCell ref="BW8:BW9"/>
-    <mergeCell ref="BF8:BF9"/>
-    <mergeCell ref="BG8:BG9"/>
-    <mergeCell ref="DV8:DV9"/>
-    <mergeCell ref="DW8:DW9"/>
-    <mergeCell ref="AW8:AW9"/>
-    <mergeCell ref="AX8:AX9"/>
-    <mergeCell ref="AY8:AY9"/>
-    <mergeCell ref="AZ8:AZ9"/>
-    <mergeCell ref="BA8:BA9"/>
-    <mergeCell ref="BB8:BB9"/>
-    <mergeCell ref="BQ2:BQ7"/>
-    <mergeCell ref="BR2:BR7"/>
-    <mergeCell ref="BS2:BS7"/>
-    <mergeCell ref="BT2:BT7"/>
-    <mergeCell ref="BU2:BU7"/>
-    <mergeCell ref="BV2:BV7"/>
-    <mergeCell ref="ED8:ED9"/>
-    <mergeCell ref="EE8:EE9"/>
-    <mergeCell ref="DW2:DW7"/>
-    <mergeCell ref="CB2:CB7"/>
-    <mergeCell ref="CC2:CC7"/>
-    <mergeCell ref="CD2:CD7"/>
-    <mergeCell ref="CE2:CE7"/>
-    <mergeCell ref="DU2:DU7"/>
-    <mergeCell ref="DV2:DV7"/>
-    <mergeCell ref="DY8:DY9"/>
-    <mergeCell ref="DX8:DX9"/>
-    <mergeCell ref="DZ8:DZ9"/>
-    <mergeCell ref="EA8:EA9"/>
-    <mergeCell ref="BX8:BX9"/>
-    <mergeCell ref="BY8:BY9"/>
-    <mergeCell ref="CR2:CR7"/>
-    <mergeCell ref="CS2:CS7"/>
-    <mergeCell ref="CT2:CT7"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AD8:AD9"/>
-    <mergeCell ref="CB8:CB9"/>
-    <mergeCell ref="CC8:CC9"/>
-    <mergeCell ref="CD8:CD9"/>
-    <mergeCell ref="CE8:CE9"/>
-    <mergeCell ref="DU8:DU9"/>
-    <mergeCell ref="EK8:EK9"/>
-    <mergeCell ref="EI8:EI9"/>
-    <mergeCell ref="EJ8:EJ9"/>
-    <mergeCell ref="CV8:CV9"/>
-    <mergeCell ref="CW8:CW9"/>
-    <mergeCell ref="CX8:CX9"/>
-    <mergeCell ref="CY8:CY9"/>
-    <mergeCell ref="CZ8:CZ9"/>
-    <mergeCell ref="DA8:DA9"/>
-    <mergeCell ref="DB8:DB9"/>
-    <mergeCell ref="DC8:DC9"/>
-    <mergeCell ref="DD8:DD9"/>
-    <mergeCell ref="DE8:DE9"/>
-    <mergeCell ref="DF8:DF9"/>
-    <mergeCell ref="DG8:DG9"/>
-    <mergeCell ref="DQ8:DQ9"/>
-    <mergeCell ref="BO8:BO9"/>
-    <mergeCell ref="BP8:BP9"/>
-    <mergeCell ref="BQ8:BQ9"/>
-    <mergeCell ref="BR8:BR9"/>
-    <mergeCell ref="BS8:BS9"/>
-    <mergeCell ref="BT8:BT9"/>
-    <mergeCell ref="BZ8:BZ9"/>
-    <mergeCell ref="CA8:CA9"/>
-    <mergeCell ref="BH8:BH9"/>
-    <mergeCell ref="BI8:BI9"/>
-    <mergeCell ref="BJ8:BJ9"/>
-    <mergeCell ref="BK8:BK9"/>
-    <mergeCell ref="BL8:BL9"/>
-    <mergeCell ref="BM8:BM9"/>
-    <mergeCell ref="BE8:BE9"/>
-    <mergeCell ref="AN8:AN9"/>
-    <mergeCell ref="AO8:AO9"/>
-    <mergeCell ref="AP8:AP9"/>
-    <mergeCell ref="AQ8:AQ9"/>
-    <mergeCell ref="AR8:AR9"/>
-    <mergeCell ref="AS8:AS9"/>
-    <mergeCell ref="AT8:AT9"/>
-    <mergeCell ref="AU8:AU9"/>
-    <mergeCell ref="AV8:AV9"/>
-    <mergeCell ref="O1:T1"/>
-    <mergeCell ref="U1:X1"/>
-    <mergeCell ref="Y1:AC1"/>
-    <mergeCell ref="AD1:AG1"/>
-    <mergeCell ref="AH1:AM1"/>
-    <mergeCell ref="AN1:AS1"/>
-    <mergeCell ref="AT1:AW1"/>
-    <mergeCell ref="BC8:BC9"/>
-    <mergeCell ref="BD8:BD9"/>
-    <mergeCell ref="AE8:AE9"/>
-    <mergeCell ref="AF8:AF9"/>
-    <mergeCell ref="AG8:AG9"/>
-    <mergeCell ref="AH8:AH9"/>
-    <mergeCell ref="AI8:AI9"/>
-    <mergeCell ref="AJ8:AJ9"/>
-    <mergeCell ref="AK8:AK9"/>
-    <mergeCell ref="AL8:AL9"/>
-    <mergeCell ref="AM8:AM9"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="DR8:DR9"/>
+    <mergeCell ref="DS8:DS9"/>
+    <mergeCell ref="DT8:DT9"/>
+    <mergeCell ref="DH8:DH9"/>
+    <mergeCell ref="DI8:DI9"/>
+    <mergeCell ref="DJ8:DJ9"/>
+    <mergeCell ref="DK8:DK9"/>
+    <mergeCell ref="DL8:DL9"/>
+    <mergeCell ref="DM8:DM9"/>
+    <mergeCell ref="DN8:DN9"/>
+    <mergeCell ref="DO8:DO9"/>
+    <mergeCell ref="DP8:DP9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -6698,49 +6769,49 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="56" t="s">
-        <v>35</v>
-      </c>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="55" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="58" t="s">
+      <c r="B3" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="59"/>
-      <c r="D3" s="62" t="s">
+      <c r="C3" s="58"/>
+      <c r="D3" s="61" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="54" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="55" t="s">
+      <c r="F3" s="54" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="55" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" s="55" t="s">
+      <c r="H3" s="55" t="s">
         <v>32</v>
-      </c>
-      <c r="H3" s="56" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="35"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="56"/>
+      <c r="A4" s="42"/>
+      <c r="B4" s="59"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="55"/>
     </row>
     <row r="5" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
@@ -6752,23 +6823,23 @@
       <c r="C5" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="17">
         <f>COUNTIF('html&amp;css'!F11:G11,0)</f>
         <v>0</v>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="17">
         <f>COUNTIF('html&amp;css'!H11:Y11,0)</f>
         <v>0</v>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="17">
         <f>COUNTIF('html&amp;css'!Z11:AY11,0)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="18">
+      <c r="G5" s="17">
         <f>COUNTIF('html&amp;css'!AZ11:BU11,0)</f>
         <v>0</v>
       </c>
-      <c r="H5" s="19"/>
+      <c r="H5" s="18"/>
     </row>
     <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
@@ -6780,23 +6851,23 @@
       <c r="C6" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="17">
         <f>COUNTIF('html&amp;css'!F12:G12,0)</f>
         <v>0</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="17">
         <f>COUNTIF('html&amp;css'!H12:Y12,0)</f>
         <v>0</v>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="17">
         <f>COUNTIF('html&amp;css'!Z12:AY12,0)</f>
         <v>0</v>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="17">
         <f>COUNTIF('html&amp;css'!AZ12:BU12,0)</f>
         <v>0</v>
       </c>
-      <c r="H6" s="19"/>
+      <c r="H6" s="18"/>
     </row>
     <row r="7" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
@@ -6808,23 +6879,23 @@
       <c r="C7" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="17">
         <f>COUNTIF('html&amp;css'!F13:G13,0)</f>
         <v>0</v>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="17">
         <f>COUNTIF('html&amp;css'!H13:Y13,0)</f>
         <v>0</v>
       </c>
-      <c r="F7" s="18">
+      <c r="F7" s="17">
         <f>COUNTIF('html&amp;css'!Z13:AY13,0)</f>
         <v>0</v>
       </c>
-      <c r="G7" s="18">
+      <c r="G7" s="17">
         <f>COUNTIF('html&amp;css'!AZ13:BU13,0)</f>
         <v>0</v>
       </c>
-      <c r="H7" s="19"/>
+      <c r="H7" s="18"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
@@ -6836,23 +6907,23 @@
       <c r="C8" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="17">
         <f>COUNTIF('html&amp;css'!F14:G14,0)</f>
         <v>0</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="17">
         <f>COUNTIF('html&amp;css'!H14:Y14,0)</f>
         <v>0</v>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="17">
         <f>COUNTIF('html&amp;css'!Z14:AY14,0)</f>
         <v>0</v>
       </c>
-      <c r="G8" s="18">
+      <c r="G8" s="17">
         <f>COUNTIF('html&amp;css'!AZ14:BU14,0)</f>
         <v>0</v>
       </c>
-      <c r="H8" s="19"/>
+      <c r="H8" s="18"/>
     </row>
     <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
@@ -6864,23 +6935,23 @@
       <c r="C9" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="17">
         <f>COUNTIF('html&amp;css'!F15:G15,0)</f>
         <v>0</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="17">
         <f>COUNTIF('html&amp;css'!H15:Y15,0)</f>
         <v>0</v>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="17">
         <f>COUNTIF('html&amp;css'!Z15:AY15,0)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="18">
+      <c r="G9" s="17">
         <f>COUNTIF('html&amp;css'!AZ15:BU15,0)</f>
         <v>0</v>
       </c>
-      <c r="H9" s="19"/>
+      <c r="H9" s="18"/>
     </row>
     <row r="10" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
@@ -6892,23 +6963,23 @@
       <c r="C10" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="17">
         <f>COUNTIF('html&amp;css'!F16:G16,0)</f>
         <v>0</v>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="17">
         <f>COUNTIF('html&amp;css'!H16:Y16,0)</f>
         <v>0</v>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="17">
         <f>COUNTIF('html&amp;css'!Z16:AY16,0)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="17">
         <f>COUNTIF('html&amp;css'!AZ16:BU16,0)</f>
         <v>0</v>
       </c>
-      <c r="H10" s="19"/>
+      <c r="H10" s="18"/>
     </row>
     <row r="11" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
@@ -6920,23 +6991,23 @@
       <c r="C11" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="17">
         <f>COUNTIF('html&amp;css'!F17:G17,0)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="17">
         <f>COUNTIF('html&amp;css'!H17:Y17,0)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="17">
         <f>COUNTIF('html&amp;css'!Z17:AY17,0)</f>
         <v>0</v>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="17">
         <f>COUNTIF('html&amp;css'!AZ17:BU17,0)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="19"/>
+      <c r="H11" s="18"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
@@ -6948,23 +7019,23 @@
       <c r="C12" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="17">
         <f>COUNTIF('html&amp;css'!F18:G18,0)</f>
         <v>0</v>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="17">
         <f>COUNTIF('html&amp;css'!H18:Y18,0)</f>
         <v>0</v>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="17">
         <f>COUNTIF('html&amp;css'!Z18:AY18,0)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="17">
         <f>COUNTIF('html&amp;css'!AZ18:BU18,0)</f>
         <v>0</v>
       </c>
-      <c r="H12" s="19"/>
+      <c r="H12" s="18"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
@@ -6972,11 +7043,11 @@
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
@@ -6984,11 +7055,11 @@
       </c>
       <c r="B14" s="13"/>
       <c r="C14" s="10"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
@@ -6996,11 +7067,11 @@
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
@@ -7008,11 +7079,11 @@
       </c>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
@@ -7020,11 +7091,11 @@
       </c>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
@@ -7032,11 +7103,11 @@
       </c>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
@@ -7044,11 +7115,11 @@
       </c>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
@@ -7056,11 +7127,11 @@
       </c>
       <c r="B20" s="10"/>
       <c r="C20" s="10"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="9">
